--- a/submissions/10-carton-bid-evaluation/solution/bid_evaluation_itb_2026_17.xlsx
+++ b/submissions/10-carton-bid-evaluation/solution/bid_evaluation_itb_2026_17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABB50D2-67A2-1A48-AB4C-151DDBA35EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E974349-F641-3E4D-80F5-079959CFB2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="467">
   <si>
     <t>Award recommendation, ITB 2026-17, corrugated shipping cartons, annual requirement</t>
   </si>
@@ -176,10 +176,13 @@
     <t>Unit price changes not considered under section 3.4</t>
   </si>
   <si>
+    <t>Informality waived under 5.7</t>
+  </si>
+  <si>
     <t>Award is by lot to the responsive and responsible bidder first in the order of 5.1 and 5.6, checked under PP-3.7.1; every figure on this page reads from the tab named beside it.</t>
   </si>
   <si>
-    <t>The award value is at or under one hundred thousand dollars, so PP-3.5.3 places the approval with the director of supply chain; the signature line below follows the policy.</t>
+    <t>The award value is over one hundred thousand dollars, so PP-3.5.3 places the approval with the vice president of operations; the signature line below follows the policy.</t>
   </si>
   <si>
     <t>Recommended by</t>
@@ -197,7 +200,7 @@
     <t>Approved</t>
   </si>
   <si>
-    <t>Director of supply chain</t>
+    <t>Torsten Nordvik, Vice President of Operations</t>
   </si>
   <si>
     <t>Terms the evaluation applies, from ITB 2026-17 as amended and policy PP-3</t>
@@ -446,9 +449,6 @@
     <t>1% 30, net 45</t>
   </si>
   <si>
-    <t>Cashier's check, $4,904.75, no. 20871</t>
-  </si>
-  <si>
     <t>1, 2</t>
   </si>
   <si>
@@ -545,603 +545,618 @@
     <t>Ridgecrest Packaging</t>
   </si>
   <si>
+    <t>Omaha</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>Origin, shipping plant</t>
+  </si>
+  <si>
+    <t>1% 20, net 45</t>
+  </si>
+  <si>
+    <t>Cashier's check, $4,554.95, no. 7730412</t>
+  </si>
+  <si>
+    <t>Items 1 to 4 Omaha, NE; item 5 Cedar Rapids, IA; office in Cedar Rapids</t>
+  </si>
+  <si>
+    <t>Thorsgard Box &amp; Label</t>
+  </si>
+  <si>
+    <t>Moorhead</t>
+  </si>
+  <si>
+    <t>2% 25, net 45</t>
+  </si>
+  <si>
+    <t>All items Moorhead, MN</t>
+  </si>
+  <si>
+    <t>Wenzel &amp; Krause Corrugated</t>
+  </si>
+  <si>
+    <t>La Crosse</t>
+  </si>
+  <si>
+    <t>2% 20, net 30</t>
+  </si>
+  <si>
+    <t>Cashier's check, $5,300.00, no. 553106</t>
+  </si>
+  <si>
+    <t>All items La Crosse, WI</t>
+  </si>
+  <si>
+    <t>Pricing conditions, exceptions and alternates read from each bid form and letter in bid_forms_itb_2026_17.docx</t>
+  </si>
+  <si>
+    <t>CONDITION_AS_STATED</t>
+  </si>
+  <si>
+    <t>TERM_AFFECTED</t>
+  </si>
+  <si>
+    <t>MATERIAL_TERM_EXCEPTION</t>
+  </si>
+  <si>
+    <t>RULE_APPLIED</t>
+  </si>
+  <si>
+    <t>PRICES_FIRM_THROUGH</t>
+  </si>
+  <si>
+    <t>None stated; the form acknowledges addendum 1 only and prices item 3 at 36,000 with item 5 on 32 ECT board</t>
+  </si>
+  <si>
+    <t>Quantity and specification as amended</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Handled under addendum 2 and PP-3.4.5 on the Responsiveness tab, not as an exception</t>
+  </si>
+  <si>
+    <t>Twelve months from award</t>
+  </si>
+  <si>
+    <t>None; releases taken in any pallet quantity; the form extends item 2 at 25,900.00 against 25,600.00 at the unit price</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>No condition on price, quantity, quality, delivery or FOB terms; the extension is corrected under 4.1 on the Extensions tab</t>
+  </si>
+  <si>
+    <t>Prices firm for twelve months, with a raw material surcharge on the unit prices should the Pulp and Paper Week 42 lb kraft linerboard index rise more than 6 percent from award; the form boxes read Yes and None</t>
+  </si>
+  <si>
+    <t>Price hold, section 4.3</t>
+  </si>
+  <si>
+    <t>section 4.3 makes a bid that conditions its prices on an index an exception to a material term; section 5.2; PP-3.4.4</t>
+  </si>
+  <si>
+    <t>None; prices hold through December 31, 2027, which runs past twelve months from any award this year</t>
+  </si>
+  <si>
+    <t>The hold meets section 4.3; the item 2 description is tested on the Responsiveness tab under PP-3.4.5</t>
+  </si>
+  <si>
+    <t>12/31/2027</t>
+  </si>
+  <si>
+    <t>None; releases requested at least ten working days ahead of delivery</t>
+  </si>
+  <si>
+    <t>A scheduling request, not a condition on price, quantity, quality, delivery or FOB terms</t>
+  </si>
+  <si>
+    <t>Item 4 offered on 200 lb test doublewall only, the Duluth plant not running 275 lb test; FOB origin, all five items from Duluth</t>
+  </si>
+  <si>
+    <t>Item as specified, section 5.2; alternate under 4.4</t>
+  </si>
+  <si>
+    <t>No bid on item 4 as specified; the alternate cannot stand alone under 4.4 and the addendum 2 answer, tested on the Responsiveness tab under 5.2. Freight is added under section 5.4 at the Minnesota rate</t>
+  </si>
+  <si>
+    <t>Pricing is for releases of 20 pallets or more; a delivery-efficiency fee of $185 applies to any release under 20 pallets; the form box reads None</t>
+  </si>
+  <si>
+    <t>Quantity, releases in pallet multiples, section 1</t>
+  </si>
+  <si>
+    <t>A fee tied to the release quantity changes the price of the releases that section 1 provides for, which makes it an exception to the quantity term under section 5.2 and PP-3.4.4. The letter of October 8 reached the office after the due time, section 3.4</t>
+  </si>
+  <si>
+    <t>Alternate for item 4 at 200 lb test doublewall, $1.512 per carton, beside the bid on the item as specified; the form is signed by a regional sales manager where 3.3 asks for an officer</t>
+  </si>
+  <si>
+    <t>None; an alternate under section 4.4; an informality on the signature</t>
+  </si>
+  <si>
+    <t>section 4.4; the alternate is not evaluated for award. The signature is an informality that does not affect price, quantity, quality or delivery, waived under 5.7 and PP-3.4.4 and recorded on the Responsiveness tab</t>
+  </si>
+  <si>
+    <t>None; FOB origin, the office in Cedar Rapids, items 1 to 4 shipped from the Omaha plant and item 5 from the Cedar Rapids plant; tooling credited back if the award arrives by October 30; a cashier's check of $4,554.95</t>
+  </si>
+  <si>
+    <t>FOB terms as permitted by 3.3</t>
+  </si>
+  <si>
+    <t>FOB origin is permitted by 3.3, with freight added under section 5.4 for the plant that ships each item. The tooling credit is not an adjustment the invitation names, so tooling is added in full under 4.2 and PP-3.4.3. The check is tested on the Bid Security tab</t>
+  </si>
+  <si>
+    <t>Prices firm through September 30, 2027; the form box reads Yes to twelve months from award</t>
+  </si>
+  <si>
+    <t>section 4.3; section 5.2; PP-3.4.4; twelve months from an award made after the October 6, 2026 opening runs past September 30, 2027</t>
+  </si>
+  <si>
+    <t>09/30/2027</t>
+  </si>
+  <si>
+    <t>None; the letter follows the linerboard index and holds prices firm for twelve months whatever the index does, offers stock holding after award that the prices do not depend on, and says the item 5 sample was run on 32 ECT board</t>
+  </si>
+  <si>
+    <t>Prices are not conditioned on the index or on the stock offer, section 4.3; the sample is tested on the Responsiveness tab under section 3.2</t>
+  </si>
+  <si>
+    <t>A condition is a material term exception where it would change price, price hold, quantity, quality, delivery or FOB terms, PP-3.4.4; the buyer does not negotiate it away before award.</t>
+  </si>
+  <si>
+    <t>Writings and messages received on the bids other than the bids themselves, from bid_correspondence_itb_2026_17.docx and bid_receipt_log_itb_2026_17.xlsx</t>
+  </si>
+  <si>
+    <t>WRITING</t>
+  </si>
+  <si>
+    <t>DATED</t>
+  </si>
+  <si>
+    <t>LOG_NO</t>
+  </si>
+  <si>
+    <t>RECEIVED_DATE</t>
+  </si>
+  <si>
+    <t>RECEIVED_TIME</t>
+  </si>
+  <si>
+    <t>RECEIVED_KEY</t>
+  </si>
+  <si>
+    <t>BEFORE_THE_DUE_TIME</t>
+  </si>
+  <si>
+    <t>SIGNED_WRITING</t>
+  </si>
+  <si>
+    <t>EFFECT_ON_THE_EVALUATION</t>
+  </si>
+  <si>
+    <t>Letter withdrawing the bid delivered October 2</t>
+  </si>
+  <si>
+    <t>10/05/2026</t>
+  </si>
+  <si>
+    <t>R-1048</t>
+  </si>
+  <si>
+    <t>15:52</t>
+  </si>
+  <si>
+    <t>Bid withdrawn and resubmitted; the bid opened is the one received October 6 at 08:15, section 3.4</t>
+  </si>
+  <si>
+    <t>Facsimile changing the five unit prices</t>
+  </si>
+  <si>
+    <t>R-1060</t>
+  </si>
+  <si>
+    <t>10/06/2026</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>Not considered; the bid stands at its sealed prices, section 3.4</t>
+  </si>
+  <si>
+    <t>Facsimile changing the item 1 unit price</t>
+  </si>
+  <si>
+    <t>R-1053</t>
+  </si>
+  <si>
+    <t>09:12</t>
+  </si>
+  <si>
+    <t>Applied; item 1 is evaluated at 0.578, and the bid keeps its receipt time, section 3.4</t>
+  </si>
+  <si>
+    <t>Telephone message asking that item 1 be read at 0.594</t>
+  </si>
+  <si>
+    <t>R-1056</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>Not considered; a modification is a signed writing, section 3.4; item 1 stands at 0.597 on the signed form</t>
+  </si>
+  <si>
+    <t>Letter withdrawing the delivery-efficiency fee</t>
+  </si>
+  <si>
+    <t>10/08/2026</t>
+  </si>
+  <si>
+    <t>R-1062</t>
+  </si>
+  <si>
+    <t>10/09/2026</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>Not considered; the exception in the bid stands, section 3.4 and PP-3.4.4</t>
+  </si>
+  <si>
+    <t>Letter on the edge crush complaint, hold QH-26-031</t>
+  </si>
+  <si>
+    <t>10/12/2026</t>
+  </si>
+  <si>
+    <t>R-1063</t>
+  </si>
+  <si>
+    <t>16:44</t>
+  </si>
+  <si>
+    <t>Not a change to the bid; the hold is cleared only by quality engineering, PP-3.7.1</t>
+  </si>
+  <si>
+    <t>UNIT_AS_BID</t>
+  </si>
+  <si>
+    <t>UNIT_AS_CHANGED</t>
+  </si>
+  <si>
+    <t>WRITING_ROW</t>
+  </si>
+  <si>
+    <t>APPLIED</t>
+  </si>
+  <si>
+    <t>CHANGE_IN_EXTENSION</t>
+  </si>
+  <si>
+    <t>Unit price changes applied</t>
+  </si>
+  <si>
+    <t>Unit price changes not considered</t>
+  </si>
+  <si>
+    <t>A modification counts when it is a signed writing that reaches the purchasing office before 10:00 on October 6, whatever date it carries, section 3.4. The Wenzel &amp; Krause facsimile is dated October 5 and came off the machine at 10:07 on October 6. The telephone message from Dahlgren at 09:38 is not a writing. The log enters the facsimiles and the message under the names of the people who sent them.</t>
+  </si>
+  <si>
+    <t>Bid security against five percent of the total bid as written, section 3.2 and addendum 2</t>
+  </si>
+  <si>
+    <t>AMOUNT_STATED</t>
+  </si>
+  <si>
+    <t>TOTAL_BID_AS_WRITTEN</t>
+  </si>
+  <si>
+    <t>FIVE_PERCENT_REQUIRED</t>
+  </si>
+  <si>
+    <t>SHORT_BY</t>
+  </si>
+  <si>
+    <t>MEETS_SECTION_3.2</t>
+  </si>
+  <si>
+    <t>A surety bond is written at five percent of the total bid and meets section 3.2 at any total. A cashier's check is a fixed amount and is tested against five percent of the total bid as written, tooling included, per addendum 2. Ridgecrest's check is five percent of its extensions alone and falls $120.00 short of five percent of its total bid as written.</t>
+  </si>
+  <si>
+    <t>When each bid that was opened reached the purchasing office, from bid_receipt_log_itb_2026_17.xlsx</t>
+  </si>
+  <si>
+    <t>NAME_IN_THE_LOG</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>Brannock Box</t>
+  </si>
+  <si>
+    <t>R-1049</t>
+  </si>
+  <si>
+    <t>16:02</t>
+  </si>
+  <si>
+    <t>Dahlgren Box, St. Cloud</t>
+  </si>
+  <si>
+    <t>R-1055</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>Halvard</t>
+  </si>
+  <si>
+    <t>R-1058</t>
+  </si>
+  <si>
+    <t>09:58</t>
+  </si>
+  <si>
+    <t>Kessel Container, Des Moines</t>
+  </si>
+  <si>
+    <t>R-1040</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>09:47</t>
+  </si>
+  <si>
+    <t>Loken &amp; Vik</t>
+  </si>
+  <si>
+    <t>R-1059</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>Handed over at 10:00, the due time; a bid is due by 10:00 and only a bid received after that time goes back unopened, section 3.1</t>
+  </si>
+  <si>
+    <t>Mesabi Container, Duluth</t>
+  </si>
+  <si>
+    <t>R-1052</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>Otter Tail Corr.</t>
+  </si>
+  <si>
+    <t>R-1051</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>Pemberton, Neenah</t>
+  </si>
+  <si>
+    <t>R-1047</t>
+  </si>
+  <si>
+    <t>11:37</t>
+  </si>
+  <si>
+    <t>The facsimile of October 6 changes the bid and leaves this receipt time, section 3.4</t>
+  </si>
+  <si>
+    <t>A. Delaney</t>
+  </si>
+  <si>
+    <t>R-1050</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>The envelope logged R-1041 on 10/02/2026 was withdrawn and handed back under R-1048; the bid opened is the resubmitted one, section 3.4</t>
+  </si>
+  <si>
+    <t>Thorsgard, Moorhead</t>
+  </si>
+  <si>
+    <t>R-1054</t>
+  </si>
+  <si>
+    <t>09:27</t>
+  </si>
+  <si>
+    <t>W &amp; K Corrugated, La Crosse</t>
+  </si>
+  <si>
+    <t>R-1057</t>
+  </si>
+  <si>
+    <t>09:41</t>
+  </si>
+  <si>
+    <t>Bids received by the due time</t>
+  </si>
+  <si>
+    <t>A twelfth envelope, from Siouxland Container, reached the office at 10:22 on October 6 and went back unopened under section 3.1; it is not a bid in this evaluation. Loken &amp; Vik's envelope was handed over at 10:00, which section 3.1 makes the last minute a bid is due, and it was opened.</t>
+  </si>
+  <si>
+    <t>Quality holds recorded against any bidder in supplier_quality_holds_2026.xlsx, matched to the bidder by name, with clearances since the extract</t>
+  </si>
+  <si>
+    <t>HOLD_NO</t>
+  </si>
+  <si>
+    <t>SUPPLIER_AS_REGISTERED</t>
+  </si>
+  <si>
+    <t>COMMODITY</t>
+  </si>
+  <si>
+    <t>OPENED</t>
+  </si>
+  <si>
+    <t>STATUS_IN_THE_EXTRACT</t>
+  </si>
+  <si>
+    <t>CLEARED</t>
+  </si>
+  <si>
+    <t>SOURCE_OF_THE_CLEARANCE</t>
+  </si>
+  <si>
+    <t>STATUS_AT_RECOMMENDATION</t>
+  </si>
+  <si>
+    <t>ADDRESS_IN_THE_REGISTER</t>
+  </si>
+  <si>
+    <t>QH-25-024</t>
+  </si>
+  <si>
+    <t>Corrugated, RSC 30 x 20 x 16</t>
+  </si>
+  <si>
+    <t>10/08/2025</t>
+  </si>
+  <si>
+    <t>Cleared</t>
+  </si>
+  <si>
+    <t>11/04/2025</t>
+  </si>
+  <si>
+    <t>Register extract of October 7</t>
+  </si>
+  <si>
+    <t>3811 12th Avenue North, Fargo, ND</t>
+  </si>
+  <si>
+    <t>QH-26-009</t>
+  </si>
+  <si>
+    <t>Corrugated, RSC 24 x 18 x 12</t>
+  </si>
+  <si>
+    <t>03/04/2026</t>
+  </si>
+  <si>
+    <t>05/12/2026</t>
+  </si>
+  <si>
+    <t>900 Industrial Drive, Neenah, WI</t>
+  </si>
+  <si>
+    <t>QH-26-031</t>
+  </si>
+  <si>
+    <t>L&amp;V Container Corp., Sioux Falls</t>
+  </si>
+  <si>
+    <t>Corrugated, RSC 16 x 12 x 8</t>
+  </si>
+  <si>
+    <t>08/27/2026</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>None recorded; quality engineering e-mail of October 20: verification lot received October 16 and passed, clearance not yet signed by the quality manager</t>
+  </si>
+  <si>
+    <t>4700 North Cliff Avenue, Sioux Falls, SD</t>
+  </si>
+  <si>
+    <t>QH-26-034</t>
+  </si>
+  <si>
+    <t>Pemberton Container, Neenah plant</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>10/15/2026</t>
+  </si>
+  <si>
+    <t>Quality engineering clearance notice of October 15</t>
+  </si>
+  <si>
+    <t>The register carries Loken &amp; Vik Container under the trade name L&amp;V Container Corp., Sioux Falls, at 4700 North Cliff Avenue, the address on its bid form. Loken Container Supply, Sioux City, Iowa, on an open hold at 2100 Dace Avenue, is a different company. PP-3.7.1 clears a hold on quality engineering's clearance, and the e-mail of October 20 says the clearance of QH-26-031 is unsigned although the verification lot passed on October 16, so the hold is open at the date of this recommendation.</t>
+  </si>
+  <si>
+    <t>Freight on the FOB origin bid under 5.4: current item weights, the plant that ships each item, and the schedule rate for that plant's state</t>
+  </si>
+  <si>
+    <t>DRAWING_REV</t>
+  </si>
+  <si>
+    <t>LB_PER_CARTON</t>
+  </si>
+  <si>
+    <t>QUANTITY</t>
+  </si>
+  <si>
+    <t>SHIPPING_LB</t>
+  </si>
+  <si>
+    <t>HUNDREDWEIGHT</t>
+  </si>
+  <si>
+    <t>SHIPPING_PLANT</t>
+  </si>
+  <si>
+    <t>STATE</t>
+  </si>
+  <si>
+    <t>RATE_PER_CWT</t>
+  </si>
+  <si>
+    <t>FREIGHT</t>
+  </si>
+  <si>
+    <t>FOB_ORIGIN_BIDDER</t>
+  </si>
+  <si>
+    <t>ORIGIN_STATE</t>
+  </si>
+  <si>
+    <t>NM-CTN-26-01 rev A</t>
+  </si>
+  <si>
+    <t>NM-CTN-26-02 rev B</t>
+  </si>
+  <si>
+    <t>NM-CTN-26-03 rev A</t>
+  </si>
+  <si>
+    <t>NM-CTN-26-04 rev A</t>
+  </si>
+  <si>
+    <t>NM-CTN-26-05 rev B</t>
+  </si>
+  <si>
     <t>Cedar Rapids</t>
   </si>
   <si>
-    <t>Origin, shipping plant</t>
-  </si>
-  <si>
-    <t>1% 20, net 45</t>
-  </si>
-  <si>
-    <t>Items 1 to 4 Cedar Rapids, IA; item 5 Omaha, NE</t>
-  </si>
-  <si>
-    <t>Thorsgard Box &amp; Label</t>
-  </si>
-  <si>
-    <t>Moorhead</t>
-  </si>
-  <si>
-    <t>2% 25, net 45</t>
-  </si>
-  <si>
-    <t>All items Moorhead, MN</t>
-  </si>
-  <si>
-    <t>Wenzel &amp; Krause Corrugated</t>
-  </si>
-  <si>
-    <t>La Crosse</t>
-  </si>
-  <si>
-    <t>2% 20, net 30</t>
-  </si>
-  <si>
-    <t>Cashier's check, $5,300.00, no. 553106</t>
-  </si>
-  <si>
-    <t>All items La Crosse, WI</t>
-  </si>
-  <si>
-    <t>Pricing conditions, exceptions and alternates read from each bid form and letter in bid_forms_itb_2026_17.docx</t>
-  </si>
-  <si>
-    <t>CONDITION_AS_STATED</t>
-  </si>
-  <si>
-    <t>TERM_AFFECTED</t>
-  </si>
-  <si>
-    <t>MATERIAL_TERM_EXCEPTION</t>
-  </si>
-  <si>
-    <t>RULE_APPLIED</t>
-  </si>
-  <si>
-    <t>PRICES_FIRM_THROUGH</t>
-  </si>
-  <si>
-    <t>None stated; the form acknowledges addendum 1 only and prices item 3 at 36,000 with item 5 on 32 ECT board</t>
-  </si>
-  <si>
-    <t>Quantity and specification as amended</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Handled under addendum 2 and PP-3.4.5 on the Responsiveness tab, not as an exception</t>
-  </si>
-  <si>
-    <t>Twelve months from award</t>
-  </si>
-  <si>
-    <t>None; releases taken in any pallet quantity</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>No condition on price, quantity, quality, delivery or FOB terms; the bid security is tested on the Bid Security tab</t>
-  </si>
-  <si>
-    <t>Prices held firm for six months from award, then adjusted quarterly to the Pulp and Paper Week 42 lb kraft linerboard index</t>
-  </si>
-  <si>
-    <t>Price hold, section 4.3</t>
-  </si>
-  <si>
-    <t>section 4.3; section 5.2; addendum 2 answer on a shorter hold or an index; PP-3.4.4</t>
-  </si>
-  <si>
-    <t>None; prices hold through December 31, 2027, which runs past twelve months from any award this year</t>
-  </si>
-  <si>
-    <t>The hold meets section 4.3; the item 2 description is tested on the Responsiveness tab under PP-3.4.5</t>
-  </si>
-  <si>
-    <t>12/31/2027</t>
-  </si>
-  <si>
-    <t>None; releases requested at least ten working days ahead of delivery</t>
-  </si>
-  <si>
-    <t>A scheduling request, not a condition on price, quantity, quality, delivery or FOB terms</t>
-  </si>
-  <si>
-    <t>Item 4 offered on 200 lb test doublewall only, the Duluth plant not running 275 lb test; FOB origin, all five items from Duluth</t>
-  </si>
-  <si>
-    <t>Item as specified, section 5.2; alternate under 4.4</t>
-  </si>
-  <si>
-    <t>No bid on item 4 as specified; the alternate cannot stand alone under 4.4 and the addendum 2 answer, tested on the Responsiveness tab under 5.2. Freight is added under section 5.4 at the Minnesota rate</t>
-  </si>
-  <si>
-    <t>Pricing assumes releases in full truckload quantities of 26 pallets; a release below a full truckload carries a $185 stop charge; the form box reads None</t>
-  </si>
-  <si>
-    <t>Quantity, releases in pallet multiples, section 1</t>
-  </si>
-  <si>
-    <t>section 5.2; addendum 2 answer on truckload releases; PP-3.4.4; the letter of October 8 reached the office after the due time, section 3.4</t>
-  </si>
-  <si>
-    <t>Alternate for item 4 at 200 lb test doublewall, $1.512 per carton, beside the bid on the item as specified</t>
-  </si>
-  <si>
-    <t>None; an alternate under section 4.4</t>
-  </si>
-  <si>
-    <t>section 4.4; the alternate is not evaluated for award</t>
-  </si>
-  <si>
-    <t>None; FOB origin, items 1 to 4 shipped from Cedar Rapids and item 5 from Omaha; tooling credited back if the award arrives by October 30</t>
-  </si>
-  <si>
-    <t>FOB terms as permitted by 3.3</t>
-  </si>
-  <si>
-    <t>3.3; freight added under section 5.4; the tooling credit is not an adjustment the invitation names, so tooling is added in full, 4.2 and PP-3.4.3</t>
-  </si>
-  <si>
-    <t>Prices firm through September 30, 2027; the form box reads Yes to twelve months from award</t>
-  </si>
-  <si>
-    <t>section 4.3; section 5.2; PP-3.4.4; twelve months from an award made after the October 6, 2026 opening runs past September 30, 2027</t>
-  </si>
-  <si>
-    <t>09/30/2027</t>
-  </si>
-  <si>
-    <t>None; the letter follows the linerboard index and holds prices firm for twelve months whatever the index does, and offers stock holding after award that the prices do not depend on</t>
-  </si>
-  <si>
-    <t>Prices are not conditioned on the index or on the stock offer, section 4.3</t>
-  </si>
-  <si>
-    <t>A condition is a material term exception where it would change price, price hold, quantity, quality, delivery or FOB terms, PP-3.4.4; the buyer does not negotiate it away before award.</t>
-  </si>
-  <si>
-    <t>Writings and messages received on the bids other than the bids themselves, from bid_correspondence_itb_2026_17.docx and bid_receipt_log_itb_2026_17.xlsx</t>
-  </si>
-  <si>
-    <t>WRITING</t>
-  </si>
-  <si>
-    <t>DATED</t>
-  </si>
-  <si>
-    <t>LOG_NO</t>
-  </si>
-  <si>
-    <t>RECEIVED_DATE</t>
-  </si>
-  <si>
-    <t>RECEIVED_TIME</t>
-  </si>
-  <si>
-    <t>RECEIVED_KEY</t>
-  </si>
-  <si>
-    <t>BEFORE_THE_DUE_TIME</t>
-  </si>
-  <si>
-    <t>SIGNED_WRITING</t>
-  </si>
-  <si>
-    <t>EFFECT_ON_THE_EVALUATION</t>
-  </si>
-  <si>
-    <t>Letter withdrawing the bid delivered October 2</t>
-  </si>
-  <si>
-    <t>10/05/2026</t>
-  </si>
-  <si>
-    <t>R-1048</t>
-  </si>
-  <si>
-    <t>15:52</t>
-  </si>
-  <si>
-    <t>Bid withdrawn and resubmitted; the bid opened is the one received October 6 at 08:15, section 3.4</t>
-  </si>
-  <si>
-    <t>Facsimile changing the five unit prices</t>
-  </si>
-  <si>
-    <t>R-1060</t>
-  </si>
-  <si>
-    <t>10/06/2026</t>
-  </si>
-  <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>Not considered; the bid stands at its sealed prices, section 3.4</t>
-  </si>
-  <si>
-    <t>Facsimile changing the item 1 unit price</t>
-  </si>
-  <si>
-    <t>R-1053</t>
-  </si>
-  <si>
-    <t>09:12</t>
-  </si>
-  <si>
-    <t>Applied; item 1 is evaluated at 0.578, and the bid keeps its receipt time, section 3.4</t>
-  </si>
-  <si>
-    <t>Telephone message asking that item 3 be read at 0.255</t>
-  </si>
-  <si>
-    <t>R-1056</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>Not considered; a modification is a signed writing, section 3.4; item 3 stands at 0.262 on the signed form</t>
-  </si>
-  <si>
-    <t>Letter withdrawing the stop charge</t>
-  </si>
-  <si>
-    <t>10/08/2026</t>
-  </si>
-  <si>
-    <t>R-1062</t>
-  </si>
-  <si>
-    <t>10/09/2026</t>
-  </si>
-  <si>
-    <t>11:46</t>
-  </si>
-  <si>
-    <t>Not considered; the exception in the bid stands, section 3.4 and PP-3.4.4</t>
-  </si>
-  <si>
-    <t>Letter on the edge crush complaint, hold QH-26-031</t>
-  </si>
-  <si>
-    <t>10/12/2026</t>
-  </si>
-  <si>
-    <t>R-1063</t>
-  </si>
-  <si>
-    <t>16:44</t>
-  </si>
-  <si>
-    <t>Not a change to the bid; the hold is cleared only by quality engineering, PP-3.7.1</t>
-  </si>
-  <si>
-    <t>UNIT_AS_BID</t>
-  </si>
-  <si>
-    <t>UNIT_AS_CHANGED</t>
-  </si>
-  <si>
-    <t>WRITING_ROW</t>
-  </si>
-  <si>
-    <t>APPLIED</t>
-  </si>
-  <si>
-    <t>CHANGE_IN_EXTENSION</t>
-  </si>
-  <si>
-    <t>Unit price changes applied</t>
-  </si>
-  <si>
-    <t>Unit price changes not considered</t>
-  </si>
-  <si>
-    <t>A modification counts when it is a signed writing that reaches the purchasing office before 10:00 on October 6, whatever date it carries, section 3.4. The Wenzel &amp; Krause facsimile is dated October 5 and came off the machine at 10:07 on October 6. The telephone message from Ridgecrest at 09:35 is not a writing. The log enters the facsimiles and the message under the names of the people who sent them.</t>
-  </si>
-  <si>
-    <t>Bid security against five percent of the total bid as written, section 3.2 and addendum 2</t>
-  </si>
-  <si>
-    <t>AMOUNT_STATED</t>
-  </si>
-  <si>
-    <t>TOTAL_BID_AS_WRITTEN</t>
-  </si>
-  <si>
-    <t>FIVE_PERCENT_REQUIRED</t>
-  </si>
-  <si>
-    <t>SHORT_BY</t>
-  </si>
-  <si>
-    <t>MEETS_SECTION_3.2</t>
-  </si>
-  <si>
-    <t>A surety bond is written at five percent of the total bid and meets section 3.2 at any total. A cashier's check is a fixed amount and is tested against five percent of the total bid as written, tooling included, per addendum 2.</t>
-  </si>
-  <si>
-    <t>When each bid that was opened reached the purchasing office, from bid_receipt_log_itb_2026_17.xlsx</t>
-  </si>
-  <si>
-    <t>NAME_IN_THE_LOG</t>
-  </si>
-  <si>
-    <t>NOTE</t>
-  </si>
-  <si>
-    <t>Brannock Box</t>
-  </si>
-  <si>
-    <t>R-1049</t>
-  </si>
-  <si>
-    <t>16:02</t>
-  </si>
-  <si>
-    <t>Dahlgren Box, St. Cloud</t>
-  </si>
-  <si>
-    <t>R-1055</t>
-  </si>
-  <si>
-    <t>09:33</t>
-  </si>
-  <si>
-    <t>Halvard</t>
-  </si>
-  <si>
-    <t>R-1058</t>
-  </si>
-  <si>
-    <t>09:58</t>
-  </si>
-  <si>
-    <t>Kessel Container, Des Moines</t>
-  </si>
-  <si>
-    <t>R-1040</t>
-  </si>
-  <si>
-    <t>10/02/2026</t>
-  </si>
-  <si>
-    <t>09:47</t>
-  </si>
-  <si>
-    <t>Loken &amp; Vik</t>
-  </si>
-  <si>
-    <t>R-1059</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>Handed over at 10:00, the due time; a bid is due by 10:00 and only a bid received after that time goes back unopened, section 3.1</t>
-  </si>
-  <si>
-    <t>Mesabi Container, Duluth</t>
-  </si>
-  <si>
-    <t>R-1052</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>Otter Tail Corr.</t>
-  </si>
-  <si>
-    <t>R-1051</t>
-  </si>
-  <si>
-    <t>08:52</t>
-  </si>
-  <si>
-    <t>Pemberton, Neenah</t>
-  </si>
-  <si>
-    <t>R-1047</t>
-  </si>
-  <si>
-    <t>11:37</t>
-  </si>
-  <si>
-    <t>The facsimile of October 6 changes the bid and leaves this receipt time, section 3.4</t>
-  </si>
-  <si>
-    <t>A. Delaney</t>
-  </si>
-  <si>
-    <t>R-1050</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>The envelope logged R-1041 on 10/02/2026 was withdrawn and handed back under R-1048; the bid opened is the resubmitted one, section 3.4</t>
-  </si>
-  <si>
-    <t>Thorsgard, Moorhead</t>
-  </si>
-  <si>
-    <t>R-1054</t>
-  </si>
-  <si>
-    <t>09:27</t>
-  </si>
-  <si>
-    <t>W &amp; K Corrugated, La Crosse</t>
-  </si>
-  <si>
-    <t>R-1057</t>
-  </si>
-  <si>
-    <t>09:41</t>
-  </si>
-  <si>
-    <t>Bids received by the due time</t>
-  </si>
-  <si>
-    <t>A twelfth envelope, from Siouxland Container, reached the office at 10:22 on October 6 and went back unopened under section 3.1; it is not a bid in this evaluation. Loken &amp; Vik's envelope was handed over at 10:00, which section 3.1 makes the last minute a bid is due, and it was opened.</t>
-  </si>
-  <si>
-    <t>Quality holds recorded against any bidder in supplier_quality_holds_2026.xlsx, matched to the bidder by name, with clearances since the extract</t>
-  </si>
-  <si>
-    <t>HOLD_NO</t>
-  </si>
-  <si>
-    <t>SUPPLIER_AS_REGISTERED</t>
-  </si>
-  <si>
-    <t>COMMODITY</t>
-  </si>
-  <si>
-    <t>OPENED</t>
-  </si>
-  <si>
-    <t>STATUS_IN_THE_EXTRACT</t>
-  </si>
-  <si>
-    <t>CLEARED</t>
-  </si>
-  <si>
-    <t>SOURCE_OF_THE_CLEARANCE</t>
-  </si>
-  <si>
-    <t>STATUS_AT_RECOMMENDATION</t>
-  </si>
-  <si>
-    <t>QH-25-024</t>
-  </si>
-  <si>
-    <t>Corrugated, RSC 30 x 20 x 16</t>
-  </si>
-  <si>
-    <t>10/08/2025</t>
-  </si>
-  <si>
-    <t>Cleared</t>
-  </si>
-  <si>
-    <t>11/04/2025</t>
-  </si>
-  <si>
-    <t>Register extract of October 7</t>
-  </si>
-  <si>
-    <t>QH-26-009</t>
-  </si>
-  <si>
-    <t>Corrugated, RSC 24 x 18 x 12</t>
-  </si>
-  <si>
-    <t>03/04/2026</t>
-  </si>
-  <si>
-    <t>05/12/2026</t>
-  </si>
-  <si>
-    <t>QH-26-031</t>
-  </si>
-  <si>
-    <t>Loken &amp; Vik Container Corp.</t>
-  </si>
-  <si>
-    <t>Corrugated, RSC 16 x 12 x 8</t>
-  </si>
-  <si>
-    <t>08/27/2026</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>None; verification lot not yet run</t>
-  </si>
-  <si>
-    <t>QH-26-034</t>
-  </si>
-  <si>
-    <t>Pemberton Container, Neenah plant</t>
-  </si>
-  <si>
-    <t>09/10/2026</t>
-  </si>
-  <si>
-    <t>10/15/2026</t>
-  </si>
-  <si>
-    <t>Quality engineering clearance notice of October 15</t>
-  </si>
-  <si>
-    <t>Loken Bros. Pallet &amp; Crate carries an open hold in the register and is a different supplier from Loken &amp; Vik Container. Loken &amp; Vik's letter of October 12 reports its own tests and a verification lot to ship October 27; quality engineering has recorded no clearance of QH-26-031.</t>
-  </si>
-  <si>
-    <t>Freight on the FOB origin bid under 5.4: current item weights, the plant that ships each item, and the schedule rate for that plant's state</t>
-  </si>
-  <si>
-    <t>DRAWING_REV</t>
-  </si>
-  <si>
-    <t>LB_PER_CARTON</t>
-  </si>
-  <si>
-    <t>QUANTITY</t>
-  </si>
-  <si>
-    <t>SHIPPING_LB</t>
-  </si>
-  <si>
-    <t>HUNDREDWEIGHT</t>
-  </si>
-  <si>
-    <t>SHIPPING_PLANT</t>
-  </si>
-  <si>
-    <t>STATE</t>
-  </si>
-  <si>
-    <t>RATE_PER_CWT</t>
-  </si>
-  <si>
-    <t>FREIGHT</t>
-  </si>
-  <si>
-    <t>FOB_ORIGIN_BIDDER</t>
-  </si>
-  <si>
-    <t>ORIGIN_STATE</t>
-  </si>
-  <si>
-    <t>NM-CTN-26-01 rev A</t>
-  </si>
-  <si>
-    <t>NM-CTN-26-02 rev B</t>
-  </si>
-  <si>
-    <t>NM-CTN-26-03 rev A</t>
-  </si>
-  <si>
-    <t>NM-CTN-26-04 rev A</t>
-  </si>
-  <si>
-    <t>NM-CTN-26-05 rev B</t>
-  </si>
-  <si>
-    <t>Omaha</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
     <t>Freight on the Ridgecrest bid</t>
   </si>
   <si>
@@ -1163,7 +1178,7 @@
     <t>Item 2 is weighed at drawing NM-CTN-26-02 revision B and item 5 at NM-CTN-26-05 revision B, the revisions addenda 1 and 2 put in place; revision A of each, at 0.61 lb and 1.40 lb, is superseded.</t>
   </si>
   <si>
-    <t>Ridgecrest's letter ships items 1 to 4 from Cedar Rapids and item 5 from Omaha, so 1,072 hundredweight is rated at the Iowa rate and 396 hundredweight at the Nebraska rate. Mesabi ships all five items from Duluth, so its 1,468 hundredweight is rated at the Minnesota rate.</t>
+    <t>Ridgecrest's office is in Cedar Rapids, and its letter ships items 1 to 4 from its Omaha plant and item 5 from its Cedar Rapids plant, so 1,072 hundredweight is rated at the Nebraska rate and 396 hundredweight at the Iowa rate. Mesabi ships all five items from Duluth, so its 1,468 hundredweight is rated at the Minnesota rate.</t>
   </si>
   <si>
     <t>Responsiveness of each bid under section 3.2, section 4.3, section 4.4, section 5.2 and PP-3.4, decided before price</t>
@@ -1175,7 +1190,7 @@
     <t>ADDENDUM_2_ACKNOWLEDGED</t>
   </si>
   <si>
-    <t>SAMPLES</t>
+    <t>SAMPLES_TO_THE_SPECIFICATION</t>
   </si>
   <si>
     <t>ITEM_3_PRICED_AT_THE_AMENDED_QUANTITY</t>
@@ -1202,6 +1217,9 @@
     <t>REASON</t>
   </si>
   <si>
+    <t>INFORMALITY_WAIVED_5.7</t>
+  </si>
+  <si>
     <t>No, item 5 on 32 ECT</t>
   </si>
   <si>
@@ -1211,12 +1229,21 @@
     <t>No, item 4 as an alternate only</t>
   </si>
   <si>
+    <t>Form signed by a regional sales manager, not an officer, 3.3; waived under 5.7, no effect on price, quantity, quality or delivery</t>
+  </si>
+  <si>
+    <t>No, item 5 sample on 32 ECT</t>
+  </si>
+  <si>
     <t>Responsiveness is decided on the invitation as amended before any price is compared, per PP-3.4.1; a bid set aside is shown on the Evaluation tab for the record and does not compete for award. Responsibility under PP-3.7 is decided afterwards, for the bidder in line, on the Responsibility tab.</t>
   </si>
   <si>
     <t>The description column of each form is read against the items as amended. Kessel's form acknowledges both addenda and describes item 2 as 18 x 12 x 12, the size addendum 1 replaced with 18 x 12 x 10. Mesabi's form carries item 4 on 200 lb test doublewall as an alternate with no line on the 275 lb test board as specified; 4.4 lets an alternate stand only alongside a bid on the item as specified.</t>
   </si>
   <si>
+    <t>Wenzel &amp; Krause's letter says its item 5 sample was run on 32 ECT board; section 3.2 and the addendum 2 answer on samples require a sample made to the specification as amended, so the bid is set aside. Pemberton's form is signed by a regional sales manager where 3.3 asks for an officer. The signature affects none of price, quantity, quality or delivery, so it is waived as an informality under 5.7 with the waiver recorded here.</t>
+  </si>
+  <si>
     <t>Responsibility of the bidder in line for award under PP-3.7.1, checked in the order 5.1 and 5.6 give among the responsive bids</t>
   </si>
   <si>
@@ -1373,49 +1400,49 @@
     <t>Torsten, this is the evaluation of the eleven bids on ITB 2026-17 opened on October 6. The recommendation on the first tab reads from the tabs behind it, and nothing on it is typed in, so a protest can be answered from the workbook.</t>
   </si>
   <si>
-    <t>The recommendation is award of the lot to Pemberton Container of Neenah at a total evaluated price of $99,959.00. Four of the eleven bids are responsive, and one of the four is passed over. The award value is under one hundred thousand dollars, so PP-3.5.3 places the approval with the director of supply chain and not with you. I have set the signature line that way, and you will want to pass the page on.</t>
-  </si>
-  <si>
-    <t>Pemberton is not the lowest evaluated price among the bids left in line. Ridgecrest Packaging evaluates at $99,927.25, which is $31.75 lower. The two bids are within $100 of each other, and 5.6 gives the award to the bid received first. Pemberton's envelope was logged at 11:37 on October 5. Ridgecrest withdrew the envelope it delivered on October 2 and delivered a new one at 08:15 on October 6, and section 3.4 times a resubmitted bid from the resubmission.</t>
-  </si>
-  <si>
-    <t>Loken &amp; Vik Container of Sioux Falls is responsive and has the lowest total evaluated price at $99,230.72, which is $728.28 below Pemberton. Its envelope was handed over at 10:00 on October 6, the minute the bids were due, and section 3.1 makes a bid due by 10:00 and returns only a bid received after that time. It is passed over because hold QH-26-031 against Loken &amp; Vik Container Corp. is open, and PP-3.7.1 makes a bidder on an open hold not responsible until quality engineering has cleared it. Its letter of October 12 reports its own tests and a verification lot to ship October 27. Whether to hold the award until that lot is judged is a matter to weigh, and the evaluation does not decide it. The current carton contract ends at the end of the month.</t>
+    <t>The recommendation is award of the lot to Pemberton Container of Neenah at a total evaluated price of $100,079.00. Three of the eleven bids are responsive, and one of the three is passed over. The award value is over one hundred thousand dollars, so PP-3.5.3 places the approval with you as vice president of operations. It sits $79.00 over the line: tooling of $1,850.00 is added in full under 4.2, and Pemberton's 2 percent discount carries a ten day period, under the twenty day floor in section 5.5, so it is not credited. Either reading taken the other way would put the award under the line and with the director of supply chain, and both would be wrong.</t>
+  </si>
+  <si>
+    <t>Pemberton is not the lowest evaluated price among the bids left in line. Dahlgren Paper Box evaluates at $100,026.33, which is $52.67 lower. The two bids are within $100 of each other, and 5.6 gives the award to the bid received first. Pemberton's envelope was logged at 11:37 on October 5, and Dahlgren's at 09:33 on October 6. Dahlgren's form extends item 2 at $25,900.00, which is not 64,000 cartons at $0.400; the extension is $25,600.00, and 4.1 has the unit price govern. The desk log records a telephone message from Dahlgren at 09:38 on October 6 asking that item 1 be read at 0.594; section 3.4 changes a bid only by a signed writing, so item 1 stands at the $0.597 on the form. Read at 0.594, Dahlgren would have been more than $100 below Pemberton and first in line, and it will ask.</t>
+  </si>
+  <si>
+    <t>Pemberton's form is signed by a regional sales manager where 3.3 asks for an officer of the bidder. That affects none of price, quantity, quality or delivery, so I have waived it as an informality under 5.7 and recorded the waiver on the responsiveness tab, as PP-3.4.4 provides.</t>
+  </si>
+  <si>
+    <t>Loken &amp; Vik Container of Sioux Falls is responsive and has the lowest total evaluated price at $99,230.72, which is $848.28 below Pemberton. Its envelope was handed over at 10:00 on October 6, the minute the bids were due, and section 3.1 makes a bid due by 10:00 and returns only a bid received after that time. It is passed over because hold QH-26-031 is open, and PP-3.7.1 makes a bidder on an open hold not responsible until quality engineering has cleared it. The register carries the hold under the trade name L&amp;V Container Corp., Sioux Falls, at 4700 North Cliff Avenue, the address on the bid form; the open hold on Loken Container Supply of Sioux City, Iowa, is a different company. Quality engineering's e-mail of October 20 reports that the verification lot passed on October 16 and that the quality manager has not signed the clearance, which is what clears a hold. Whether to hold the award until that signature is in the file is a matter to weigh, and the evaluation does not decide it. The current carton contract ends at the end of the month.</t>
   </si>
   <si>
     <t>Pemberton's own hold QH-26-034 was open in the register extract of October 7. Quality engineering cleared it on October 15 after the verification lot passed, so Pemberton is responsible at the date of this recommendation.</t>
   </si>
   <si>
-    <t>Pemberton's price rests on two readings of its bid. Its form extends item 2 at $26,912.00, which is not 64,000 cartons at $0.408; the extension is $26,112.00, and 4.1 has the unit price govern. Its facsimile changing the item 1 unit price from $0.602 to $0.578 was logged at 09:12 on October 6, before the due time, so section 3.4 applies it. Corrected, the extensions sum to $98,109.00, with $1,850.00 of tooling and no freight. Its 2 percent discount has a ten day period, under the twenty day floor in section 5.5, and is not credited.</t>
-  </si>
-  <si>
-    <t>Ridgecrest is the low bid on paper at $93,499.00 because its prices are FOB origin. Section 5.4 adds freight on 1,072 hundredweight from Cedar Rapids at $4.87 and 396 hundredweight from Omaha at $5.35, which is $7,339.24 at the current drawing revisions, each item rated for the plant that ships it. Its 1 percent, twenty day discount is credited at $910.99. Its tooling of $2,400.00 is added in full; the credit its letter offers for an award by October 30 is not an adjustment the invitation names. The tabulation keys its item 4 unit price as 1.557, and the signed form reads 1.575, which is the price evaluated. The desk log records a telephone message from Ridgecrest at 09:35 on October 6 asking that item 3 be read at 0.255; section 3.4 changes a bid only by a signed writing, so item 3 stands at the $0.262 on the form. Read at 0.255, Ridgecrest would have been more than $100 below Pemberton and first in line, and it will ask.</t>
-  </si>
-  <si>
-    <t>Mesabi Container Co. of Duluth is set aside on item 4. Its form prices item 4 on 200 lb test doublewall as an alternate and carries no price for the 275 lb test board as specified, and its letter says the Duluth plant does not run that board. Section 4.4 and the answer in addendum 2 allow an alternate only alongside a bid on the item as specified, and 5.2 makes a bid responsive only where it offers every item as specified. Its prices are FOB origin from one plant, so freight of $4,991.20 on 1,468 hundredweight at the Minnesota rate is shown for the record, and it would have evaluated at $98,963.18, the lowest figure in the file. It will ask, and the answer is that the invitation asked for a price on the item as specified.</t>
-  </si>
-  <si>
-    <t>Brannock Box Company is the lowest delivered bid as written at $100,058.00 and is set aside. Its form acknowledges addendum 1 only, prices item 3 at the superseded 36,000 cartons, and describes item 5 on 32 ECT board. Its figures are shown for the record and do not compete.</t>
-  </si>
-  <si>
-    <t>Dahlgren Paper Box is set aside on its bid security. Its cashier's check is $4,904.75, and five percent of its total bid as written of $100,045.00 is $5,002.25, so the check is $97.50 short. Addendum 2 treats a bid with less than five percent as a bid without security. It would have evaluated at $99,064.05.</t>
+    <t>Pemberton's price rests on two readings of its bid. Its form extends item 2 at $26,912.00, which is not 64,000 cartons at $0.408; the extension is $26,112.00. Its facsimile changing the item 1 unit price from $0.602 to $0.578 was logged at 09:12 on October 6, before the due time, so section 3.4 applies it. Corrected, the extensions sum to $98,229.00, with $1,850.00 of tooling and no freight.</t>
+  </si>
+  <si>
+    <t>Ridgecrest is the low bid on paper at $93,499.00 and is set aside on its bid security. Its cashier's check is $4,554.95, five percent of its extensions, and five percent of its total bid as written of $93,499.00 is $4,674.95, so the check is $120.00 short. Addendum 2 treats a bid with less than five percent as a bid without security. For the record, its prices are FOB origin: its office is in Cedar Rapids, its letter ships items 1 to 4 from its Omaha plant and item 5 from its Cedar Rapids plant, and section 5.4 rates 1,072 hundredweight at the Nebraska rate of $5.35 and 396 hundredweight at the Iowa rate of $4.87, which is $7,663.72. With its discount credited at $910.99 and tooling of $2,400.00 added in full, it would have evaluated at $100,251.73. The tabulation keys its item 4 unit price as 1.557, and the signed form reads 1.575.</t>
+  </si>
+  <si>
+    <t>Mesabi Container Co. of Duluth is set aside on item 4. Its form prices item 4 on 200 lb test doublewall as an alternate and carries no price for the 275 lb test board as specified, and its letter says the Duluth plant does not run that board. Section 4.4 and the answer in addendum 2 allow an alternate only alongside a bid on the item as specified, and 5.2 makes a bid responsive only where it offers every item as specified. Its prices are FOB origin from one plant, so freight of $4,991.20 on 1,468 hundredweight at the Minnesota rate is shown for the record, and it would have evaluated at $98,963.18, the lowest figure in the file.</t>
+  </si>
+  <si>
+    <t>Brannock Box Company is set aside. Its form acknowledges addendum 1 only, prices item 3 at the superseded 36,000 cartons, and describes item 5 on 32 ECT board. Its figures are shown for the record and do not compete.</t>
   </si>
   <si>
     <t>Kessel Container Corp. is set aside under PP-3.4.5. Its form acknowledges both addenda and describes item 2 as 18 x 12 x 12, the size that addendum 1 replaced with 18 x 12 x 10, so it is a bid on a superseded specification. It would have evaluated at $98,895.24.</t>
   </si>
   <si>
-    <t>Halvard Corrugated and Thorsgard Box &amp; Label are set aside for exceptions to the price hold, a material term. Halvard's letter holds prices for six months and then adjusts them quarterly to a linerboard index. Thorsgard's form marks the twelve months Yes, and its letter holds prices firm through September 30, 2027, which is short of twelve months from any award made after the opening. They would have evaluated at $98,627.84 and $98,883.64.</t>
-  </si>
-  <si>
-    <t>Otter Tail Corrugated is set aside for conditioning its prices on full truckload releases, with a $185 stop charge on smaller releases. Addendum 2 calls that an exception to the quantity term. Its letter of October 8 withdrawing the stop charge reached the office after the due time, and PP-3.4.4 does not let the buyer negotiate an exception away before award. It would have evaluated at $99,567.00.</t>
-  </si>
-  <si>
-    <t>Wenzel &amp; Krause Corrugated is responsive at $103,793.46 on its sealed prices. Its facsimile lowering all five unit prices is dated October 5 and was logged at 10:07 on October 6, after the due time, so section 3.4 does not consider it. At the changed prices it would have evaluated at $98,535.76, and it will ask.</t>
+    <t>Halvard Corrugated and Thorsgard Box &amp; Label are set aside for exceptions to the price hold, a material term. Halvard's letter holds prices for twelve months and then adds a raw material surcharge whenever a linerboard index rises more than 6 percent, which conditions the prices on an index, and section 4.3 makes that an exception. Thorsgard's form marks the twelve months Yes, and its letter holds prices firm through September 30, 2027, which is short of twelve months from any award made after the opening. They would have evaluated at $98,627.84 and $98,883.64.</t>
+  </si>
+  <si>
+    <t>Otter Tail Corrugated is set aside for a delivery-efficiency fee of $185 on any release under 20 pallets. Section 1 places releases monthly in pallet multiples at the quantities the schedule requires, quantity is a material term under 5.2, and a fee that turns on the release quantity changes the price of those releases. Its letter of October 8 withdrawing the fee reached the office after the due time, and PP-3.4.4 does not let the buyer negotiate an exception away before award. It would have evaluated at $99,567.00.</t>
+  </si>
+  <si>
+    <t>Wenzel &amp; Krause Corrugated is set aside on its item 5 sample. Its letter says the sample was run on 32 ECT board, and section 3.2 with the addendum 2 answer on samples requires one made to the specification as amended, which is 44 ECT. Its facsimile lowering all five unit prices is dated October 5 and was logged at 10:07 on October 6, after the due time, so section 3.4 would not have considered it in any case. It would have evaluated at $103,793.46 on its sealed prices.</t>
   </si>
   <si>
     <t>Two other things to weigh that the evaluation does not decide. First, Pemberton offered an alternate for item 4 at 200 lb test doublewall for $1.512 a carton against $1.704 as specified. Section 4.4 keeps it out of the evaluation, and it can be taken up after award if engineering accepts the lighter board. Second, the award rests on the recomputation of one extension, and Pemberton has not been asked to confirm the unit price. That confirmation belongs in the file before the notice goes out.</t>
   </si>
   <si>
-    <t>For the bidder that was low on paper: tell Ridgecrest that its prices were FOB origin, that freight under section 5.4 and its discount credit put its total evaluated price at $99,927.25, that a price change by telephone is not a modification under section 3.4, and that 5.6 gave the award to a bid within $100 that was received first. Tell Mesabi that the invitation asked for a price on item 4 as specified. Tell Brannock that its bid did not acknowledge addendum 2. Tell Loken &amp; Vik that its bid was responsive and lowest in evaluated price and was passed over under PP-3.7.1 for the open hold. Under PP-3.6.1 the unsuccessful bidders are notified in writing within five business days of award, and a debriefing is limited to the bidder's own bid.</t>
+    <t>For the bidder that was low on paper: tell Ridgecrest that its cashier's check was five percent of its extensions and not of its total bid as written, which addendum 2 treats as a bid without security, and that its freight under section 5.4 would in any case have placed it above the award. Tell Dahlgren that a price change by telephone is not a modification under section 3.4 and that 5.6 gave the award to a bid within $100 that was received first. Tell Mesabi that the invitation asked for a price on item 4 as specified. Tell Loken &amp; Vik that its bid was responsive and lowest in evaluated price and was passed over under PP-3.7.1 for the open hold. Under PP-3.6.1 the unsuccessful bidders are notified in writing within five business days of award, and a debriefing is limited to the bidder's own bid.</t>
   </si>
 </sst>
 </file>
@@ -1904,7 +1931,7 @@
       </c>
       <c r="J5" s="4" t="str">
         <f>Terms!B12&amp;", "&amp;Terms!C12</f>
-        <v>Cedar Rapids, IA</v>
+        <v>Omaha, NE</v>
       </c>
       <c r="K5" s="4" t="str">
         <f>Terms!B13&amp;", "&amp;Terms!C13</f>
@@ -1928,7 +1955,7 @@
       </c>
       <c r="C6" s="4" t="str">
         <f>Responsiveness!K5</f>
-        <v>Non-responsive</v>
+        <v>Responsive</v>
       </c>
       <c r="D6" s="4" t="str">
         <f>Responsiveness!K6</f>
@@ -1956,7 +1983,7 @@
       </c>
       <c r="J6" s="4" t="str">
         <f>Responsiveness!K12</f>
-        <v>Responsive</v>
+        <v>Non-responsive</v>
       </c>
       <c r="K6" s="4" t="str">
         <f>Responsiveness!K13</f>
@@ -1964,7 +1991,7 @@
       </c>
       <c r="L6" s="4" t="str">
         <f>Responsiveness!K14</f>
-        <v>Responsive</v>
+        <v>Non-responsive</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>6</v>
@@ -1980,7 +2007,7 @@
       </c>
       <c r="C7" s="4" t="str">
         <f>Responsiveness!L5</f>
-        <v>Bid security under five percent of the total bid as written, section 3.2 and addendum 2.</v>
+        <v/>
       </c>
       <c r="D7" s="4" t="str">
         <f>Responsiveness!L6</f>
@@ -2008,7 +2035,7 @@
       </c>
       <c r="J7" s="4" t="str">
         <f>Responsiveness!L12</f>
-        <v/>
+        <v>Bid security under five percent of the total bid as written, section 3.2 and addendum 2.</v>
       </c>
       <c r="K7" s="4" t="str">
         <f>Responsiveness!L13</f>
@@ -2016,7 +2043,7 @@
       </c>
       <c r="L7" s="4" t="str">
         <f>Responsiveness!L14</f>
-        <v/>
+        <v>Sample not made to the specification as amended, item 5 sample on 32 ECT, section 3.2.</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>6</v>
@@ -2032,7 +2059,7 @@
       </c>
       <c r="C8" s="4" t="str">
         <f>IFERROR(INDEX(Responsibility!$G$4:$G$14,MATCH(C4,Responsibility!$B$4:$B$14,0)),"Set aside before price")</f>
-        <v>Set aside before price</v>
+        <v>Not decided, PP-3.7.1</v>
       </c>
       <c r="D8" s="4" t="str">
         <f>IFERROR(INDEX(Responsibility!$G$4:$G$14,MATCH(D4,Responsibility!$B$4:$B$14,0)),"Set aside before price")</f>
@@ -2060,7 +2087,7 @@
       </c>
       <c r="J8" s="4" t="str">
         <f>IFERROR(INDEX(Responsibility!$G$4:$G$14,MATCH(J4,Responsibility!$B$4:$B$14,0)),"Set aside before price")</f>
-        <v>Not decided, PP-3.7.1</v>
+        <v>Set aside before price</v>
       </c>
       <c r="K8" s="4" t="str">
         <f>IFERROR(INDEX(Responsibility!$G$4:$G$14,MATCH(K4,Responsibility!$B$4:$B$14,0)),"Set aside before price")</f>
@@ -2068,7 +2095,7 @@
       </c>
       <c r="L8" s="4" t="str">
         <f>IFERROR(INDEX(Responsibility!$G$4:$G$14,MATCH(L4,Responsibility!$B$4:$B$14,0)),"Set aside before price")</f>
-        <v>Not decided, PP-3.7.1</v>
+        <v>Set aside before price</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>9</v>
@@ -2084,7 +2111,7 @@
       </c>
       <c r="C9" s="5">
         <f>Evaluation!C22</f>
-        <v>100045</v>
+        <v>101317</v>
       </c>
       <c r="D9" s="5">
         <f>Evaluation!D22</f>
@@ -2108,7 +2135,7 @@
       </c>
       <c r="I9" s="5">
         <f>Evaluation!I22</f>
-        <v>101839</v>
+        <v>101959</v>
       </c>
       <c r="J9" s="5">
         <f>Evaluation!J22</f>
@@ -2136,7 +2163,7 @@
       </c>
       <c r="C10" s="5">
         <f>Evaluation!C14</f>
-        <v>98095</v>
+        <v>99067</v>
       </c>
       <c r="D10" s="5">
         <f>Evaluation!D14</f>
@@ -2160,7 +2187,7 @@
       </c>
       <c r="I10" s="5">
         <f>Evaluation!I14</f>
-        <v>98109</v>
+        <v>98229</v>
       </c>
       <c r="J10" s="5">
         <f>Evaluation!J14</f>
@@ -2268,7 +2295,7 @@
       </c>
       <c r="J12" s="5">
         <f>Evaluation!J17</f>
-        <v>7339.24</v>
+        <v>7663.72</v>
       </c>
       <c r="K12" s="5">
         <f>Evaluation!K17</f>
@@ -2292,7 +2319,7 @@
       </c>
       <c r="C13" s="5">
         <f>Evaluation!C20</f>
-        <v>980.95</v>
+        <v>990.67</v>
       </c>
       <c r="D13" s="5">
         <f>Evaluation!D20</f>
@@ -2344,7 +2371,7 @@
       </c>
       <c r="C14" s="5">
         <f>Evaluation!C21</f>
-        <v>99064.05</v>
+        <v>100026.33</v>
       </c>
       <c r="D14" s="5">
         <f>Evaluation!D21</f>
@@ -2368,11 +2395,11 @@
       </c>
       <c r="I14" s="5">
         <f>Evaluation!I21</f>
-        <v>99959</v>
+        <v>100079</v>
       </c>
       <c r="J14" s="5">
         <f>Evaluation!J21</f>
-        <v>99927.25</v>
+        <v>100251.73</v>
       </c>
       <c r="K14" s="5">
         <f>Evaluation!K21</f>
@@ -2394,9 +2421,9 @@
         <f>Evaluation!B25</f>
         <v>Set aside</v>
       </c>
-      <c r="C15" s="4" t="str">
+      <c r="C15" s="4">
         <f>Evaluation!C25</f>
-        <v>Set aside</v>
+        <v>3</v>
       </c>
       <c r="D15" s="4" t="str">
         <f>Evaluation!D25</f>
@@ -2422,17 +2449,17 @@
         <f>Evaluation!I25</f>
         <v>2</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="4" t="str">
         <f>Evaluation!J25</f>
-        <v>3</v>
+        <v>Set aside</v>
       </c>
       <c r="K15" s="4" t="str">
         <f>Evaluation!K25</f>
         <v>Set aside</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="4" t="str">
         <f>Evaluation!L25</f>
-        <v>4</v>
+        <v>Set aside</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>13</v>
@@ -2513,7 +2540,7 @@
       </c>
       <c r="B20" s="7">
         <f>Responsibility!B19</f>
-        <v>99959</v>
+        <v>100079</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>9</v>
@@ -2525,7 +2552,7 @@
       </c>
       <c r="B21" s="2" t="str">
         <f>Evaluation!B32</f>
-        <v>Director of supply chain</v>
+        <v>Vice president of operations</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>13</v>
@@ -2537,7 +2564,7 @@
       </c>
       <c r="B22" s="2" t="str">
         <f>Responsibility!B20</f>
-        <v>Ridgecrest Packaging</v>
+        <v>Dahlgren Paper Box Co.</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>9</v>
@@ -2549,7 +2576,7 @@
       </c>
       <c r="B23" s="7">
         <f>Responsibility!B21</f>
-        <v>99927.25</v>
+        <v>100026.33</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>9</v>
@@ -2561,7 +2588,7 @@
       </c>
       <c r="B24" s="7">
         <f>Responsibility!B22</f>
-        <v>31.75</v>
+        <v>52.67</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>9</v>
@@ -2597,7 +2624,7 @@
       </c>
       <c r="B27" s="2" t="str">
         <f>Responsibility!B25</f>
-        <v>10/06/2026 08:15</v>
+        <v>10/06/2026 09:33</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>20</v>
@@ -2609,7 +2636,7 @@
       </c>
       <c r="B28" s="2">
         <f>Responsiveness!B16</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>6</v>
@@ -2621,7 +2648,7 @@
       </c>
       <c r="B29" s="2">
         <f>Responsiveness!B17</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>6</v>
@@ -2657,7 +2684,7 @@
       </c>
       <c r="B32" s="7">
         <f>Responsibility!B28</f>
-        <v>728.28</v>
+        <v>848.28</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>9</v>
@@ -2681,7 +2708,7 @@
       </c>
       <c r="B34" s="2">
         <f>Extensions!H59</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>38</v>
@@ -2735,42 +2762,54 @@
         <v>42</v>
       </c>
     </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="2" t="str">
+        <f>Responsiveness!M11</f>
+        <v>Form signed by a regional sales manager, not an officer, 3.3; waived under 5.7, no effect on price, quantity, quality or delivery</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2798,48 +2837,48 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -2847,7 +2886,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C4" s="8">
         <v>0.9</v>
@@ -2868,21 +2907,21 @@
         <v>167</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="I4" s="8">
         <f t="shared" ref="I4:I13" si="1">INDEX($N$4:$N$10,MATCH(H4,$M$4:$M$10,0))</f>
-        <v>4.87</v>
+        <v>5.35</v>
       </c>
       <c r="J4" s="7">
         <f t="shared" ref="J4:J13" si="2">ROUND(F4*I4,2)</f>
-        <v>1972.35</v>
+        <v>2166.75</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>166</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N4" s="8">
         <v>3.4</v>
@@ -2893,7 +2932,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C5" s="8">
         <v>0.55</v>
@@ -2914,15 +2953,15 @@
         <v>167</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="I5" s="8">
         <f t="shared" si="1"/>
-        <v>4.87</v>
+        <v>5.35</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" si="2"/>
-        <v>1714.24</v>
+        <v>1883.2</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>166</v>
@@ -2939,7 +2978,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C6" s="8">
         <v>0.3</v>
@@ -2960,15 +2999,15 @@
         <v>167</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="I6" s="8">
         <f t="shared" si="1"/>
-        <v>4.87</v>
+        <v>5.35</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" si="2"/>
-        <v>394.47</v>
+        <v>433.35</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>166</v>
@@ -2985,7 +3024,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C7" s="8">
         <v>2.6</v>
@@ -3006,21 +3045,21 @@
         <v>167</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="I7" s="8">
         <f t="shared" si="1"/>
-        <v>4.87</v>
+        <v>5.35</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="2"/>
-        <v>1139.58</v>
+        <v>1251.9</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>166</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N7" s="8">
         <v>5.6</v>
@@ -3031,7 +3070,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C8" s="8">
         <v>1.65</v>
@@ -3049,18 +3088,18 @@
         <v>396</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>365</v>
+        <v>144</v>
       </c>
       <c r="I8" s="8">
         <f t="shared" si="1"/>
-        <v>5.35</v>
+        <v>4.87</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" si="2"/>
-        <v>2118.6</v>
+        <v>1928.52</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>166</v>
@@ -3077,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C9" s="8">
         <v>0.9</v>
@@ -3098,7 +3137,7 @@
         <v>154</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I9" s="8">
         <f t="shared" si="1"/>
@@ -3123,7 +3162,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C10" s="8">
         <v>0.55</v>
@@ -3144,7 +3183,7 @@
         <v>154</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I10" s="8">
         <f t="shared" si="1"/>
@@ -3158,7 +3197,7 @@
         <v>153</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>365</v>
+        <v>168</v>
       </c>
       <c r="N10" s="8">
         <v>5.35</v>
@@ -3169,7 +3208,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C11" s="8">
         <v>0.3</v>
@@ -3190,7 +3229,7 @@
         <v>154</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I11" s="8">
         <f t="shared" si="1"/>
@@ -3209,7 +3248,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C12" s="8">
         <v>2.6</v>
@@ -3230,7 +3269,7 @@
         <v>154</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I12" s="8">
         <f t="shared" si="1"/>
@@ -3249,7 +3288,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C13" s="8">
         <v>1.65</v>
@@ -3270,7 +3309,7 @@
         <v>154</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I13" s="8">
         <f t="shared" si="1"/>
@@ -3286,16 +3325,16 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="J14" s="11">
         <f>SUMIFS(J4:J13,K4:K13,"Ridgecrest Packaging")</f>
-        <v>7339.24</v>
+        <v>7663.72</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J15" s="11">
         <f>SUMIFS(J4:J13,K4:K13,"Mesabi Container Co.")</f>
@@ -3304,25 +3343,25 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F16" s="7">
         <f>SUMIFS(F4:F13,H4:H13,"IA")</f>
-        <v>1072</v>
+        <v>396</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F17" s="7">
         <f>SUMIFS(F4:F13,H4:H13,"NE")</f>
-        <v>396</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F18" s="7">
         <f>SUMIFS(F4:F13,H4:H13,"MN")</f>
@@ -3331,17 +3370,17 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3351,13 +3390,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
@@ -3365,52 +3404,56 @@
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="90" customWidth="1"/>
+    <col min="13" max="13" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>390</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="str">
         <f>Terms!A4</f>
         <v>Brannock Box Company</v>
@@ -3423,19 +3466,18 @@
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H4)),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="D4" s="2" t="str">
-        <f>IF(Terms!I4="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D4" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E4" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!D7,2)=ROUND('Bids as Written'!C7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>No, superseded 36,000</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H4" s="2" t="str">
         <f>'Bid Conditions'!D4</f>
@@ -3450,40 +3492,42 @@
         <v>No</v>
       </c>
       <c r="K4" s="2" t="str">
-        <f t="shared" ref="K4:K14" si="0">IF(AND(B4="Yes",C4="Yes",D4="Yes",LEFT(E4,3)="Yes",F4="Yes",G4="Yes",H4="No"),"Responsive","Non-responsive")</f>
+        <f t="shared" ref="K4:K14" si="0">IF(AND(B4="Yes",C4="Yes",LEFT(D4,3)="Yes",LEFT(E4,3)="Yes",F4="Yes",G4="Yes",H4="No"),"Responsive","Non-responsive")</f>
         <v>Non-responsive</v>
       </c>
       <c r="L4" s="4" t="str">
-        <f>TRIM(IF(B4="No","No bid security, section 3.2. ","")&amp;IF(B4="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C4="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D4="No","Samples not received, section 3.2. ","")&amp;IF(AND(C4="Yes",LEFT(E4,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C4="Yes",LEFT(F4,2)="No"),"Bid on a superseded specification, "&amp;MID(F4,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G4,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H4="Yes","Exception to a material term, "&amp;'Bid Conditions'!C4&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <f>TRIM(IF(B4="No","No bid security, section 3.2. ","")&amp;IF(B4="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C4="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D4,2)="No","Sample not made to the specification as amended, "&amp;MID(D4,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C4="Yes",LEFT(E4,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C4="Yes",LEFT(F4,2)="No"),"Bid on a superseded specification, "&amp;MID(F4,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G4,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H4="Yes","Exception to a material term, "&amp;'Bid Conditions'!C4&amp;", section 5.2 and PP-3.4.4. ",""))</f>
         <v>Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5.</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M4" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="str">
         <f>Terms!A5</f>
         <v>Dahlgren Paper Box Co.</v>
       </c>
       <c r="B5" s="2" t="str">
         <f>'Bid Security'!G5</f>
-        <v>No, short</v>
+        <v>Yes</v>
       </c>
       <c r="C5" s="2" t="str">
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H5)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="D5" s="2" t="str">
-        <f>IF(Terms!I5="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D5" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E5" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!F7,2)=ROUND('Bids as Written'!E7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H5" s="2" t="str">
         <f>'Bid Conditions'!D5</f>
@@ -3491,7 +3535,7 @@
       </c>
       <c r="I5" s="4" t="str">
         <f>'Bid Conditions'!B5</f>
-        <v>None; releases taken in any pallet quantity</v>
+        <v>None; releases taken in any pallet quantity; the form extends item 2 at 25,900.00 against 25,600.00 at the unit price</v>
       </c>
       <c r="J5" s="2" t="str">
         <f>IF(ISNUMBER(SEARCH("lternate",'Bid Conditions'!B5)),"Yes, not evaluated","No")</f>
@@ -3499,14 +3543,17 @@
       </c>
       <c r="K5" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Non-responsive</v>
+        <v>Responsive</v>
       </c>
       <c r="L5" s="4" t="str">
-        <f>TRIM(IF(B5="No","No bid security, section 3.2. ","")&amp;IF(B5="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C5="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D5="No","Samples not received, section 3.2. ","")&amp;IF(AND(C5="Yes",LEFT(E5,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C5="Yes",LEFT(F5,2)="No"),"Bid on a superseded specification, "&amp;MID(F5,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G5,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H5="Yes","Exception to a material term, "&amp;'Bid Conditions'!C5&amp;", section 5.2 and PP-3.4.4. ",""))</f>
-        <v>Bid security under five percent of the total bid as written, section 3.2 and addendum 2.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <f>TRIM(IF(B5="No","No bid security, section 3.2. ","")&amp;IF(B5="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C5="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D5,2)="No","Sample not made to the specification as amended, "&amp;MID(D5,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C5="Yes",LEFT(E5,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C5="Yes",LEFT(F5,2)="No"),"Bid on a superseded specification, "&amp;MID(F5,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G5,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H5="Yes","Exception to a material term, "&amp;'Bid Conditions'!C5&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <v/>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="str">
         <f>Terms!A6</f>
         <v>Halvard Corrugated</v>
@@ -3519,19 +3566,18 @@
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H6)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="D6" s="2" t="str">
-        <f>IF(Terms!I6="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D6" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E6" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!H7,2)=ROUND('Bids as Written'!G7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H6" s="2" t="str">
         <f>'Bid Conditions'!D6</f>
@@ -3539,7 +3585,7 @@
       </c>
       <c r="I6" s="4" t="str">
         <f>'Bid Conditions'!B6</f>
-        <v>Prices held firm for six months from award, then adjusted quarterly to the Pulp and Paper Week 42 lb kraft linerboard index</v>
+        <v>Prices firm for twelve months, with a raw material surcharge on the unit prices should the Pulp and Paper Week 42 lb kraft linerboard index rise more than 6 percent from award; the form boxes read Yes and None</v>
       </c>
       <c r="J6" s="2" t="str">
         <f>IF(ISNUMBER(SEARCH("lternate",'Bid Conditions'!B6)),"Yes, not evaluated","No")</f>
@@ -3550,11 +3596,14 @@
         <v>Non-responsive</v>
       </c>
       <c r="L6" s="4" t="str">
-        <f>TRIM(IF(B6="No","No bid security, section 3.2. ","")&amp;IF(B6="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C6="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D6="No","Samples not received, section 3.2. ","")&amp;IF(AND(C6="Yes",LEFT(E6,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C6="Yes",LEFT(F6,2)="No"),"Bid on a superseded specification, "&amp;MID(F6,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G6,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H6="Yes","Exception to a material term, "&amp;'Bid Conditions'!C6&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <f>TRIM(IF(B6="No","No bid security, section 3.2. ","")&amp;IF(B6="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C6="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D6,2)="No","Sample not made to the specification as amended, "&amp;MID(D6,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C6="Yes",LEFT(E6,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C6="Yes",LEFT(F6,2)="No"),"Bid on a superseded specification, "&amp;MID(F6,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G6,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H6="Yes","Exception to a material term, "&amp;'Bid Conditions'!C6&amp;", section 5.2 and PP-3.4.4. ",""))</f>
         <v>Exception to a material term, Price hold, section 4.3, section 5.2 and PP-3.4.4.</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M6" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="str">
         <f>Terms!A7</f>
         <v>Kessel Container Corp.</v>
@@ -3567,19 +3616,18 @@
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H7)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="D7" s="2" t="str">
-        <f>IF(Terms!I7="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D7" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E7" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!J7,2)=ROUND('Bids as Written'!I7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H7" s="2" t="str">
         <f>'Bid Conditions'!D7</f>
@@ -3598,11 +3646,14 @@
         <v>Non-responsive</v>
       </c>
       <c r="L7" s="4" t="str">
-        <f>TRIM(IF(B7="No","No bid security, section 3.2. ","")&amp;IF(B7="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C7="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D7="No","Samples not received, section 3.2. ","")&amp;IF(AND(C7="Yes",LEFT(E7,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C7="Yes",LEFT(F7,2)="No"),"Bid on a superseded specification, "&amp;MID(F7,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G7,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H7="Yes","Exception to a material term, "&amp;'Bid Conditions'!C7&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <f>TRIM(IF(B7="No","No bid security, section 3.2. ","")&amp;IF(B7="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C7="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D7,2)="No","Sample not made to the specification as amended, "&amp;MID(D7,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C7="Yes",LEFT(E7,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C7="Yes",LEFT(F7,2)="No"),"Bid on a superseded specification, "&amp;MID(F7,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G7,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H7="Yes","Exception to a material term, "&amp;'Bid Conditions'!C7&amp;", section 5.2 and PP-3.4.4. ",""))</f>
         <v>Bid on a superseded specification, item 2 as 18 x 12 x 12, PP-3.4.5.</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M7" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="str">
         <f>Terms!A8</f>
         <v>Loken &amp; Vik Container</v>
@@ -3615,19 +3666,18 @@
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H8)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="D8" s="2" t="str">
-        <f>IF(Terms!I8="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D8" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E8" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!L7,2)=ROUND('Bids as Written'!K7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H8" s="2" t="str">
         <f>'Bid Conditions'!D8</f>
@@ -3646,11 +3696,14 @@
         <v>Responsive</v>
       </c>
       <c r="L8" s="4" t="str">
-        <f>TRIM(IF(B8="No","No bid security, section 3.2. ","")&amp;IF(B8="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C8="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D8="No","Samples not received, section 3.2. ","")&amp;IF(AND(C8="Yes",LEFT(E8,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C8="Yes",LEFT(F8,2)="No"),"Bid on a superseded specification, "&amp;MID(F8,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G8,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H8="Yes","Exception to a material term, "&amp;'Bid Conditions'!C8&amp;", section 5.2 and PP-3.4.4. ",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <f>TRIM(IF(B8="No","No bid security, section 3.2. ","")&amp;IF(B8="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C8="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D8,2)="No","Sample not made to the specification as amended, "&amp;MID(D8,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C8="Yes",LEFT(E8,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C8="Yes",LEFT(F8,2)="No"),"Bid on a superseded specification, "&amp;MID(F8,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G8,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H8="Yes","Exception to a material term, "&amp;'Bid Conditions'!C8&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <v/>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="str">
         <f>Terms!A9</f>
         <v>Mesabi Container Co.</v>
@@ -3663,19 +3716,18 @@
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H9)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="D9" s="2" t="str">
-        <f>IF(Terms!I9="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D9" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E9" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!N7,2)=ROUND('Bids as Written'!M7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H9" s="2" t="str">
         <f>'Bid Conditions'!D9</f>
@@ -3694,11 +3746,14 @@
         <v>Non-responsive</v>
       </c>
       <c r="L9" s="4" t="str">
-        <f>TRIM(IF(B9="No","No bid security, section 3.2. ","")&amp;IF(B9="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C9="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D9="No","Samples not received, section 3.2. ","")&amp;IF(AND(C9="Yes",LEFT(E9,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C9="Yes",LEFT(F9,2)="No"),"Bid on a superseded specification, "&amp;MID(F9,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G9,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H9="Yes","Exception to a material term, "&amp;'Bid Conditions'!C9&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <f>TRIM(IF(B9="No","No bid security, section 3.2. ","")&amp;IF(B9="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C9="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D9,2)="No","Sample not made to the specification as amended, "&amp;MID(D9,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C9="Yes",LEFT(E9,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C9="Yes",LEFT(F9,2)="No"),"Bid on a superseded specification, "&amp;MID(F9,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G9,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H9="Yes","Exception to a material term, "&amp;'Bid Conditions'!C9&amp;", section 5.2 and PP-3.4.4. ",""))</f>
         <v>Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4.</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M9" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="str">
         <f>Terms!A10</f>
         <v>Otter Tail Corrugated</v>
@@ -3711,19 +3766,18 @@
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H10)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="D10" s="2" t="str">
-        <f>IF(Terms!I10="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D10" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E10" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!P7,2)=ROUND('Bids as Written'!O7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H10" s="2" t="str">
         <f>'Bid Conditions'!D10</f>
@@ -3731,7 +3785,7 @@
       </c>
       <c r="I10" s="4" t="str">
         <f>'Bid Conditions'!B10</f>
-        <v>Pricing assumes releases in full truckload quantities of 26 pallets; a release below a full truckload carries a $185 stop charge; the form box reads None</v>
+        <v>Pricing is for releases of 20 pallets or more; a delivery-efficiency fee of $185 applies to any release under 20 pallets; the form box reads None</v>
       </c>
       <c r="J10" s="2" t="str">
         <f>IF(ISNUMBER(SEARCH("lternate",'Bid Conditions'!B10)),"Yes, not evaluated","No")</f>
@@ -3742,11 +3796,14 @@
         <v>Non-responsive</v>
       </c>
       <c r="L10" s="4" t="str">
-        <f>TRIM(IF(B10="No","No bid security, section 3.2. ","")&amp;IF(B10="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C10="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D10="No","Samples not received, section 3.2. ","")&amp;IF(AND(C10="Yes",LEFT(E10,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C10="Yes",LEFT(F10,2)="No"),"Bid on a superseded specification, "&amp;MID(F10,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G10,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H10="Yes","Exception to a material term, "&amp;'Bid Conditions'!C10&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <f>TRIM(IF(B10="No","No bid security, section 3.2. ","")&amp;IF(B10="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C10="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D10,2)="No","Sample not made to the specification as amended, "&amp;MID(D10,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C10="Yes",LEFT(E10,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C10="Yes",LEFT(F10,2)="No"),"Bid on a superseded specification, "&amp;MID(F10,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G10,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H10="Yes","Exception to a material term, "&amp;'Bid Conditions'!C10&amp;", section 5.2 and PP-3.4.4. ",""))</f>
         <v>Exception to a material term, Quantity, releases in pallet multiples, section 1, section 5.2 and PP-3.4.4.</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M10" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="str">
         <f>Terms!A11</f>
         <v>Pemberton Container</v>
@@ -3759,19 +3816,18 @@
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H11)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="D11" s="2" t="str">
-        <f>IF(Terms!I11="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D11" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E11" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!R7,2)=ROUND('Bids as Written'!Q7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H11" s="2" t="str">
         <f>'Bid Conditions'!D11</f>
@@ -3779,7 +3835,7 @@
       </c>
       <c r="I11" s="4" t="str">
         <f>'Bid Conditions'!B11</f>
-        <v>Alternate for item 4 at 200 lb test doublewall, $1.512 per carton, beside the bid on the item as specified</v>
+        <v>Alternate for item 4 at 200 lb test doublewall, $1.512 per carton, beside the bid on the item as specified; the form is signed by a regional sales manager where 3.3 asks for an officer</v>
       </c>
       <c r="J11" s="2" t="str">
         <f>IF(ISNUMBER(SEARCH("lternate",'Bid Conditions'!B11)),"Yes, not evaluated","No")</f>
@@ -3790,36 +3846,38 @@
         <v>Responsive</v>
       </c>
       <c r="L11" s="4" t="str">
-        <f>TRIM(IF(B11="No","No bid security, section 3.2. ","")&amp;IF(B11="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C11="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D11="No","Samples not received, section 3.2. ","")&amp;IF(AND(C11="Yes",LEFT(E11,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C11="Yes",LEFT(F11,2)="No"),"Bid on a superseded specification, "&amp;MID(F11,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G11,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H11="Yes","Exception to a material term, "&amp;'Bid Conditions'!C11&amp;", section 5.2 and PP-3.4.4. ",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <f>TRIM(IF(B11="No","No bid security, section 3.2. ","")&amp;IF(B11="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C11="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D11,2)="No","Sample not made to the specification as amended, "&amp;MID(D11,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C11="Yes",LEFT(E11,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C11="Yes",LEFT(F11,2)="No"),"Bid on a superseded specification, "&amp;MID(F11,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G11,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H11="Yes","Exception to a material term, "&amp;'Bid Conditions'!C11&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <v/>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="str">
         <f>Terms!A12</f>
         <v>Ridgecrest Packaging</v>
       </c>
       <c r="B12" s="2" t="str">
         <f>'Bid Security'!G12</f>
-        <v>Yes</v>
+        <v>No, short</v>
       </c>
       <c r="C12" s="2" t="str">
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H12)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="D12" s="2" t="str">
-        <f>IF(Terms!I12="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D12" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E12" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!T7,2)=ROUND('Bids as Written'!S7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H12" s="2" t="str">
         <f>'Bid Conditions'!D12</f>
@@ -3827,7 +3885,7 @@
       </c>
       <c r="I12" s="4" t="str">
         <f>'Bid Conditions'!B12</f>
-        <v>None; FOB origin, items 1 to 4 shipped from Cedar Rapids and item 5 from Omaha; tooling credited back if the award arrives by October 30</v>
+        <v>None; FOB origin, the office in Cedar Rapids, items 1 to 4 shipped from the Omaha plant and item 5 from the Cedar Rapids plant; tooling credited back if the award arrives by October 30; a cashier's check of $4,554.95</v>
       </c>
       <c r="J12" s="2" t="str">
         <f>IF(ISNUMBER(SEARCH("lternate",'Bid Conditions'!B12)),"Yes, not evaluated","No")</f>
@@ -3835,14 +3893,17 @@
       </c>
       <c r="K12" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Responsive</v>
+        <v>Non-responsive</v>
       </c>
       <c r="L12" s="4" t="str">
-        <f>TRIM(IF(B12="No","No bid security, section 3.2. ","")&amp;IF(B12="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C12="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D12="No","Samples not received, section 3.2. ","")&amp;IF(AND(C12="Yes",LEFT(E12,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C12="Yes",LEFT(F12,2)="No"),"Bid on a superseded specification, "&amp;MID(F12,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G12,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H12="Yes","Exception to a material term, "&amp;'Bid Conditions'!C12&amp;", section 5.2 and PP-3.4.4. ",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <f>TRIM(IF(B12="No","No bid security, section 3.2. ","")&amp;IF(B12="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C12="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D12,2)="No","Sample not made to the specification as amended, "&amp;MID(D12,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C12="Yes",LEFT(E12,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C12="Yes",LEFT(F12,2)="No"),"Bid on a superseded specification, "&amp;MID(F12,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G12,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H12="Yes","Exception to a material term, "&amp;'Bid Conditions'!C12&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <v>Bid security under five percent of the total bid as written, section 3.2 and addendum 2.</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="str">
         <f>Terms!A13</f>
         <v>Thorsgard Box &amp; Label</v>
@@ -3855,19 +3916,18 @@
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H13)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="D13" s="2" t="str">
-        <f>IF(Terms!I13="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D13" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E13" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!V7,2)=ROUND('Bids as Written'!U7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H13" s="2" t="str">
         <f>'Bid Conditions'!D13</f>
@@ -3886,11 +3946,14 @@
         <v>Non-responsive</v>
       </c>
       <c r="L13" s="4" t="str">
-        <f>TRIM(IF(B13="No","No bid security, section 3.2. ","")&amp;IF(B13="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C13="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D13="No","Samples not received, section 3.2. ","")&amp;IF(AND(C13="Yes",LEFT(E13,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C13="Yes",LEFT(F13,2)="No"),"Bid on a superseded specification, "&amp;MID(F13,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G13,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H13="Yes","Exception to a material term, "&amp;'Bid Conditions'!C13&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <f>TRIM(IF(B13="No","No bid security, section 3.2. ","")&amp;IF(B13="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C13="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D13,2)="No","Sample not made to the specification as amended, "&amp;MID(D13,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C13="Yes",LEFT(E13,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C13="Yes",LEFT(F13,2)="No"),"Bid on a superseded specification, "&amp;MID(F13,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G13,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H13="Yes","Exception to a material term, "&amp;'Bid Conditions'!C13&amp;", section 5.2 and PP-3.4.4. ",""))</f>
         <v>Exception to a material term, Price hold, section 4.3, section 5.2 and PP-3.4.4.</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M13" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="str">
         <f>Terms!A14</f>
         <v>Wenzel &amp; Krause Corrugated</v>
@@ -3903,19 +3966,18 @@
         <f>IF(ISNUMBER(SEARCH(Parameters!$B$9,Terms!H14)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="D14" s="2" t="str">
-        <f>IF(Terms!I14="Yes","Yes","No")</f>
-        <v>Yes</v>
+      <c r="D14" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="E14" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!X7,2)=ROUND('Bids as Written'!W7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
         <v>Yes</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H14" s="2" t="str">
         <f>'Bid Conditions'!D14</f>
@@ -3923,7 +3985,7 @@
       </c>
       <c r="I14" s="4" t="str">
         <f>'Bid Conditions'!B14</f>
-        <v>None; the letter follows the linerboard index and holds prices firm for twelve months whatever the index does, and offers stock holding after award that the prices do not depend on</v>
+        <v>None; the letter follows the linerboard index and holds prices firm for twelve months whatever the index does, offers stock holding after award that the prices do not depend on, and says the item 5 sample was run on 32 ECT board</v>
       </c>
       <c r="J14" s="2" t="str">
         <f>IF(ISNUMBER(SEARCH("lternate",'Bid Conditions'!B14)),"Yes, not evaluated","No")</f>
@@ -3931,20 +3993,23 @@
       </c>
       <c r="K14" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Responsive</v>
+        <v>Non-responsive</v>
       </c>
       <c r="L14" s="4" t="str">
-        <f>TRIM(IF(B14="No","No bid security, section 3.2. ","")&amp;IF(B14="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C14="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(D14="No","Samples not received, section 3.2. ","")&amp;IF(AND(C14="Yes",LEFT(E14,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C14="Yes",LEFT(F14,2)="No"),"Bid on a superseded specification, "&amp;MID(F14,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G14,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H14="Yes","Exception to a material term, "&amp;'Bid Conditions'!C14&amp;", section 5.2 and PP-3.4.4. ",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+        <f>TRIM(IF(B14="No","No bid security, section 3.2. ","")&amp;IF(B14="No, short","Bid security under five percent of the total bid as written, section 3.2 and addendum 2. ","")&amp;IF(C14="No","Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5. ","")&amp;IF(LEFT(D14,2)="No","Sample not made to the specification as amended, "&amp;MID(D14,5,40)&amp;", section 3.2. ","")&amp;IF(AND(C14="Yes",LEFT(E14,2)="No"),"Item 3 priced at the superseded quantity, PP-3.4.5. ","")&amp;IF(AND(C14="Yes",LEFT(F14,2)="No"),"Bid on a superseded specification, "&amp;MID(F14,5,40)&amp;", PP-3.4.5. ","")&amp;IF(LEFT(G14,2)="No","Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4. ","")&amp;IF(H14="Yes","Exception to a material term, "&amp;'Bid Conditions'!C14&amp;", section 5.2 and PP-3.4.4. ",""))</f>
+        <v>Sample not made to the specification as amended, item 5 sample on 32 ECT, section 3.2.</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="2">
         <f>COUNTIF(K4:K14,"Responsive")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -3953,17 +4018,22 @@
       </c>
       <c r="B17" s="2">
         <f>COUNTIF(K4:K14,"Non-responsive")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>390</v>
+        <v>398</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -3988,33 +4058,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -4060,7 +4130,7 @@
       </c>
       <c r="C5" s="7">
         <f>IF(B5="","",INDEX(Evaluation!$B$21:$L$21,MATCH(A5,Evaluation!$B$25:$L$25,0)))</f>
-        <v>99959</v>
+        <v>100079</v>
       </c>
       <c r="D5" s="2" t="str">
         <f>IF(B5="","",INDEX('Bid Receipt'!$D$4:$D$14,MATCH(B5,'Bid Receipt'!$A$4:$A$14,0))&amp;" "&amp;INDEX('Bid Receipt'!$E$4:$E$14,MATCH(B5,'Bid Receipt'!$A$4:$A$14,0)))</f>
@@ -4089,15 +4159,15 @@
       </c>
       <c r="B6" s="2" t="str">
         <f>IFERROR(INDEX(Evaluation!$B$3:$L$3,MATCH(A6,Evaluation!$B$25:$L$25,0)),"")</f>
-        <v>Ridgecrest Packaging</v>
+        <v>Dahlgren Paper Box Co.</v>
       </c>
       <c r="C6" s="7">
         <f>IF(B6="","",INDEX(Evaluation!$B$21:$L$21,MATCH(A6,Evaluation!$B$25:$L$25,0)))</f>
-        <v>99927.25</v>
+        <v>100026.33</v>
       </c>
       <c r="D6" s="2" t="str">
         <f>IF(B6="","",INDEX('Bid Receipt'!$D$4:$D$14,MATCH(B6,'Bid Receipt'!$A$4:$A$14,0))&amp;" "&amp;INDEX('Bid Receipt'!$E$4:$E$14,MATCH(B6,'Bid Receipt'!$A$4:$A$14,0)))</f>
-        <v>10/06/2026 08:15</v>
+        <v>10/06/2026 09:33</v>
       </c>
       <c r="E6" s="2">
         <f>IF(B6="","",COUNTIFS('Holds on Bidders'!$C$4:$C$7,B6,'Holds on Bidders'!$I$4:$I$7,"Open"))</f>
@@ -4122,31 +4192,31 @@
       </c>
       <c r="B7" s="2" t="str">
         <f>IFERROR(INDEX(Evaluation!$B$3:$L$3,MATCH(A7,Evaluation!$B$25:$L$25,0)),"")</f>
-        <v>Wenzel &amp; Krause Corrugated</v>
-      </c>
-      <c r="C7" s="7">
+        <v/>
+      </c>
+      <c r="C7" s="7" t="str">
         <f>IF(B7="","",INDEX(Evaluation!$B$21:$L$21,MATCH(A7,Evaluation!$B$25:$L$25,0)))</f>
-        <v>103793.46</v>
+        <v/>
       </c>
       <c r="D7" s="2" t="str">
         <f>IF(B7="","",INDEX('Bid Receipt'!$D$4:$D$14,MATCH(B7,'Bid Receipt'!$A$4:$A$14,0))&amp;" "&amp;INDEX('Bid Receipt'!$E$4:$E$14,MATCH(B7,'Bid Receipt'!$A$4:$A$14,0)))</f>
-        <v>10/06/2026 09:41</v>
-      </c>
-      <c r="E7" s="2">
+        <v/>
+      </c>
+      <c r="E7" s="2" t="str">
         <f>IF(B7="","",COUNTIFS('Holds on Bidders'!$C$4:$C$7,B7,'Holds on Bidders'!$I$4:$I$7,"Open"))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F7" s="2" t="str">
         <f>IF(B7="","",IF(COUNTIF($F$4:F6,"Award")&gt;0,"Not reached",IF(E7=0,"Award","Passed over")))</f>
-        <v>Not reached</v>
+        <v/>
       </c>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Not decided, PP-3.7.1</v>
+        <v/>
       </c>
       <c r="H7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Responsibility decided only for the bidder in line, PP-3.7.1</v>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -4400,7 +4470,7 @@
       </c>
       <c r="B19" s="7">
         <f>INDEX(C4:C14,MATCH("Award",F4:F14,0))</f>
-        <v>99959</v>
+        <v>100079</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -4409,7 +4479,7 @@
       </c>
       <c r="B20" s="2" t="str">
         <f>IFERROR(INDEX(B4:B14,MATCH("Award",F4:F14,0)+1),"None")</f>
-        <v>Ridgecrest Packaging</v>
+        <v>Dahlgren Paper Box Co.</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -4418,7 +4488,7 @@
       </c>
       <c r="B21" s="7">
         <f>IFERROR(INDEX(C4:C14,MATCH("Award",F4:F14,0)+1),0)</f>
-        <v>99927.25</v>
+        <v>100026.33</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4427,7 +4497,7 @@
       </c>
       <c r="B22" s="7">
         <f>ROUND(B19-B21,2)</f>
-        <v>31.75</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4454,7 +4524,7 @@
       </c>
       <c r="B25" s="2" t="str">
         <f>IFERROR(INDEX(D4:D14,MATCH("Award",F4:F14,0)+1),"None")</f>
-        <v>10/06/2026 08:15</v>
+        <v>10/06/2026 09:33</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -4481,17 +4551,17 @@
       </c>
       <c r="B28" s="7">
         <f>ROUND(B19-B27,2)</f>
-        <v>728.28</v>
+        <v>848.28</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -4511,18 +4581,18 @@
   <sheetData>
     <row r="1" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>137</v>
@@ -4546,18 +4616,18 @@
         <v>166</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B4" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!C5)</f>
@@ -4565,7 +4635,7 @@
       </c>
       <c r="C4" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!E5)</f>
-        <v>0.591</v>
+        <v>0.597</v>
       </c>
       <c r="D4" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!G5)</f>
@@ -4604,12 +4674,12 @@
         <v>0.628</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="B5" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!C6)</f>
@@ -4617,7 +4687,7 @@
       </c>
       <c r="C5" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!E6)</f>
-        <v>0.397</v>
+        <v>0.4</v>
       </c>
       <c r="D5" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!G6)</f>
@@ -4656,12 +4726,12 @@
         <v>0.428</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B6" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,3,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,3,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!C7)</f>
@@ -4708,12 +4778,12 @@
         <v>0.301</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="B7" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!C8)</f>
@@ -4721,7 +4791,7 @@
       </c>
       <c r="C7" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!E8)</f>
-        <v>1.688</v>
+        <v>1.702</v>
       </c>
       <c r="D7" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!G8)</f>
@@ -4760,12 +4830,12 @@
         <v>1.79</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="B8" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!C9)</f>
@@ -4773,7 +4843,7 @@
       </c>
       <c r="C8" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!E9)</f>
-        <v>0.968</v>
+        <v>0.984</v>
       </c>
       <c r="D8" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!G9)</f>
@@ -4797,7 +4867,7 @@
       </c>
       <c r="I8" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,I$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,I$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!Q9)</f>
-        <v>0.952</v>
+        <v>0.957</v>
       </c>
       <c r="J8" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,J$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,J$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!S9)</f>
@@ -4812,12 +4882,12 @@
         <v>1.012</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B9" s="7">
         <f>ROUND(B4*Parameters!$B$15,2)</f>
@@ -4825,7 +4895,7 @@
       </c>
       <c r="C9" s="7">
         <f>ROUND(C4*Parameters!$B$15,2)</f>
-        <v>26595</v>
+        <v>26865</v>
       </c>
       <c r="D9" s="7">
         <f>ROUND(D4*Parameters!$B$15,2)</f>
@@ -4864,12 +4934,12 @@
         <v>28260</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B10" s="7">
         <f>ROUND(B5*Parameters!$B$16,2)</f>
@@ -4877,7 +4947,7 @@
       </c>
       <c r="C10" s="7">
         <f>ROUND(C5*Parameters!$B$16,2)</f>
-        <v>25408</v>
+        <v>25600</v>
       </c>
       <c r="D10" s="7">
         <f>ROUND(D5*Parameters!$B$16,2)</f>
@@ -4916,12 +4986,12 @@
         <v>27392</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B11" s="7">
         <f>ROUND(B6*Parameters!$B$17,2)</f>
@@ -4968,12 +5038,12 @@
         <v>8127</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B12" s="7">
         <f>ROUND(B7*Parameters!$B$18,2)</f>
@@ -4981,7 +5051,7 @@
       </c>
       <c r="C12" s="7">
         <f>ROUND(C7*Parameters!$B$18,2)</f>
-        <v>15192</v>
+        <v>15318</v>
       </c>
       <c r="D12" s="7">
         <f>ROUND(D7*Parameters!$B$18,2)</f>
@@ -5020,12 +5090,12 @@
         <v>16110</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="B13" s="7">
         <f>ROUND(B8*Parameters!$B$19,2)</f>
@@ -5033,7 +5103,7 @@
       </c>
       <c r="C13" s="7">
         <f>ROUND(C8*Parameters!$B$19,2)</f>
-        <v>23232</v>
+        <v>23616</v>
       </c>
       <c r="D13" s="7">
         <f>ROUND(D8*Parameters!$B$19,2)</f>
@@ -5057,7 +5127,7 @@
       </c>
       <c r="I13" s="7">
         <f>ROUND(I8*Parameters!$B$19,2)</f>
-        <v>22848</v>
+        <v>22968</v>
       </c>
       <c r="J13" s="7">
         <f>ROUND(J8*Parameters!$B$19,2)</f>
@@ -5072,12 +5142,12 @@
         <v>24288</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B14" s="11">
         <f t="shared" ref="B14:L14" si="0">SUM(B9:B13)</f>
@@ -5085,7 +5155,7 @@
       </c>
       <c r="C14" s="11">
         <f t="shared" si="0"/>
-        <v>98095</v>
+        <v>99067</v>
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
@@ -5109,7 +5179,7 @@
       </c>
       <c r="I14" s="11">
         <f t="shared" si="0"/>
-        <v>98109</v>
+        <v>98229</v>
       </c>
       <c r="J14" s="11">
         <f t="shared" si="0"/>
@@ -5124,12 +5194,12 @@
         <v>104177</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B15" s="7">
         <f>'Bids as Written'!D10</f>
@@ -5176,12 +5246,12 @@
         <v>1700</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B16" s="2" t="str">
         <f>Terms!D4</f>
@@ -5228,7 +5298,7 @@
         <v>Destination</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
@@ -5269,7 +5339,7 @@
       </c>
       <c r="J17" s="7">
         <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,J$3)</f>
-        <v>7339.24</v>
+        <v>7663.72</v>
       </c>
       <c r="K17" s="7">
         <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,K$3)</f>
@@ -5280,12 +5350,12 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="B18" s="12">
         <f>IFERROR(VALUE(LEFT(Terms!E4,FIND("%",Terms!E4)-1))/100,0)</f>
@@ -5332,12 +5402,12 @@
         <v>0.02</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B19" s="2">
         <f>IFERROR(VALUE(MID(Terms!E4,FIND("%",Terms!E4)+2,FIND(",",Terms!E4)-FIND("%",Terms!E4)-2)),0)</f>
@@ -5384,7 +5454,7 @@
         <v>20</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -5397,7 +5467,7 @@
       </c>
       <c r="C20" s="7">
         <f>IF(C19&gt;=Parameters!$B$4,ROUND(C14*C18,2),0)</f>
-        <v>980.95</v>
+        <v>990.67</v>
       </c>
       <c r="D20" s="7">
         <f>IF(D19&gt;=Parameters!$B$4,ROUND(D14*D18,2),0)</f>
@@ -5436,7 +5506,7 @@
         <v>2083.54</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
@@ -5449,7 +5519,7 @@
       </c>
       <c r="C21" s="11">
         <f t="shared" si="1"/>
-        <v>99064.05</v>
+        <v>100026.33</v>
       </c>
       <c r="D21" s="11">
         <f t="shared" si="1"/>
@@ -5473,11 +5543,11 @@
       </c>
       <c r="I21" s="11">
         <f t="shared" si="1"/>
-        <v>99959</v>
+        <v>100079</v>
       </c>
       <c r="J21" s="11">
         <f t="shared" si="1"/>
-        <v>99927.25</v>
+        <v>100251.73</v>
       </c>
       <c r="K21" s="11">
         <f t="shared" si="1"/>
@@ -5488,7 +5558,7 @@
         <v>103793.46</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
@@ -5501,7 +5571,7 @@
       </c>
       <c r="C22" s="7">
         <f>'Bids as Written'!F11</f>
-        <v>100045</v>
+        <v>101317</v>
       </c>
       <c r="D22" s="7">
         <f>'Bids as Written'!H11</f>
@@ -5525,7 +5595,7 @@
       </c>
       <c r="I22" s="7">
         <f>'Bids as Written'!R11</f>
-        <v>101839</v>
+        <v>101959</v>
       </c>
       <c r="J22" s="7">
         <f>'Bids as Written'!T11</f>
@@ -5553,7 +5623,7 @@
       </c>
       <c r="C23" s="2" t="str">
         <f>Responsiveness!K5</f>
-        <v>Non-responsive</v>
+        <v>Responsive</v>
       </c>
       <c r="D23" s="2" t="str">
         <f>Responsiveness!K6</f>
@@ -5581,7 +5651,7 @@
       </c>
       <c r="J23" s="2" t="str">
         <f>Responsiveness!K12</f>
-        <v>Responsive</v>
+        <v>Non-responsive</v>
       </c>
       <c r="K23" s="2" t="str">
         <f>Responsiveness!K13</f>
@@ -5589,7 +5659,7 @@
       </c>
       <c r="L23" s="2" t="str">
         <f>Responsiveness!K14</f>
-        <v>Responsive</v>
+        <v>Non-responsive</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>6</v>
@@ -5597,7 +5667,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="B24" s="9">
         <f>'Bid Receipt'!F4</f>
@@ -5649,15 +5719,15 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="B25" s="2" t="str">
         <f>IF(B23="Responsive",COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&lt;"&amp;(B21-Parameters!$B$7))+COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&gt;="&amp;(B21-Parameters!$B$7),$B$21:$L$21,"&lt;="&amp;(B21+Parameters!$B$7),$B$24:$L$24,"&lt;"&amp;B24)+1,"Set aside")</f>
         <v>Set aside</v>
       </c>
-      <c r="C25" s="2" t="str">
+      <c r="C25" s="2">
         <f>IF(C23="Responsive",COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&lt;"&amp;(C21-Parameters!$B$7))+COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&gt;="&amp;(C21-Parameters!$B$7),$B$21:$L$21,"&lt;="&amp;(C21+Parameters!$B$7),$B$24:$L$24,"&lt;"&amp;C24)+1,"Set aside")</f>
-        <v>Set aside</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2" t="str">
         <f>IF(D23="Responsive",COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&lt;"&amp;(D21-Parameters!$B$7))+COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&gt;="&amp;(D21-Parameters!$B$7),$B$21:$L$21,"&lt;="&amp;(D21+Parameters!$B$7),$B$24:$L$24,"&lt;"&amp;D24)+1,"Set aside")</f>
@@ -5683,25 +5753,25 @@
         <f>IF(I23="Responsive",COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&lt;"&amp;(I21-Parameters!$B$7))+COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&gt;="&amp;(I21-Parameters!$B$7),$B$21:$L$21,"&lt;="&amp;(I21+Parameters!$B$7),$B$24:$L$24,"&lt;"&amp;I24)+1,"Set aside")</f>
         <v>2</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="2" t="str">
         <f>IF(J23="Responsive",COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&lt;"&amp;(J21-Parameters!$B$7))+COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&gt;="&amp;(J21-Parameters!$B$7),$B$21:$L$21,"&lt;="&amp;(J21+Parameters!$B$7),$B$24:$L$24,"&lt;"&amp;J24)+1,"Set aside")</f>
-        <v>3</v>
+        <v>Set aside</v>
       </c>
       <c r="K25" s="2" t="str">
         <f>IF(K23="Responsive",COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&lt;"&amp;(K21-Parameters!$B$7))+COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&gt;="&amp;(K21-Parameters!$B$7),$B$21:$L$21,"&lt;="&amp;(K21+Parameters!$B$7),$B$24:$L$24,"&lt;"&amp;K24)+1,"Set aside")</f>
         <v>Set aside</v>
       </c>
-      <c r="L25" s="2">
+      <c r="L25" s="2" t="str">
         <f>IF(L23="Responsive",COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&lt;"&amp;(L21-Parameters!$B$7))+COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&gt;="&amp;(L21-Parameters!$B$7),$B$21:$L$21,"&lt;="&amp;(L21+Parameters!$B$7),$B$24:$L$24,"&lt;"&amp;L24)+1,"Set aside")</f>
-        <v>4</v>
+        <v>Set aside</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="B27" s="7">
         <f>_xlfn.MINIFS(B21:L21,B23:L23,"Responsive")</f>
@@ -5710,7 +5780,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B28" s="2" t="str">
         <f>INDEX($B$3:$L$3,MATCH(1,$B$25:$L$25,0))</f>
@@ -5719,7 +5789,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="B29" s="2" t="str">
         <f>Responsibility!B18</f>
@@ -5732,12 +5802,12 @@
       </c>
       <c r="B30" s="7">
         <f>Responsibility!B19</f>
-        <v>99959</v>
+        <v>100079</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B31" s="2" t="str">
         <f>INDEX($B$3:$L$3,MATCH(MIN(B22:L22),B22:L22,0))</f>
@@ -5750,12 +5820,12 @@
       </c>
       <c r="B32" s="2" t="str">
         <f>IF(B30&gt;Parameters!$B$5,"Vice president of operations","Director of supply chain")</f>
-        <v>Director of supply chain</v>
+        <v>Vice president of operations</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -5780,41 +5850,41 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
@@ -5850,7 +5920,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -5886,7 +5956,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
@@ -5922,7 +5992,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" s="2">
         <v>4</v>
@@ -5958,7 +6028,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
@@ -5994,18 +6064,18 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
       </c>
       <c r="C9" s="10">
         <f>'Bids as Written'!E5</f>
-        <v>0.591</v>
+        <v>0.597</v>
       </c>
       <c r="D9" s="10">
         <f>Evaluation!C4</f>
-        <v>0.591</v>
+        <v>0.597</v>
       </c>
       <c r="E9" s="2">
         <f>Parameters!B15</f>
@@ -6013,11 +6083,11 @@
       </c>
       <c r="F9" s="7">
         <f>'Bids as Written'!F5</f>
-        <v>26595</v>
+        <v>26865</v>
       </c>
       <c r="G9" s="7">
         <f>Evaluation!C9</f>
-        <v>26595</v>
+        <v>26865</v>
       </c>
       <c r="H9" s="7">
         <f t="shared" si="0"/>
@@ -6030,18 +6100,18 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
       </c>
       <c r="C10" s="10">
         <f>'Bids as Written'!E6</f>
-        <v>0.397</v>
+        <v>0.4</v>
       </c>
       <c r="D10" s="10">
         <f>Evaluation!C5</f>
-        <v>0.397</v>
+        <v>0.4</v>
       </c>
       <c r="E10" s="2">
         <f>Parameters!B16</f>
@@ -6049,24 +6119,24 @@
       </c>
       <c r="F10" s="7">
         <f>'Bids as Written'!F6</f>
-        <v>25408</v>
+        <v>25900</v>
       </c>
       <c r="G10" s="7">
         <f>Evaluation!C10</f>
-        <v>25408</v>
+        <v>25600</v>
       </c>
       <c r="H10" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I10" s="2" t="str">
         <f>IF(H10=0,"",IF(C10&lt;&gt;D10,"Unit price changed by a modification received before the due time, section 3.4",IF(ROUND(C10*Parameters!$B$10,2)=F10,"Extension written at the superseded quantity, corrected, 4.1 and PP-3.4.5","Extension corrected, unit price governs, 4.1")))</f>
-        <v/>
+        <v>Extension corrected, unit price governs, 4.1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B11" s="2">
         <v>3</v>
@@ -6102,18 +6172,18 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B12" s="2">
         <v>4</v>
       </c>
       <c r="C12" s="10">
         <f>'Bids as Written'!E8</f>
-        <v>1.688</v>
+        <v>1.702</v>
       </c>
       <c r="D12" s="10">
         <f>Evaluation!C7</f>
-        <v>1.688</v>
+        <v>1.702</v>
       </c>
       <c r="E12" s="2">
         <f>Parameters!B18</f>
@@ -6121,11 +6191,11 @@
       </c>
       <c r="F12" s="7">
         <f>'Bids as Written'!F8</f>
-        <v>15192</v>
+        <v>15318</v>
       </c>
       <c r="G12" s="7">
         <f>Evaluation!C12</f>
-        <v>15192</v>
+        <v>15318</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="0"/>
@@ -6138,18 +6208,18 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
       </c>
       <c r="C13" s="10">
         <f>'Bids as Written'!E9</f>
-        <v>0.968</v>
+        <v>0.984</v>
       </c>
       <c r="D13" s="10">
         <f>Evaluation!C8</f>
-        <v>0.968</v>
+        <v>0.984</v>
       </c>
       <c r="E13" s="2">
         <f>Parameters!B19</f>
@@ -6157,11 +6227,11 @@
       </c>
       <c r="F13" s="7">
         <f>'Bids as Written'!F9</f>
-        <v>23232</v>
+        <v>23616</v>
       </c>
       <c r="G13" s="7">
         <f>Evaluation!C13</f>
-        <v>23232</v>
+        <v>23616</v>
       </c>
       <c r="H13" s="7">
         <f t="shared" si="0"/>
@@ -7225,11 +7295,11 @@
       </c>
       <c r="C43" s="10">
         <f>'Bids as Written'!Q9</f>
-        <v>0.952</v>
+        <v>0.957</v>
       </c>
       <c r="D43" s="10">
         <f>Evaluation!I8</f>
-        <v>0.952</v>
+        <v>0.957</v>
       </c>
       <c r="E43" s="2">
         <f>Parameters!B19</f>
@@ -7237,11 +7307,11 @@
       </c>
       <c r="F43" s="7">
         <f>'Bids as Written'!R9</f>
-        <v>22848</v>
+        <v>22968</v>
       </c>
       <c r="G43" s="7">
         <f>Evaluation!I13</f>
-        <v>22848</v>
+        <v>22968</v>
       </c>
       <c r="H43" s="7">
         <f t="shared" si="1"/>
@@ -7434,7 +7504,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B49" s="2">
         <v>1</v>
@@ -7470,7 +7540,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B50" s="2">
         <v>2</v>
@@ -7506,7 +7576,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B51" s="2">
         <v>3</v>
@@ -7542,7 +7612,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B52" s="2">
         <v>4</v>
@@ -7578,7 +7648,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B53" s="2">
         <v>5</v>
@@ -7614,7 +7684,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B54" s="2">
         <v>1</v>
@@ -7650,7 +7720,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B55" s="2">
         <v>2</v>
@@ -7686,7 +7756,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B56" s="2">
         <v>3</v>
@@ -7722,7 +7792,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B57" s="2">
         <v>4</v>
@@ -7758,7 +7828,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B58" s="2">
         <v>5</v>
@@ -7798,12 +7868,12 @@
       </c>
       <c r="H59" s="2">
         <f>COUNTIF(I4:I58,"Extension*")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="H60" s="2">
         <f>COUNTIF(I4:I58,"Unit price changed*")</f>
@@ -7812,7 +7882,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -7830,87 +7900,87 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="160" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="128" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="128" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -7930,128 +8000,128 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2">
         <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2">
         <v>100000</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2">
         <v>100</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2">
         <v>36000</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" s="8">
         <v>0.05</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B12" s="9">
         <v>202610061000</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -8062,7 +8132,7 @@
         <v>45000</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -8073,7 +8143,7 @@
         <v>64000</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -8084,7 +8154,7 @@
         <v>27000</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -8095,7 +8165,7 @@
         <v>9000</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -8106,7 +8176,7 @@
         <v>24000</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -8147,81 +8217,81 @@
   <sheetData>
     <row r="1" spans="1:24" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
@@ -8229,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="10">
         <v>0.571</v>
@@ -8238,10 +8308,10 @@
         <v>25695</v>
       </c>
       <c r="E5" s="10">
-        <v>0.591</v>
+        <v>0.597</v>
       </c>
       <c r="F5" s="7">
-        <v>26595</v>
+        <v>26865</v>
       </c>
       <c r="G5" s="10">
         <v>0.594</v>
@@ -8303,7 +8373,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="10">
         <v>0.398</v>
@@ -8312,10 +8382,10 @@
         <v>25472</v>
       </c>
       <c r="E6" s="10">
-        <v>0.397</v>
+        <v>0.4</v>
       </c>
       <c r="F6" s="7">
-        <v>25408</v>
+        <v>25900</v>
       </c>
       <c r="G6" s="10">
         <v>0.404</v>
@@ -8377,7 +8447,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="10">
         <v>0.276</v>
@@ -8451,7 +8521,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="10">
         <v>1.655</v>
@@ -8460,10 +8530,10 @@
         <v>14895</v>
       </c>
       <c r="E8" s="10">
-        <v>1.688</v>
+        <v>1.702</v>
       </c>
       <c r="F8" s="7">
-        <v>15192</v>
+        <v>15318</v>
       </c>
       <c r="G8" s="10">
         <v>1.702</v>
@@ -8525,7 +8595,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="10">
         <v>0.94</v>
@@ -8534,10 +8604,10 @@
         <v>22560</v>
       </c>
       <c r="E9" s="10">
-        <v>0.968</v>
+        <v>0.984</v>
       </c>
       <c r="F9" s="7">
-        <v>23232</v>
+        <v>23616</v>
       </c>
       <c r="G9" s="10">
         <v>0.972</v>
@@ -8570,10 +8640,10 @@
         <v>23184</v>
       </c>
       <c r="Q9" s="10">
-        <v>0.952</v>
+        <v>0.957</v>
       </c>
       <c r="R9" s="7">
-        <v>22848</v>
+        <v>22968</v>
       </c>
       <c r="S9" s="10">
         <v>0.9</v>
@@ -8596,7 +8666,7 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D10" s="7">
         <v>1500</v>
@@ -8642,7 +8712,7 @@
       </c>
       <c r="F11" s="11">
         <f>SUM(F5:F10)</f>
-        <v>100045</v>
+        <v>101317</v>
       </c>
       <c r="H11" s="11">
         <f>SUM(H5:H10)</f>
@@ -8666,7 +8736,7 @@
       </c>
       <c r="R11" s="11">
         <f>SUM(R5:R10)</f>
-        <v>101839</v>
+        <v>101959</v>
       </c>
       <c r="T11" s="11">
         <f>SUM(T5:T10)</f>
@@ -8683,7 +8753,7 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -8710,100 +8780,100 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>136</v>
@@ -8820,22 +8890,22 @@
         <v>139</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>140</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>141</v>
@@ -8852,22 +8922,22 @@
         <v>144</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>145</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>146</v>
@@ -8884,13 +8954,13 @@
         <v>149</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>150</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>151</v>
@@ -8899,7 +8969,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>152</v>
@@ -8913,7 +8983,7 @@
         <v>154</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>155</v>
@@ -8922,16 +8992,16 @@
         <v>145</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>156</v>
@@ -8945,25 +9015,25 @@
         <v>158</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>160</v>
@@ -8980,22 +9050,22 @@
         <v>163</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>164</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>165</v>
@@ -9009,92 +9079,92 @@
         <v>167</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>163</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -9117,27 +9187,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9146,19 +9216,19 @@
         <v>Brannock Box Company</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9167,19 +9237,19 @@
         <v>Dahlgren Paper Box Co.</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9188,19 +9258,19 @@
         <v>Halvard Corrugated</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9209,19 +9279,19 @@
         <v>Kessel Container Corp.</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9230,19 +9300,19 @@
         <v>Loken &amp; Vik Container</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9251,19 +9321,19 @@
         <v>Mesabi Container Co.</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9272,19 +9342,19 @@
         <v>Otter Tail Corrugated</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9293,19 +9363,19 @@
         <v>Pemberton Container</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9314,19 +9384,19 @@
         <v>Ridgecrest Packaging</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9335,19 +9405,19 @@
         <v>Thorsgard Box &amp; Label</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9356,24 +9426,24 @@
         <v>Wenzel &amp; Krause Corrugated</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -9400,39 +9470,39 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -9440,19 +9510,19 @@
         <v>166</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G4" s="9">
         <f t="shared" ref="G4:G9" si="0">VALUE(RIGHT(E4,4)&amp;LEFT(E4,2)&amp;MID(E4,4,2)&amp;LEFT(F4,2)&amp;RIGHT(F4,2))</f>
@@ -9463,30 +9533,30 @@
         <v>Yes</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G5" s="9">
         <f t="shared" si="0"/>
@@ -9497,10 +9567,10 @@
         <v>No</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -9508,19 +9578,19 @@
         <v>161</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="0"/>
@@ -9531,44 +9601,44 @@
         <v>Yes</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G7" s="9">
         <f t="shared" si="0"/>
-        <v>202610060935</v>
+        <v>202610060938</v>
       </c>
       <c r="H7" s="2" t="str">
         <f>IF(G7&lt;Parameters!$B$12,"Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -9576,19 +9646,19 @@
         <v>157</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G8" s="9">
         <f t="shared" si="0"/>
@@ -9599,10 +9669,10 @@
         <v>No</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -9610,19 +9680,19 @@
         <v>147</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G9" s="9">
         <f t="shared" si="0"/>
@@ -9633,33 +9703,33 @@
         <v>No</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -9689,16 +9759,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" s="10">
-        <v>0.262</v>
+        <v>0.597</v>
       </c>
       <c r="D14" s="10">
-        <v>0.255</v>
+        <v>0.594</v>
       </c>
       <c r="E14" s="2">
         <v>7</v>
@@ -9709,12 +9779,12 @@
       </c>
       <c r="G14" s="7">
         <f>ROUND((D14-C14)*INDEX(Parameters!$B$15:$B$19,B14),2)</f>
-        <v>-189</v>
+        <v>-135</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B15" s="2">
         <v>1</v>
@@ -9739,7 +9809,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -9764,7 +9834,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
@@ -9789,7 +9859,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -9814,7 +9884,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -9839,7 +9909,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B21" s="2">
         <f>COUNTIF(F13:F19,"Yes")</f>
@@ -9848,7 +9918,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B22" s="2">
         <f>COUNTIF(F13:F19,"No")</f>
@@ -9857,7 +9927,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -9880,30 +9950,30 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -9939,26 +10009,23 @@
       </c>
       <c r="B5" s="2" t="str">
         <f>Terms!G5</f>
-        <v>Cashier's check, $4,904.75, no. 20871</v>
-      </c>
-      <c r="C5" s="7">
-        <v>4904.75</v>
+        <v>Surety bond</v>
       </c>
       <c r="D5" s="7">
         <f>'Bids as Written'!F11</f>
-        <v>100045</v>
+        <v>101317</v>
       </c>
       <c r="E5" s="7">
         <f>ROUND(D5*Parameters!$B$11,2)</f>
-        <v>5002.25</v>
+        <v>5065.85</v>
       </c>
       <c r="F5" s="7">
         <f t="shared" si="0"/>
-        <v>97.5</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="str">
         <f>IF(Terms!F5&lt;&gt;"Yes","No",IF(F5&gt;0,"No, short","Yes"))</f>
-        <v>No, short</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -10105,11 +10172,11 @@
       </c>
       <c r="D11" s="7">
         <f>'Bids as Written'!R11</f>
-        <v>101839</v>
+        <v>101959</v>
       </c>
       <c r="E11" s="7">
         <f>ROUND(D11*Parameters!$B$11,2)</f>
-        <v>5091.95</v>
+        <v>5097.95</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" si="0"/>
@@ -10127,7 +10194,10 @@
       </c>
       <c r="B12" s="2" t="str">
         <f>Terms!G12</f>
-        <v>Surety bond</v>
+        <v>Cashier's check, $4,554.95, no. 7730412</v>
+      </c>
+      <c r="C12" s="7">
+        <v>4554.95</v>
       </c>
       <c r="D12" s="7">
         <f>'Bids as Written'!T11</f>
@@ -10139,11 +10209,11 @@
       </c>
       <c r="F12" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G12" s="2" t="str">
         <f>IF(Terms!F12&lt;&gt;"Yes","No",IF(F12&gt;0,"No, short","Yes"))</f>
-        <v>Yes</v>
+        <v>No, short</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -10203,7 +10273,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -10227,30 +10297,30 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -10259,16 +10329,16 @@
         <v>Brannock Box Company</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F4" s="9">
         <f t="shared" ref="F4:F14" si="0">VALUE(RIGHT(D4,4)&amp;LEFT(D4,2)&amp;MID(D4,4,2)&amp;LEFT(E4,2)&amp;RIGHT(E4,2))</f>
@@ -10281,16 +10351,16 @@
         <v>Dahlgren Paper Box Co.</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F5" s="9">
         <f t="shared" si="0"/>
@@ -10303,16 +10373,16 @@
         <v>Halvard Corrugated</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="0"/>
@@ -10325,16 +10395,16 @@
         <v>Kessel Container Corp.</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F7" s="9">
         <f t="shared" si="0"/>
@@ -10347,23 +10417,23 @@
         <v>Loken &amp; Vik Container</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F8" s="9">
         <f t="shared" si="0"/>
         <v>202610061000</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -10372,16 +10442,16 @@
         <v>Mesabi Container Co.</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F9" s="9">
         <f t="shared" si="0"/>
@@ -10394,16 +10464,16 @@
         <v>Otter Tail Corrugated</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F10" s="9">
         <f t="shared" si="0"/>
@@ -10416,23 +10486,23 @@
         <v>Pemberton Container</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F11" s="9">
         <f t="shared" si="0"/>
         <v>202610051137</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -10441,23 +10511,23 @@
         <v>Ridgecrest Packaging</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F12" s="9">
         <f t="shared" si="0"/>
         <v>202610060815</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -10466,16 +10536,16 @@
         <v>Thorsgard Box &amp; Label</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F13" s="9">
         <f t="shared" si="0"/>
@@ -10488,16 +10558,16 @@
         <v>Wenzel &amp; Krause Corrugated</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F14" s="9">
         <f t="shared" si="0"/>
@@ -10506,7 +10576,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B16" s="2">
         <f>COUNTIF(F4:F14,"&lt;="&amp;Parameters!$B$12)</f>
@@ -10515,7 +10585,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -10525,7 +10595,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -10537,45 +10607,49 @@
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="44" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>137</v>
@@ -10584,28 +10658,31 @@
         <v>137</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I4" s="2" t="str">
         <f>IF(G4="","Open","Cleared")</f>
         <v>Cleared</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>161</v>
@@ -10614,85 +10691,94 @@
         <v>161</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="I5" s="2" t="str">
         <f>IF(G5="","Open","Cleared")</f>
         <v>Cleared</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J5" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>147</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="I6" s="2" t="str">
         <f>IF(G6="","Open","Cleared")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J6" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="I7" s="2" t="str">
         <f>IF(G7="","Open","Cleared")</f>
         <v>Cleared</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J7" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/submissions/10-carton-bid-evaluation/solution/bid_evaluation_itb_2026_17.xlsx
+++ b/submissions/10-carton-bid-evaluation/solution/bid_evaluation_itb_2026_17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E974349-F641-3E4D-80F5-079959CFB2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3156A4-BE2D-6941-A44D-265ED5A895FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="470">
   <si>
     <t>Award recommendation, ITB 2026-17, corrugated shipping cartons, annual requirement</t>
   </si>
@@ -182,7 +182,7 @@
     <t>Award is by lot to the responsive and responsible bidder first in the order of 5.1 and 5.6, checked under PP-3.7.1; every figure on this page reads from the tab named beside it.</t>
   </si>
   <si>
-    <t>The award value is over one hundred thousand dollars, so PP-3.5.3 places the approval with the vice president of operations; the signature line below follows the policy.</t>
+    <t>The award value is at or under one hundred thousand dollars, so PP-3.5.3 places the approval with the director of supply chain; the signature line below follows the policy.</t>
   </si>
   <si>
     <t>Recommended by</t>
@@ -200,7 +200,7 @@
     <t>Approved</t>
   </si>
   <si>
-    <t>Torsten Nordvik, Vice President of Operations</t>
+    <t>Director of supply chain</t>
   </si>
   <si>
     <t>Terms the evaluation applies, from ITB 2026-17 as amended and policy PP-3</t>
@@ -446,13 +446,16 @@
     <t>MN</t>
   </si>
   <si>
-    <t>1% 30, net 45</t>
+    <t>Origin, shipping plant</t>
+  </si>
+  <si>
+    <t>2% 10, net 30</t>
   </si>
   <si>
     <t>1, 2</t>
   </si>
   <si>
-    <t>All items St. Cloud, MN</t>
+    <t>Items 1 to 3 St. Cloud, MN; items 4 and 5 Eau Claire, WI</t>
   </si>
   <si>
     <t>Halvard Corrugated</t>
@@ -536,9 +539,6 @@
     <t>WI</t>
   </si>
   <si>
-    <t>2% 10, net 30</t>
-  </si>
-  <si>
     <t>All items Neenah, WI</t>
   </si>
   <si>
@@ -551,9 +551,6 @@
     <t>NE</t>
   </si>
   <si>
-    <t>Origin, shipping plant</t>
-  </si>
-  <si>
     <t>1% 20, net 45</t>
   </si>
   <si>
@@ -623,27 +620,30 @@
     <t>Twelve months from award</t>
   </si>
   <si>
-    <t>None; releases taken in any pallet quantity; the form extends item 2 at 25,900.00 against 25,600.00 at the unit price</t>
+    <t>None; FOB origin at the shipping plant, items 1 to 3 from St. Cloud and items 4 and 5 from Eau Claire; the form extends item 2 at 24,044.00 against 23,744.00 at the unit price; the first envelope of October 1 was withdrawn and handed back on October 5</t>
+  </si>
+  <si>
+    <t>FOB terms as permitted by 3.3</t>
+  </si>
+  <si>
+    <t>FOB origin is permitted by 3.3, with freight added under section 5.4 for the plant that ships each item. The extension is corrected under 4.1 on the Extensions tab. The bid opened is the resubmitted envelope of October 6, section 3.4</t>
+  </si>
+  <si>
+    <t>Prices firm for twelve months, with a raw material surcharge on the unit prices should the Pulp and Paper Week 42 lb kraft linerboard index rise more than 6 percent from award; the form boxes read Yes and None</t>
+  </si>
+  <si>
+    <t>Price hold, section 4.3</t>
+  </si>
+  <si>
+    <t>section 4.3 makes a bid that conditions its prices on an index an exception to a material term; section 5.2; PP-3.4.4</t>
+  </si>
+  <si>
+    <t>None; prices hold through December 31, 2027, which runs past twelve months from any award this year</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>No condition on price, quantity, quality, delivery or FOB terms; the extension is corrected under 4.1 on the Extensions tab</t>
-  </si>
-  <si>
-    <t>Prices firm for twelve months, with a raw material surcharge on the unit prices should the Pulp and Paper Week 42 lb kraft linerboard index rise more than 6 percent from award; the form boxes read Yes and None</t>
-  </si>
-  <si>
-    <t>Price hold, section 4.3</t>
-  </si>
-  <si>
-    <t>section 4.3 makes a bid that conditions its prices on an index an exception to a material term; section 5.2; PP-3.4.4</t>
-  </si>
-  <si>
-    <t>None; prices hold through December 31, 2027, which runs past twelve months from any award this year</t>
-  </si>
-  <si>
     <t>The hold meets section 4.3; the item 2 description is tested on the Responsiveness tab under PP-3.4.5</t>
   </si>
   <si>
@@ -674,21 +674,18 @@
     <t>A fee tied to the release quantity changes the price of the releases that section 1 provides for, which makes it an exception to the quantity term under section 5.2 and PP-3.4.4. The letter of October 8 reached the office after the due time, section 3.4</t>
   </si>
   <si>
-    <t>Alternate for item 4 at 200 lb test doublewall, $1.512 per carton, beside the bid on the item as specified; the form is signed by a regional sales manager where 3.3 asks for an officer</t>
+    <t>Alternate for item 4 at 200 lb test doublewall, $1.512 per carton, beside the bid on the item as specified. The form is signed by a regional sales manager where 3.3 asks for an officer. The envelope of October 2 is modified by the facsimile of October 6</t>
   </si>
   <si>
     <t>None; an alternate under section 4.4; an informality on the signature</t>
   </si>
   <si>
-    <t>section 4.4; the alternate is not evaluated for award. The signature is an informality that does not affect price, quantity, quality or delivery, waived under 5.7 and PP-3.4.4 and recorded on the Responsiveness tab</t>
+    <t>section 4.4; the alternate is not evaluated for award. The signature is an informality that does not affect price, quantity, quality or delivery, waived under 5.7 and PP-3.4.4 and recorded on the Responsiveness tab. The facsimile changes the bid without changing its receipt time, section 3.4</t>
   </si>
   <si>
     <t>None; FOB origin, the office in Cedar Rapids, items 1 to 4 shipped from the Omaha plant and item 5 from the Cedar Rapids plant; tooling credited back if the award arrives by October 30; a cashier's check of $4,554.95</t>
   </si>
   <si>
-    <t>FOB terms as permitted by 3.3</t>
-  </si>
-  <si>
     <t>FOB origin is permitted by 3.3, with freight added under section 5.4 for the plant that ships each item. The tooling credit is not an adjustment the invitation names, so tooling is added in full under 4.2 and PP-3.4.3. The check is tested on the Bid Security tab</t>
   </si>
   <si>
@@ -740,7 +737,7 @@
     <t>EFFECT_ON_THE_EVALUATION</t>
   </si>
   <si>
-    <t>Letter withdrawing the bid delivered October 2</t>
+    <t>Letter withdrawing the bid delivered October 1</t>
   </si>
   <si>
     <t>10/05/2026</t>
@@ -752,7 +749,7 @@
     <t>15:52</t>
   </si>
   <si>
-    <t>Bid withdrawn and resubmitted; the bid opened is the one received October 6 at 08:15, section 3.4</t>
+    <t>Bid withdrawn and resubmitted; the bid opened is the one received October 6 at 09:52, section 3.4</t>
   </si>
   <si>
     <t>Facsimile changing the five unit prices</t>
@@ -779,216 +776,216 @@
     <t>09:12</t>
   </si>
   <si>
-    <t>Applied; item 1 is evaluated at 0.578, and the bid keeps its receipt time, section 3.4</t>
-  </si>
-  <si>
-    <t>Telephone message asking that item 1 be read at 0.594</t>
+    <t>Applied; item 1 is evaluated at 0.578, and the bid keeps its receipt time of October 2 at 10:26, section 3.4</t>
+  </si>
+  <si>
+    <t>Telephone message asking that item 1 be read at 0.548</t>
+  </si>
+  <si>
+    <t>R-1057</t>
+  </si>
+  <si>
+    <t>09:56</t>
+  </si>
+  <si>
+    <t>Not considered; a modification is a signed writing, section 3.4; item 1 stands at 0.551 on the signed form</t>
+  </si>
+  <si>
+    <t>Letter withdrawing the delivery-efficiency fee</t>
+  </si>
+  <si>
+    <t>10/08/2026</t>
+  </si>
+  <si>
+    <t>R-1062</t>
+  </si>
+  <si>
+    <t>10/09/2026</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>Not considered; the exception in the bid stands, section 3.4 and PP-3.4.4</t>
+  </si>
+  <si>
+    <t>Letter on the edge crush complaint, hold QH-26-031</t>
+  </si>
+  <si>
+    <t>10/12/2026</t>
+  </si>
+  <si>
+    <t>R-1063</t>
+  </si>
+  <si>
+    <t>16:44</t>
+  </si>
+  <si>
+    <t>Not a change to the bid; the hold is cleared only by quality engineering, PP-3.7.1</t>
+  </si>
+  <si>
+    <t>UNIT_AS_BID</t>
+  </si>
+  <si>
+    <t>UNIT_AS_CHANGED</t>
+  </si>
+  <si>
+    <t>WRITING_ROW</t>
+  </si>
+  <si>
+    <t>APPLIED</t>
+  </si>
+  <si>
+    <t>CHANGE_IN_EXTENSION</t>
+  </si>
+  <si>
+    <t>Unit price changes applied</t>
+  </si>
+  <si>
+    <t>Unit price changes not considered</t>
+  </si>
+  <si>
+    <t>A modification counts when it is a signed writing that reaches the purchasing office before 10:00 on October 6, whatever date it carries, section 3.4. The Wenzel &amp; Krause facsimile is dated October 5 and came off the machine at 10:07 on October 6. The telephone message from Dahlgren at 09:56 is not a writing. The log enters the facsimiles and the message under the names of the people who sent them.</t>
+  </si>
+  <si>
+    <t>Bid security against five percent of the total bid as written, section 3.2 and addendum 2</t>
+  </si>
+  <si>
+    <t>AMOUNT_STATED</t>
+  </si>
+  <si>
+    <t>TOTAL_BID_AS_WRITTEN</t>
+  </si>
+  <si>
+    <t>FIVE_PERCENT_REQUIRED</t>
+  </si>
+  <si>
+    <t>SHORT_BY</t>
+  </si>
+  <si>
+    <t>MEETS_SECTION_3.2</t>
+  </si>
+  <si>
+    <t>A surety bond is written at five percent of the total bid and meets section 3.2 at any total. A cashier's check is a fixed amount and is tested against five percent of the total bid as written, tooling included, per addendum 2. Ridgecrest's check is five percent of its extensions alone and falls $120.00 short of five percent of its total bid as written.</t>
+  </si>
+  <si>
+    <t>When each bid that was opened reached the purchasing office, from bid_receipt_log_itb_2026_17.xlsx</t>
+  </si>
+  <si>
+    <t>NAME_IN_THE_LOG</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>Brannock Box</t>
+  </si>
+  <si>
+    <t>R-1049</t>
+  </si>
+  <si>
+    <t>16:02</t>
+  </si>
+  <si>
+    <t>C. Hennen</t>
   </si>
   <si>
     <t>R-1056</t>
   </si>
   <si>
-    <t>09:38</t>
-  </si>
-  <si>
-    <t>Not considered; a modification is a signed writing, section 3.4; item 1 stands at 0.597 on the signed form</t>
-  </si>
-  <si>
-    <t>Letter withdrawing the delivery-efficiency fee</t>
-  </si>
-  <si>
-    <t>10/08/2026</t>
-  </si>
-  <si>
-    <t>R-1062</t>
-  </si>
-  <si>
-    <t>10/09/2026</t>
-  </si>
-  <si>
-    <t>11:46</t>
-  </si>
-  <si>
-    <t>Not considered; the exception in the bid stands, section 3.4 and PP-3.4.4</t>
-  </si>
-  <si>
-    <t>Letter on the edge crush complaint, hold QH-26-031</t>
-  </si>
-  <si>
-    <t>10/12/2026</t>
-  </si>
-  <si>
-    <t>R-1063</t>
-  </si>
-  <si>
-    <t>16:44</t>
-  </si>
-  <si>
-    <t>Not a change to the bid; the hold is cleared only by quality engineering, PP-3.7.1</t>
-  </si>
-  <si>
-    <t>UNIT_AS_BID</t>
-  </si>
-  <si>
-    <t>UNIT_AS_CHANGED</t>
-  </si>
-  <si>
-    <t>WRITING_ROW</t>
-  </si>
-  <si>
-    <t>APPLIED</t>
-  </si>
-  <si>
-    <t>CHANGE_IN_EXTENSION</t>
-  </si>
-  <si>
-    <t>Unit price changes applied</t>
-  </si>
-  <si>
-    <t>Unit price changes not considered</t>
-  </si>
-  <si>
-    <t>A modification counts when it is a signed writing that reaches the purchasing office before 10:00 on October 6, whatever date it carries, section 3.4. The Wenzel &amp; Krause facsimile is dated October 5 and came off the machine at 10:07 on October 6. The telephone message from Dahlgren at 09:38 is not a writing. The log enters the facsimiles and the message under the names of the people who sent them.</t>
-  </si>
-  <si>
-    <t>Bid security against five percent of the total bid as written, section 3.2 and addendum 2</t>
-  </si>
-  <si>
-    <t>AMOUNT_STATED</t>
-  </si>
-  <si>
-    <t>TOTAL_BID_AS_WRITTEN</t>
-  </si>
-  <si>
-    <t>FIVE_PERCENT_REQUIRED</t>
-  </si>
-  <si>
-    <t>SHORT_BY</t>
-  </si>
-  <si>
-    <t>MEETS_SECTION_3.2</t>
-  </si>
-  <si>
-    <t>A surety bond is written at five percent of the total bid and meets section 3.2 at any total. A cashier's check is a fixed amount and is tested against five percent of the total bid as written, tooling included, per addendum 2. Ridgecrest's check is five percent of its extensions alone and falls $120.00 short of five percent of its total bid as written.</t>
-  </si>
-  <si>
-    <t>When each bid that was opened reached the purchasing office, from bid_receipt_log_itb_2026_17.xlsx</t>
-  </si>
-  <si>
-    <t>NAME_IN_THE_LOG</t>
-  </si>
-  <si>
-    <t>NOTE</t>
-  </si>
-  <si>
-    <t>Brannock Box</t>
-  </si>
-  <si>
-    <t>R-1049</t>
-  </si>
-  <si>
-    <t>16:02</t>
-  </si>
-  <si>
-    <t>Dahlgren Box, St. Cloud</t>
+    <t>09:52</t>
+  </si>
+  <si>
+    <t>The envelope logged R-1040 on 10/01/2026 was withdrawn and handed back under R-1048; the bid opened is the resubmitted one, received when it reached the office, section 3.4</t>
+  </si>
+  <si>
+    <t>Halvard</t>
+  </si>
+  <si>
+    <t>R-1058</t>
+  </si>
+  <si>
+    <t>09:58</t>
+  </si>
+  <si>
+    <t>Kessel Container, Des Moines</t>
+  </si>
+  <si>
+    <t>R-1041</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>09:47</t>
+  </si>
+  <si>
+    <t>Loken &amp; Vik</t>
+  </si>
+  <si>
+    <t>R-1059</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>Handed over at 10:00, the due time; a bid is due by 10:00 and only a bid received after that time goes back unopened, section 3.1</t>
+  </si>
+  <si>
+    <t>Mesabi Container, Duluth</t>
+  </si>
+  <si>
+    <t>R-1052</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>Otter Tail Corr.</t>
+  </si>
+  <si>
+    <t>R-1051</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>Pemberton, Neenah</t>
+  </si>
+  <si>
+    <t>R-1042</t>
+  </si>
+  <si>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>The facsimile of October 6 changes the bid and leaves this receipt time, section 3.4</t>
+  </si>
+  <si>
+    <t>Ridgecrest Pkg, Cedar Rapids</t>
+  </si>
+  <si>
+    <t>R-1050</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>Thorsgard, Moorhead</t>
+  </si>
+  <si>
+    <t>R-1054</t>
+  </si>
+  <si>
+    <t>09:27</t>
+  </si>
+  <si>
+    <t>W &amp; K Corrugated, La Crosse</t>
   </si>
   <si>
     <t>R-1055</t>
   </si>
   <si>
-    <t>09:33</t>
-  </si>
-  <si>
-    <t>Halvard</t>
-  </si>
-  <si>
-    <t>R-1058</t>
-  </si>
-  <si>
-    <t>09:58</t>
-  </si>
-  <si>
-    <t>Kessel Container, Des Moines</t>
-  </si>
-  <si>
-    <t>R-1040</t>
-  </si>
-  <si>
-    <t>10/02/2026</t>
-  </si>
-  <si>
-    <t>09:47</t>
-  </si>
-  <si>
-    <t>Loken &amp; Vik</t>
-  </si>
-  <si>
-    <t>R-1059</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>Handed over at 10:00, the due time; a bid is due by 10:00 and only a bid received after that time goes back unopened, section 3.1</t>
-  </si>
-  <si>
-    <t>Mesabi Container, Duluth</t>
-  </si>
-  <si>
-    <t>R-1052</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>Otter Tail Corr.</t>
-  </si>
-  <si>
-    <t>R-1051</t>
-  </si>
-  <si>
-    <t>08:52</t>
-  </si>
-  <si>
-    <t>Pemberton, Neenah</t>
-  </si>
-  <si>
-    <t>R-1047</t>
-  </si>
-  <si>
-    <t>11:37</t>
-  </si>
-  <si>
-    <t>The facsimile of October 6 changes the bid and leaves this receipt time, section 3.4</t>
-  </si>
-  <si>
-    <t>A. Delaney</t>
-  </si>
-  <si>
-    <t>R-1050</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>The envelope logged R-1041 on 10/02/2026 was withdrawn and handed back under R-1048; the bid opened is the resubmitted one, section 3.4</t>
-  </si>
-  <si>
-    <t>Thorsgard, Moorhead</t>
-  </si>
-  <si>
-    <t>R-1054</t>
-  </si>
-  <si>
-    <t>09:27</t>
-  </si>
-  <si>
-    <t>W &amp; K Corrugated, La Crosse</t>
-  </si>
-  <si>
-    <t>R-1057</t>
-  </si>
-  <si>
     <t>09:41</t>
   </si>
   <si>
@@ -1079,7 +1076,7 @@
     <t>Open</t>
   </si>
   <si>
-    <t>None recorded; quality engineering e-mail of October 20: verification lot received October 16 and passed, clearance not yet signed by the quality manager</t>
+    <t>None recorded; quality engineering e-mail of October 20: verification lot received October 16 and passed, clearance to be signed at the monthly review on October 28</t>
   </si>
   <si>
     <t>4700 North Cliff Avenue, Sioux Falls, SD</t>
@@ -1097,10 +1094,10 @@
     <t>10/15/2026</t>
   </si>
   <si>
-    <t>Quality engineering clearance notice of October 15</t>
-  </si>
-  <si>
-    <t>The register carries Loken &amp; Vik Container under the trade name L&amp;V Container Corp., Sioux Falls, at 4700 North Cliff Avenue, the address on its bid form. Loken Container Supply, Sioux City, Iowa, on an open hold at 2100 Dace Avenue, is a different company. PP-3.7.1 clears a hold on quality engineering's clearance, and the e-mail of October 20 says the clearance of QH-26-031 is unsigned although the verification lot passed on October 16, so the hold is open at the date of this recommendation.</t>
+    <t>Clearance notice of October 15 for verification lot P-26-1009 at the Neenah plant, the lot the register note names for this hold</t>
+  </si>
+  <si>
+    <t>The register carries Loken &amp; Vik Container under the trade name L&amp;V Container Corp., Sioux Falls, at 4700 North Cliff Avenue, the address on its bid form. Loken Container Supply, Sioux City, Iowa, on an open hold at 2100 Dace Avenue, is a different company, and so is Pemberton Fibre Products, Green Bay, on open hold QH-26-029 at 1200 Lime Kiln Road. The clearance notice of October 15 names only verification lot P-26-1009 and the Neenah plant; the register note on QH-26-034 names that lot, so the notice clears QH-26-034. The e-mail of October 20 says the clearance of QH-26-031 is to be signed at the review of October 28, after the date of this recommendation, so that hold is open.</t>
   </si>
   <si>
     <t>Freight on the FOB origin bid under 5.4: current item weights, the plant that ships each item, and the schedule rate for that plant's state</t>
@@ -1157,19 +1154,31 @@
     <t>Cedar Rapids</t>
   </si>
   <si>
+    <t>Eau Claire</t>
+  </si>
+  <si>
     <t>Freight on the Ridgecrest bid</t>
   </si>
   <si>
     <t>Freight on the Mesabi bid</t>
   </si>
   <si>
-    <t>Hundredweight from Cedar Rapids, Iowa</t>
-  </si>
-  <si>
-    <t>Hundredweight from Omaha, Nebraska</t>
-  </si>
-  <si>
-    <t>Hundredweight from Duluth, Minnesota</t>
+    <t>Freight on the Dahlgren bid</t>
+  </si>
+  <si>
+    <t>Hundredweight, Ridgecrest, from Omaha, Nebraska</t>
+  </si>
+  <si>
+    <t>Hundredweight, Ridgecrest, from Cedar Rapids, Iowa</t>
+  </si>
+  <si>
+    <t>Hundredweight, Mesabi, from Duluth, Minnesota</t>
+  </si>
+  <si>
+    <t>Hundredweight, Dahlgren, from St. Cloud, Minnesota</t>
+  </si>
+  <si>
+    <t>Hundredweight, Dahlgren, from Eau Claire, Wisconsin</t>
   </si>
   <si>
     <t>Freight for a bid offered FOB origin is each item's hundredweight at the rate for the state of the plant that ships it, per section 5.4; no truckload allowance applies, per addendum 2.</t>
@@ -1178,7 +1187,7 @@
     <t>Item 2 is weighed at drawing NM-CTN-26-02 revision B and item 5 at NM-CTN-26-05 revision B, the revisions addenda 1 and 2 put in place; revision A of each, at 0.61 lb and 1.40 lb, is superseded.</t>
   </si>
   <si>
-    <t>Ridgecrest's office is in Cedar Rapids, and its letter ships items 1 to 4 from its Omaha plant and item 5 from its Cedar Rapids plant, so 1,072 hundredweight is rated at the Nebraska rate and 396 hundredweight at the Iowa rate. Mesabi ships all five items from Duluth, so its 1,468 hundredweight is rated at the Minnesota rate.</t>
+    <t>Ridgecrest's office is in Cedar Rapids, and its letter ships items 1 to 4 from its Omaha plant and item 5 from its Cedar Rapids plant, so 1,072 hundredweight is rated at the Nebraska rate and 396 hundredweight at the Iowa rate. Mesabi ships all five items from Duluth, so its 1,468 hundredweight is rated at the Minnesota rate. Dahlgren ships items 1 to 3 from St. Cloud and items 4 and 5 from Eau Claire, so 838 hundredweight is rated at the Minnesota rate and 630 hundredweight at the Wisconsin rate.</t>
   </si>
   <si>
     <t>Responsiveness of each bid under section 3.2, section 4.3, section 4.4, section 5.2 and PP-3.4, decided before price</t>
@@ -1400,37 +1409,37 @@
     <t>Torsten, this is the evaluation of the eleven bids on ITB 2026-17 opened on October 6. The recommendation on the first tab reads from the tabs behind it, and nothing on it is typed in, so a protest can be answered from the workbook.</t>
   </si>
   <si>
-    <t>The recommendation is award of the lot to Pemberton Container of Neenah at a total evaluated price of $100,079.00. Three of the eleven bids are responsive, and one of the three is passed over. The award value is over one hundred thousand dollars, so PP-3.5.3 places the approval with you as vice president of operations. It sits $79.00 over the line: tooling of $1,850.00 is added in full under 4.2, and Pemberton's 2 percent discount carries a ten day period, under the twenty day floor in section 5.5, so it is not credited. Either reading taken the other way would put the award under the line and with the director of supply chain, and both would be wrong.</t>
-  </si>
-  <si>
-    <t>Pemberton is not the lowest evaluated price among the bids left in line. Dahlgren Paper Box evaluates at $100,026.33, which is $52.67 lower. The two bids are within $100 of each other, and 5.6 gives the award to the bid received first. Pemberton's envelope was logged at 11:37 on October 5, and Dahlgren's at 09:33 on October 6. Dahlgren's form extends item 2 at $25,900.00, which is not 64,000 cartons at $0.400; the extension is $25,600.00, and 4.1 has the unit price govern. The desk log records a telephone message from Dahlgren at 09:38 on October 6 asking that item 1 be read at 0.594; section 3.4 changes a bid only by a signed writing, so item 1 stands at the $0.597 on the form. Read at 0.594, Dahlgren would have been more than $100 below Pemberton and first in line, and it will ask.</t>
+    <t>The recommendation is award of the lot to Pemberton Container of Neenah at a total evaluated price of $99,761.99. Three of the eleven bids are responsive, and one of the three is passed over. The award value is under one hundred thousand dollars, so PP-3.5.3 places the approval with the director of supply chain and not with you. It is under the line only because Pemberton's 1 percent, twenty day discount is credited at $989.01 under section 5.5; before the credit the price is $100,750.99 and would have been yours to approve. I have set the signature line for the director, and you will want to pass the page on.</t>
+  </si>
+  <si>
+    <t>Pemberton is not the lowest evaluated price among the bids left in line. Dahlgren Paper Box evaluates at $99,700.20, which is $61.79 lower. The two bids are within $100 of each other, and 5.6 gives the award to the bid received first. Pemberton's envelope was logged at 10:26 on October 2; its facsimile of October 6 changed one unit price and, under section 3.4, left that receipt time where it was. Dahlgren delivered an envelope on October 1, withdrew it by letter on October 5 and delivered a new one at 09:52 on October 6, and section 3.4 times a resubmitted bid from the resubmission. Dahlgren's form extends item 2 at $24,044.00, which is not 64,000 cartons at $0.371; the extension is $23,744.00, and 4.1 has the unit price govern. The desk log records a telephone message from Dahlgren at 09:56 on October 6 asking that item 1 be read at 0.548; a modification is a signed writing, so item 1 stands at the $0.551 on the form. Its 2 percent discount has a ten day period, under the twenty day floor, and is not credited.</t>
+  </si>
+  <si>
+    <t>Dahlgren's prices are FOB origin from two plants. Its letter makes items 1 to 3 at St. Cloud and items 4 and 5 at Eau Claire, so section 5.4 rates 838 hundredweight at the Minnesota rate of $3.40 and 630 hundredweight at the Wisconsin rate of $5.10, which is $6,062.20 at the current drawing revisions, item 2 at 0.55 pounds under revision B and item 5 at 1.65 pounds. Rated at the superseded weights, or wholly at one plant's rate, Dahlgren would stand more than $100 clear of Pemberton and 5.6 would not reach the order.</t>
   </si>
   <si>
     <t>Pemberton's form is signed by a regional sales manager where 3.3 asks for an officer of the bidder. That affects none of price, quantity, quality or delivery, so I have waived it as an informality under 5.7 and recorded the waiver on the responsiveness tab, as PP-3.4.4 provides.</t>
   </si>
   <si>
-    <t>Loken &amp; Vik Container of Sioux Falls is responsive and has the lowest total evaluated price at $99,230.72, which is $848.28 below Pemberton. Its envelope was handed over at 10:00 on October 6, the minute the bids were due, and section 3.1 makes a bid due by 10:00 and returns only a bid received after that time. It is passed over because hold QH-26-031 is open, and PP-3.7.1 makes a bidder on an open hold not responsible until quality engineering has cleared it. The register carries the hold under the trade name L&amp;V Container Corp., Sioux Falls, at 4700 North Cliff Avenue, the address on the bid form; the open hold on Loken Container Supply of Sioux City, Iowa, is a different company. Quality engineering's e-mail of October 20 reports that the verification lot passed on October 16 and that the quality manager has not signed the clearance, which is what clears a hold. Whether to hold the award until that signature is in the file is a matter to weigh, and the evaluation does not decide it. The current carton contract ends at the end of the month.</t>
-  </si>
-  <si>
-    <t>Pemberton's own hold QH-26-034 was open in the register extract of October 7. Quality engineering cleared it on October 15 after the verification lot passed, so Pemberton is responsible at the date of this recommendation.</t>
-  </si>
-  <si>
-    <t>Pemberton's price rests on two readings of its bid. Its form extends item 2 at $26,912.00, which is not 64,000 cartons at $0.408; the extension is $26,112.00. Its facsimile changing the item 1 unit price from $0.602 to $0.578 was logged at 09:12 on October 6, before the due time, so section 3.4 applies it. Corrected, the extensions sum to $98,229.00, with $1,850.00 of tooling and no freight.</t>
+    <t>Loken &amp; Vik Container of Sioux Falls is responsive and has the lowest total evaluated price at $99,230.72, which is $531.27 below Pemberton. Its envelope was handed over at 10:00 on October 6, the minute the bids were due, and section 3.1 makes a bid due by 10:00 and returns only a bid received after that time. It is passed over because hold QH-26-031 is open, and PP-3.7.1 makes a bidder on an open hold not responsible until quality engineering has cleared it. The register carries the hold under the trade name L&amp;V Container Corp., Sioux Falls, at 4700 North Cliff Avenue, the address on the bid form; the open hold on Loken Container Supply of Sioux City, Iowa, is a different company. Quality engineering's e-mail of October 20 reports that the verification lot passed on October 16 and that the clearance is to be signed at the monthly review on October 28, after the date of this recommendation. Whether to hold the award until that signature is in the file is a matter to weigh, and the evaluation does not decide it. The current carton contract ends at the end of the month.</t>
+  </si>
+  <si>
+    <t>Pemberton's own hold QH-26-034 was open in the register extract of October 7, with the register note naming verification lot P-26-1009 as due from Neenah. The clearance notice of October 15 names only that lot and the Neenah plant; it does not name the supplier or the hold, and the open hold on Pemberton Fibre Products of Green Bay is a different company with a different lot. The lot and plant match QH-26-034, so Pemberton is responsible at the date of this recommendation.</t>
+  </si>
+  <si>
+    <t>Pemberton's price rests on two readings of its bid. Its form extends item 2 at $26,912.00, which is not 64,000 cartons at $0.408; the extension is $26,112.00. Its facsimile changing the item 1 unit price from $0.602 to $0.578 was logged at 09:12 on October 6, before the due time, so section 3.4 applies it. Corrected, the extensions sum to $98,901.00, with $1,850.00 of tooling and no freight.</t>
   </si>
   <si>
     <t>Ridgecrest is the low bid on paper at $93,499.00 and is set aside on its bid security. Its cashier's check is $4,554.95, five percent of its extensions, and five percent of its total bid as written of $93,499.00 is $4,674.95, so the check is $120.00 short. Addendum 2 treats a bid with less than five percent as a bid without security. For the record, its prices are FOB origin: its office is in Cedar Rapids, its letter ships items 1 to 4 from its Omaha plant and item 5 from its Cedar Rapids plant, and section 5.4 rates 1,072 hundredweight at the Nebraska rate of $5.35 and 396 hundredweight at the Iowa rate of $4.87, which is $7,663.72. With its discount credited at $910.99 and tooling of $2,400.00 added in full, it would have evaluated at $100,251.73. The tabulation keys its item 4 unit price as 1.557, and the signed form reads 1.575.</t>
   </si>
   <si>
-    <t>Mesabi Container Co. of Duluth is set aside on item 4. Its form prices item 4 on 200 lb test doublewall as an alternate and carries no price for the 275 lb test board as specified, and its letter says the Duluth plant does not run that board. Section 4.4 and the answer in addendum 2 allow an alternate only alongside a bid on the item as specified, and 5.2 makes a bid responsive only where it offers every item as specified. Its prices are FOB origin from one plant, so freight of $4,991.20 on 1,468 hundredweight at the Minnesota rate is shown for the record, and it would have evaluated at $98,963.18, the lowest figure in the file.</t>
-  </si>
-  <si>
-    <t>Brannock Box Company is set aside. Its form acknowledges addendum 1 only, prices item 3 at the superseded 36,000 cartons, and describes item 5 on 32 ECT board. Its figures are shown for the record and do not compete.</t>
-  </si>
-  <si>
-    <t>Kessel Container Corp. is set aside under PP-3.4.5. Its form acknowledges both addenda and describes item 2 as 18 x 12 x 12, the size that addendum 1 replaced with 18 x 12 x 10, so it is a bid on a superseded specification. It would have evaluated at $98,895.24.</t>
-  </si>
-  <si>
-    <t>Halvard Corrugated and Thorsgard Box &amp; Label are set aside for exceptions to the price hold, a material term. Halvard's letter holds prices for twelve months and then adds a raw material surcharge whenever a linerboard index rises more than 6 percent, which conditions the prices on an index, and section 4.3 makes that an exception. Thorsgard's form marks the twelve months Yes, and its letter holds prices firm through September 30, 2027, which is short of twelve months from any award made after the opening. They would have evaluated at $98,627.84 and $98,883.64.</t>
+    <t>Mesabi Container Co. of Duluth is set aside on item 4. Its form prices item 4 on 200 lb test doublewall as an alternate and carries no price for the 275 lb test board as specified, and its letter says the Duluth plant does not run that board. Section 4.4 and the answer in addendum 2 allow an alternate only alongside a bid on the item as specified, and 5.2 makes a bid responsive only where it offers every item as specified. Its prices are FOB origin from one plant, so freight of $4,991.20 on 1,468 hundredweight at the Minnesota rate is shown for the record, and it would have evaluated at $98,963.18.</t>
+  </si>
+  <si>
+    <t>Thorsgard Box &amp; Label would have been the lowest responsive price at $98,883.64 and is set aside. Its form marks the twelve months Yes, and its letter holds prices firm through September 30, 2027, which is short of twelve months from any award made after the opening, an exception to the price hold under 4.3. Halvard Corrugated is set aside on the same term: its letter holds prices for twelve months and then adds a raw material surcharge whenever a linerboard index rises more than 6 percent, which conditions the prices on an index. It would have evaluated at $98,627.84.</t>
+  </si>
+  <si>
+    <t>Kessel Container Corp. is set aside under PP-3.4.5. Its form acknowledges both addenda and describes item 2 as 18 x 12 x 12, the size that addendum 1 replaced with 18 x 12 x 10, so it is a bid on a superseded specification. It would have evaluated at $98,895.24. Brannock Box Company is set aside on the same policy: its form acknowledges addendum 1 only, prices item 3 at the superseded 36,000 cartons, and describes item 5 on 32 ECT board. Its figures are shown for the record and do not compete.</t>
   </si>
   <si>
     <t>Otter Tail Corrugated is set aside for a delivery-efficiency fee of $185 on any release under 20 pallets. Section 1 places releases monthly in pallet multiples at the quantities the schedule requires, quantity is a material term under 5.2, and a fee that turns on the release quantity changes the price of those releases. Its letter of October 8 withdrawing the fee reached the office after the due time, and PP-3.4.4 does not let the buyer negotiate an exception away before award. It would have evaluated at $99,567.00.</t>
@@ -1442,7 +1451,7 @@
     <t>Two other things to weigh that the evaluation does not decide. First, Pemberton offered an alternate for item 4 at 200 lb test doublewall for $1.512 a carton against $1.704 as specified. Section 4.4 keeps it out of the evaluation, and it can be taken up after award if engineering accepts the lighter board. Second, the award rests on the recomputation of one extension, and Pemberton has not been asked to confirm the unit price. That confirmation belongs in the file before the notice goes out.</t>
   </si>
   <si>
-    <t>For the bidder that was low on paper: tell Ridgecrest that its cashier's check was five percent of its extensions and not of its total bid as written, which addendum 2 treats as a bid without security, and that its freight under section 5.4 would in any case have placed it above the award. Tell Dahlgren that a price change by telephone is not a modification under section 3.4 and that 5.6 gave the award to a bid within $100 that was received first. Tell Mesabi that the invitation asked for a price on item 4 as specified. Tell Loken &amp; Vik that its bid was responsive and lowest in evaluated price and was passed over under PP-3.7.1 for the open hold. Under PP-3.6.1 the unsuccessful bidders are notified in writing within five business days of award, and a debriefing is limited to the bidder's own bid.</t>
+    <t>For the bidder that was low on paper: tell Ridgecrest that its cashier's check was five percent of its extensions and not of its total bid as written, which addendum 2 treats as a bid without security, and that its freight under section 5.4 would in any case have placed it above the award. Tell Dahlgren that a price change by telephone is not a modification under section 3.4, that a resubmitted bid is received when the new envelope arrives, and that 5.6 gave the award to a bid within $100 that was received first. Tell Mesabi that the invitation asked for a price on item 4 as specified. Tell Loken &amp; Vik that its bid was responsive and lowest in evaluated price and was passed over under PP-3.7.1 for the open hold. Under PP-3.6.1 the unsuccessful bidders are notified in writing within five business days of award, and a debriefing is limited to the bidder's own bid.</t>
   </si>
 </sst>
 </file>
@@ -2111,7 +2120,7 @@
       </c>
       <c r="C9" s="5">
         <f>Evaluation!C22</f>
-        <v>101317</v>
+        <v>93938</v>
       </c>
       <c r="D9" s="5">
         <f>Evaluation!D22</f>
@@ -2135,7 +2144,7 @@
       </c>
       <c r="I9" s="5">
         <f>Evaluation!I22</f>
-        <v>101959</v>
+        <v>102631</v>
       </c>
       <c r="J9" s="5">
         <f>Evaluation!J22</f>
@@ -2163,7 +2172,7 @@
       </c>
       <c r="C10" s="5">
         <f>Evaluation!C14</f>
-        <v>99067</v>
+        <v>91688</v>
       </c>
       <c r="D10" s="5">
         <f>Evaluation!D14</f>
@@ -2187,7 +2196,7 @@
       </c>
       <c r="I10" s="5">
         <f>Evaluation!I14</f>
-        <v>98229</v>
+        <v>98901</v>
       </c>
       <c r="J10" s="5">
         <f>Evaluation!J14</f>
@@ -2267,7 +2276,7 @@
       </c>
       <c r="C12" s="5">
         <f>Evaluation!C17</f>
-        <v>0</v>
+        <v>6062.2</v>
       </c>
       <c r="D12" s="5">
         <f>Evaluation!D17</f>
@@ -2319,7 +2328,7 @@
       </c>
       <c r="C13" s="5">
         <f>Evaluation!C20</f>
-        <v>990.67</v>
+        <v>0</v>
       </c>
       <c r="D13" s="5">
         <f>Evaluation!D20</f>
@@ -2343,7 +2352,7 @@
       </c>
       <c r="I13" s="5">
         <f>Evaluation!I20</f>
-        <v>0</v>
+        <v>989.01</v>
       </c>
       <c r="J13" s="5">
         <f>Evaluation!J20</f>
@@ -2371,7 +2380,7 @@
       </c>
       <c r="C14" s="5">
         <f>Evaluation!C21</f>
-        <v>100026.33</v>
+        <v>99700.2</v>
       </c>
       <c r="D14" s="5">
         <f>Evaluation!D21</f>
@@ -2395,7 +2404,7 @@
       </c>
       <c r="I14" s="5">
         <f>Evaluation!I21</f>
-        <v>100079</v>
+        <v>99761.99</v>
       </c>
       <c r="J14" s="5">
         <f>Evaluation!J21</f>
@@ -2475,7 +2484,7 @@
       </c>
       <c r="C16" s="4" t="str">
         <f>INDEX('Bid Receipt'!$D$4:$D$14,2)&amp;" "&amp;INDEX('Bid Receipt'!$E$4:$E$14,2)</f>
-        <v>10/06/2026 09:33</v>
+        <v>10/06/2026 09:52</v>
       </c>
       <c r="D16" s="4" t="str">
         <f>INDEX('Bid Receipt'!$D$4:$D$14,3)&amp;" "&amp;INDEX('Bid Receipt'!$E$4:$E$14,3)</f>
@@ -2499,7 +2508,7 @@
       </c>
       <c r="I16" s="4" t="str">
         <f>INDEX('Bid Receipt'!$D$4:$D$14,8)&amp;" "&amp;INDEX('Bid Receipt'!$E$4:$E$14,8)</f>
-        <v>10/05/2026 11:37</v>
+        <v>10/02/2026 10:26</v>
       </c>
       <c r="J16" s="4" t="str">
         <f>INDEX('Bid Receipt'!$D$4:$D$14,9)&amp;" "&amp;INDEX('Bid Receipt'!$E$4:$E$14,9)</f>
@@ -2540,7 +2549,7 @@
       </c>
       <c r="B20" s="7">
         <f>Responsibility!B19</f>
-        <v>100079</v>
+        <v>99761.99</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>9</v>
@@ -2552,7 +2561,7 @@
       </c>
       <c r="B21" s="2" t="str">
         <f>Evaluation!B32</f>
-        <v>Vice president of operations</v>
+        <v>Director of supply chain</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>13</v>
@@ -2576,7 +2585,7 @@
       </c>
       <c r="B23" s="7">
         <f>Responsibility!B21</f>
-        <v>100026.33</v>
+        <v>99700.2</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>9</v>
@@ -2588,7 +2597,7 @@
       </c>
       <c r="B24" s="7">
         <f>Responsibility!B22</f>
-        <v>52.67</v>
+        <v>61.79</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>9</v>
@@ -2612,7 +2621,7 @@
       </c>
       <c r="B26" s="2" t="str">
         <f>Responsibility!B24</f>
-        <v>10/05/2026 11:37</v>
+        <v>10/02/2026 10:26</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>20</v>
@@ -2624,7 +2633,7 @@
       </c>
       <c r="B27" s="2" t="str">
         <f>Responsibility!B25</f>
-        <v>10/06/2026 09:33</v>
+        <v>10/06/2026 09:52</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>20</v>
@@ -2684,7 +2693,7 @@
       </c>
       <c r="B32" s="7">
         <f>Responsibility!B28</f>
-        <v>848.28</v>
+        <v>531.27</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>9</v>
@@ -2819,7 +2828,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2837,7 +2846,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -2845,40 +2854,40 @@
         <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>364</v>
-      </c>
       <c r="N3" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -2886,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C4" s="8">
         <v>0.9</v>
@@ -2896,7 +2905,7 @@
         <v>45000</v>
       </c>
       <c r="E4" s="7">
-        <f t="shared" ref="E4:E13" si="0">ROUND(C4*D4,2)</f>
+        <f t="shared" ref="E4:E18" si="0">ROUND(C4*D4,2)</f>
         <v>40500</v>
       </c>
       <c r="F4" s="7">
@@ -2910,11 +2919,11 @@
         <v>168</v>
       </c>
       <c r="I4" s="8">
-        <f t="shared" ref="I4:I13" si="1">INDEX($N$4:$N$10,MATCH(H4,$M$4:$M$10,0))</f>
+        <f t="shared" ref="I4:I18" si="1">INDEX($N$4:$N$10,MATCH(H4,$M$4:$M$10,0))</f>
         <v>5.35</v>
       </c>
       <c r="J4" s="7">
-        <f t="shared" ref="J4:J13" si="2">ROUND(F4*I4,2)</f>
+        <f t="shared" ref="J4:J18" si="2">ROUND(F4*I4,2)</f>
         <v>2166.75</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -2932,7 +2941,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C5" s="8">
         <v>0.55</v>
@@ -2967,7 +2976,7 @@
         <v>166</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N5" s="8">
         <v>4.87</v>
@@ -2978,7 +2987,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C6" s="8">
         <v>0.3</v>
@@ -3013,7 +3022,7 @@
         <v>166</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N6" s="8">
         <v>5.1</v>
@@ -3024,7 +3033,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C7" s="8">
         <v>2.6</v>
@@ -3070,7 +3079,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C8" s="8">
         <v>1.65</v>
@@ -3088,10 +3097,10 @@
         <v>396</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I8" s="8">
         <f t="shared" si="1"/>
@@ -3105,7 +3114,7 @@
         <v>166</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N8" s="8">
         <v>4.2</v>
@@ -3116,7 +3125,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C9" s="8">
         <v>0.9</v>
@@ -3134,7 +3143,7 @@
         <v>405</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>133</v>
@@ -3148,10 +3157,10 @@
         <v>1377</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N9" s="8">
         <v>4.6</v>
@@ -3162,7 +3171,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C10" s="8">
         <v>0.55</v>
@@ -3180,7 +3189,7 @@
         <v>352</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>133</v>
@@ -3194,7 +3203,7 @@
         <v>1196.8</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>168</v>
@@ -3208,7 +3217,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C11" s="8">
         <v>0.3</v>
@@ -3226,7 +3235,7 @@
         <v>81</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>133</v>
@@ -3240,7 +3249,7 @@
         <v>275.4</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -3248,7 +3257,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C12" s="8">
         <v>2.6</v>
@@ -3266,7 +3275,7 @@
         <v>234</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>133</v>
@@ -3280,7 +3289,7 @@
         <v>795.6</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -3288,7 +3297,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C13" s="8">
         <v>1.65</v>
@@ -3306,7 +3315,7 @@
         <v>396</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>133</v>
@@ -3320,67 +3329,294 @@
         <v>1346.4</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="2">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="D14" s="2">
+        <f>Parameters!B15</f>
+        <v>45000</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" si="0"/>
+        <v>40500</v>
+      </c>
+      <c r="F14" s="7">
+        <f>ROUND(E14/Parameters!$B$8,2)</f>
+        <v>405</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4</v>
+      </c>
+      <c r="J14" s="7">
+        <f t="shared" si="2"/>
+        <v>1377</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.55</v>
+      </c>
+      <c r="D15" s="2">
+        <f>Parameters!B16</f>
+        <v>64000</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="0"/>
+        <v>35200</v>
+      </c>
+      <c r="F15" s="7">
+        <f>ROUND(E15/Parameters!$B$8,2)</f>
+        <v>352</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="2"/>
+        <v>1196.8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>3</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="D16" s="2">
+        <f>Parameters!B17</f>
+        <v>27000</v>
+      </c>
+      <c r="E16" s="7">
+        <f t="shared" si="0"/>
+        <v>8100</v>
+      </c>
+      <c r="F16" s="7">
+        <f>ROUND(E16/Parameters!$B$8,2)</f>
+        <v>81</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4</v>
+      </c>
+      <c r="J16" s="7">
+        <f t="shared" si="2"/>
+        <v>275.4</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="D17" s="2">
+        <f>Parameters!B18</f>
+        <v>9000</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="0"/>
+        <v>23400</v>
+      </c>
+      <c r="F17" s="7">
+        <f>ROUND(E17/Parameters!$B$8,2)</f>
+        <v>234</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="1"/>
+        <v>5.1</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="2"/>
+        <v>1193.4</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C18" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="D18" s="2">
+        <f>Parameters!B19</f>
+        <v>24000</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" si="0"/>
+        <v>39600</v>
+      </c>
+      <c r="F18" s="7">
+        <f>ROUND(E18/Parameters!$B$8,2)</f>
+        <v>396</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="1"/>
+        <v>5.1</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="2"/>
+        <v>2019.6</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="J14" s="11">
-        <f>SUMIFS(J4:J13,K4:K13,"Ridgecrest Packaging")</f>
+      <c r="J19" s="11">
+        <f>SUMIFS(J4:J18,K4:K18,"Ridgecrest Packaging")</f>
         <v>7663.72</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="J15" s="11">
-        <f>SUMIFS(J4:J13,K4:K13,"Mesabi Container Co.")</f>
+      <c r="J20" s="11">
+        <f>SUMIFS(J4:J18,K4:K18,"Mesabi Container Co.")</f>
         <v>4991.2</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="F16" s="7">
-        <f>SUMIFS(F4:F13,H4:H13,"IA")</f>
+      <c r="J21" s="11">
+        <f>SUMIFS(J4:J18,K4:K18,"Dahlgren Paper Box Co.")</f>
+        <v>6062.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F22" s="7">
+        <f>SUMIFS(F4:F18,H4:H18,"NE",K4:K18,"Ridgecrest Packaging")</f>
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F23" s="7">
+        <f>SUMIFS(F4:F18,H4:H18,"IA",K4:K18,"Ridgecrest Packaging")</f>
         <v>396</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="F17" s="7">
-        <f>SUMIFS(F4:F13,H4:H13,"NE")</f>
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F18" s="7">
-        <f>SUMIFS(F4:F13,H4:H13,"MN")</f>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F24" s="7">
+        <f>SUMIFS(F4:F18,H4:H18,"MN",K4:K18,"Mesabi Container Co.")</f>
         <v>1468</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+      <c r="F25" s="7">
+        <f>SUMIFS(F4:F18,H4:H18,"MN",K4:K18,"Dahlgren Paper Box Co.")</f>
+        <v>838</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>378</v>
+      </c>
+      <c r="F26" s="7">
+        <f>SUMIFS(F4:F18,H4:H18,"WI",K4:K18,"Dahlgren Paper Box Co.")</f>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -3409,7 +3645,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -3417,40 +3653,40 @@
         <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3474,7 +3710,7 @@
         <v>No, superseded 36,000</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>127</v>
@@ -3500,7 +3736,7 @@
         <v>Addendum 2 not acknowledged, section 3.2; bid on the superseded item 3 quantity and item 5 grade, PP-3.4.5.</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3535,7 +3771,7 @@
       </c>
       <c r="I5" s="4" t="str">
         <f>'Bid Conditions'!B5</f>
-        <v>None; releases taken in any pallet quantity; the form extends item 2 at 25,900.00 against 25,600.00 at the unit price</v>
+        <v>None; FOB origin at the shipping plant, items 1 to 3 from St. Cloud and items 4 and 5 from Eau Claire; the form extends item 2 at 24,044.00 against 23,744.00 at the unit price; the first envelope of October 1 was withdrawn and handed back on October 5</v>
       </c>
       <c r="J5" s="2" t="str">
         <f>IF(ISNUMBER(SEARCH("lternate",'Bid Conditions'!B5)),"Yes, not evaluated","No")</f>
@@ -3550,7 +3786,7 @@
         <v/>
       </c>
       <c r="M5" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3600,7 +3836,7 @@
         <v>Exception to a material term, Price hold, section 4.3, section 5.2 and PP-3.4.4.</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3624,7 +3860,7 @@
         <v>Yes</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>127</v>
@@ -3650,7 +3886,7 @@
         <v>Bid on a superseded specification, item 2 as 18 x 12 x 12, PP-3.4.5.</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3700,7 +3936,7 @@
         <v/>
       </c>
       <c r="M8" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3727,7 +3963,7 @@
         <v>127</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H9" s="2" t="str">
         <f>'Bid Conditions'!D9</f>
@@ -3750,7 +3986,7 @@
         <v>Item 4 offered only as an alternate, with no bid on the item as specified, section 5.2 and 4.4.</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3800,7 +4036,7 @@
         <v>Exception to a material term, Quantity, releases in pallet multiples, section 1, section 5.2 and PP-3.4.4.</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3835,7 +4071,7 @@
       </c>
       <c r="I11" s="4" t="str">
         <f>'Bid Conditions'!B11</f>
-        <v>Alternate for item 4 at 200 lb test doublewall, $1.512 per carton, beside the bid on the item as specified; the form is signed by a regional sales manager where 3.3 asks for an officer</v>
+        <v>Alternate for item 4 at 200 lb test doublewall, $1.512 per carton, beside the bid on the item as specified. The form is signed by a regional sales manager where 3.3 asks for an officer. The envelope of October 2 is modified by the facsimile of October 6</v>
       </c>
       <c r="J11" s="2" t="str">
         <f>IF(ISNUMBER(SEARCH("lternate",'Bid Conditions'!B11)),"Yes, not evaluated","No")</f>
@@ -3850,7 +4086,7 @@
         <v/>
       </c>
       <c r="M11" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3900,7 +4136,7 @@
         <v>Bid security under five percent of the total bid as written, section 3.2 and addendum 2.</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3950,7 +4186,7 @@
         <v>Exception to a material term, Price hold, section 4.3, section 5.2 and PP-3.4.4.</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3967,7 +4203,7 @@
         <v>Yes</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E14" s="2" t="str">
         <f>IF(ROUND('Bids as Written'!X7,2)=ROUND('Bids as Written'!W7*Parameters!$B$10,2),"No, superseded 36,000","Yes")</f>
@@ -4000,7 +4236,7 @@
         <v>Sample not made to the specification as amended, item 5 sample on 32 ECT, section 3.2.</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
@@ -4023,17 +4259,17 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -4058,33 +4294,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -4130,11 +4366,11 @@
       </c>
       <c r="C5" s="7">
         <f>IF(B5="","",INDEX(Evaluation!$B$21:$L$21,MATCH(A5,Evaluation!$B$25:$L$25,0)))</f>
-        <v>100079</v>
+        <v>99761.99</v>
       </c>
       <c r="D5" s="2" t="str">
         <f>IF(B5="","",INDEX('Bid Receipt'!$D$4:$D$14,MATCH(B5,'Bid Receipt'!$A$4:$A$14,0))&amp;" "&amp;INDEX('Bid Receipt'!$E$4:$E$14,MATCH(B5,'Bid Receipt'!$A$4:$A$14,0)))</f>
-        <v>10/05/2026 11:37</v>
+        <v>10/02/2026 10:26</v>
       </c>
       <c r="E5" s="2">
         <f>IF(B5="","",COUNTIFS('Holds on Bidders'!$C$4:$C$7,B5,'Holds on Bidders'!$I$4:$I$7,"Open"))</f>
@@ -4163,11 +4399,11 @@
       </c>
       <c r="C6" s="7">
         <f>IF(B6="","",INDEX(Evaluation!$B$21:$L$21,MATCH(A6,Evaluation!$B$25:$L$25,0)))</f>
-        <v>100026.33</v>
+        <v>99700.2</v>
       </c>
       <c r="D6" s="2" t="str">
         <f>IF(B6="","",INDEX('Bid Receipt'!$D$4:$D$14,MATCH(B6,'Bid Receipt'!$A$4:$A$14,0))&amp;" "&amp;INDEX('Bid Receipt'!$E$4:$E$14,MATCH(B6,'Bid Receipt'!$A$4:$A$14,0)))</f>
-        <v>10/06/2026 09:33</v>
+        <v>10/06/2026 09:52</v>
       </c>
       <c r="E6" s="2">
         <f>IF(B6="","",COUNTIFS('Holds on Bidders'!$C$4:$C$7,B6,'Holds on Bidders'!$I$4:$I$7,"Open"))</f>
@@ -4470,7 +4706,7 @@
       </c>
       <c r="B19" s="7">
         <f>INDEX(C4:C14,MATCH("Award",F4:F14,0))</f>
-        <v>100079</v>
+        <v>99761.99</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -4488,7 +4724,7 @@
       </c>
       <c r="B21" s="7">
         <f>IFERROR(INDEX(C4:C14,MATCH("Award",F4:F14,0)+1),0)</f>
-        <v>100026.33</v>
+        <v>99700.2</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4497,7 +4733,7 @@
       </c>
       <c r="B22" s="7">
         <f>ROUND(B19-B21,2)</f>
-        <v>52.67</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4515,7 +4751,7 @@
       </c>
       <c r="B24" s="2" t="str">
         <f>INDEX(D4:D14,MATCH("Award",F4:F14,0))</f>
-        <v>10/05/2026 11:37</v>
+        <v>10/02/2026 10:26</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -4524,7 +4760,7 @@
       </c>
       <c r="B25" s="2" t="str">
         <f>IFERROR(INDEX(D4:D14,MATCH("Award",F4:F14,0)+1),"None")</f>
-        <v>10/06/2026 09:33</v>
+        <v>10/06/2026 09:52</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -4551,17 +4787,17 @@
       </c>
       <c r="B28" s="7">
         <f>ROUND(B19-B27,2)</f>
-        <v>848.28</v>
+        <v>531.27</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -4581,12 +4817,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>122</v>
@@ -4595,31 +4831,31 @@
         <v>131</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>166</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>56</v>
@@ -4627,7 +4863,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B4" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!C5)</f>
@@ -4635,7 +4871,7 @@
       </c>
       <c r="C4" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!E5)</f>
-        <v>0.597</v>
+        <v>0.551</v>
       </c>
       <c r="D4" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,1,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!G5)</f>
@@ -4674,12 +4910,12 @@
         <v>0.628</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B5" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!C6)</f>
@@ -4687,7 +4923,7 @@
       </c>
       <c r="C5" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!E6)</f>
-        <v>0.4</v>
+        <v>0.371</v>
       </c>
       <c r="D5" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,2,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!G6)</f>
@@ -4726,12 +4962,12 @@
         <v>0.428</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B6" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,3,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,3,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!C7)</f>
@@ -4739,7 +4975,7 @@
       </c>
       <c r="C6" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,3,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,3,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!E7)</f>
-        <v>0.284</v>
+        <v>0.263</v>
       </c>
       <c r="D6" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,3,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,3,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!G7)</f>
@@ -4778,12 +5014,12 @@
         <v>0.301</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B7" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!C8)</f>
@@ -4791,7 +5027,7 @@
       </c>
       <c r="C7" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!E8)</f>
-        <v>1.702</v>
+        <v>1.576</v>
       </c>
       <c r="D7" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,4,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!G8)</f>
@@ -4830,12 +5066,12 @@
         <v>1.79</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B8" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,B$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!C9)</f>
@@ -4843,7 +5079,7 @@
       </c>
       <c r="C8" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,C$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!E9)</f>
-        <v>0.984</v>
+        <v>0.911</v>
       </c>
       <c r="D8" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,D$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!G9)</f>
@@ -4867,7 +5103,7 @@
       </c>
       <c r="I8" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,I$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,I$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!Q9)</f>
-        <v>0.957</v>
+        <v>0.985</v>
       </c>
       <c r="J8" s="10">
         <f>IF(COUNTIFS('Later Writings'!$A$13:$A$19,J$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes")&gt;0,SUMIFS('Later Writings'!$D$13:$D$19,'Later Writings'!$A$13:$A$19,J$3,'Later Writings'!$B$13:$B$19,5,'Later Writings'!$F$13:$F$19,"Yes"),'Bids as Written'!S9)</f>
@@ -4882,12 +5118,12 @@
         <v>1.012</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B9" s="7">
         <f>ROUND(B4*Parameters!$B$15,2)</f>
@@ -4895,7 +5131,7 @@
       </c>
       <c r="C9" s="7">
         <f>ROUND(C4*Parameters!$B$15,2)</f>
-        <v>26865</v>
+        <v>24795</v>
       </c>
       <c r="D9" s="7">
         <f>ROUND(D4*Parameters!$B$15,2)</f>
@@ -4934,12 +5170,12 @@
         <v>28260</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B10" s="7">
         <f>ROUND(B5*Parameters!$B$16,2)</f>
@@ -4947,7 +5183,7 @@
       </c>
       <c r="C10" s="7">
         <f>ROUND(C5*Parameters!$B$16,2)</f>
-        <v>25600</v>
+        <v>23744</v>
       </c>
       <c r="D10" s="7">
         <f>ROUND(D5*Parameters!$B$16,2)</f>
@@ -4986,12 +5222,12 @@
         <v>27392</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B11" s="7">
         <f>ROUND(B6*Parameters!$B$17,2)</f>
@@ -4999,7 +5235,7 @@
       </c>
       <c r="C11" s="7">
         <f>ROUND(C6*Parameters!$B$17,2)</f>
-        <v>7668</v>
+        <v>7101</v>
       </c>
       <c r="D11" s="7">
         <f>ROUND(D6*Parameters!$B$17,2)</f>
@@ -5038,12 +5274,12 @@
         <v>8127</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B12" s="7">
         <f>ROUND(B7*Parameters!$B$18,2)</f>
@@ -5051,7 +5287,7 @@
       </c>
       <c r="C12" s="7">
         <f>ROUND(C7*Parameters!$B$18,2)</f>
-        <v>15318</v>
+        <v>14184</v>
       </c>
       <c r="D12" s="7">
         <f>ROUND(D7*Parameters!$B$18,2)</f>
@@ -5090,12 +5326,12 @@
         <v>16110</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B13" s="7">
         <f>ROUND(B8*Parameters!$B$19,2)</f>
@@ -5103,7 +5339,7 @@
       </c>
       <c r="C13" s="7">
         <f>ROUND(C8*Parameters!$B$19,2)</f>
-        <v>23616</v>
+        <v>21864</v>
       </c>
       <c r="D13" s="7">
         <f>ROUND(D8*Parameters!$B$19,2)</f>
@@ -5127,7 +5363,7 @@
       </c>
       <c r="I13" s="7">
         <f>ROUND(I8*Parameters!$B$19,2)</f>
-        <v>22968</v>
+        <v>23640</v>
       </c>
       <c r="J13" s="7">
         <f>ROUND(J8*Parameters!$B$19,2)</f>
@@ -5142,12 +5378,12 @@
         <v>24288</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B14" s="11">
         <f t="shared" ref="B14:L14" si="0">SUM(B9:B13)</f>
@@ -5155,7 +5391,7 @@
       </c>
       <c r="C14" s="11">
         <f t="shared" si="0"/>
-        <v>99067</v>
+        <v>91688</v>
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
@@ -5179,7 +5415,7 @@
       </c>
       <c r="I14" s="11">
         <f t="shared" si="0"/>
-        <v>98229</v>
+        <v>98901</v>
       </c>
       <c r="J14" s="11">
         <f t="shared" si="0"/>
@@ -5194,12 +5430,12 @@
         <v>104177</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B15" s="7">
         <f>'Bids as Written'!D10</f>
@@ -5246,12 +5482,12 @@
         <v>1700</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B16" s="2" t="str">
         <f>Terms!D4</f>
@@ -5259,7 +5495,7 @@
       </c>
       <c r="C16" s="2" t="str">
         <f>Terms!D5</f>
-        <v>Destination</v>
+        <v>Origin, shipping plant</v>
       </c>
       <c r="D16" s="2" t="str">
         <f>Terms!D6</f>
@@ -5298,7 +5534,7 @@
         <v>Destination</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
@@ -5306,56 +5542,56 @@
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,B$3)</f>
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,B$3)</f>
         <v>0</v>
       </c>
       <c r="C17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,C$3)</f>
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,C$3)</f>
+        <v>6062.2</v>
+      </c>
+      <c r="D17" s="7">
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,D$3)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,D$3)</f>
+      <c r="E17" s="7">
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,E$3)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,E$3)</f>
+      <c r="F17" s="7">
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,F$3)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,F$3)</f>
+      <c r="G17" s="7">
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,G$3)</f>
+        <v>4991.2</v>
+      </c>
+      <c r="H17" s="7">
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,H$3)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,G$3)</f>
-        <v>4991.2</v>
-      </c>
-      <c r="H17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,H$3)</f>
+      <c r="I17" s="7">
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,I$3)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,I$3)</f>
+      <c r="J17" s="7">
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,J$3)</f>
+        <v>7663.72</v>
+      </c>
+      <c r="K17" s="7">
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,K$3)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,J$3)</f>
-        <v>7663.72</v>
-      </c>
-      <c r="K17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,K$3)</f>
+      <c r="L17" s="7">
+        <f>SUMIFS(Freight!$J$4:$J$18,Freight!$K$4:$K$18,L$3)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="7">
-        <f>SUMIFS(Freight!$J$4:$J$13,Freight!$K$4:$K$13,L$3)</f>
-        <v>0</v>
-      </c>
       <c r="M17" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B18" s="12">
         <f>IFERROR(VALUE(LEFT(Terms!E4,FIND("%",Terms!E4)-1))/100,0)</f>
@@ -5363,7 +5599,7 @@
       </c>
       <c r="C18" s="12">
         <f>IFERROR(VALUE(LEFT(Terms!E5,FIND("%",Terms!E5)-1))/100,0)</f>
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D18" s="12">
         <f>IFERROR(VALUE(LEFT(Terms!E6,FIND("%",Terms!E6)-1))/100,0)</f>
@@ -5387,7 +5623,7 @@
       </c>
       <c r="I18" s="12">
         <f>IFERROR(VALUE(LEFT(Terms!E11,FIND("%",Terms!E11)-1))/100,0)</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="J18" s="12">
         <f>IFERROR(VALUE(LEFT(Terms!E12,FIND("%",Terms!E12)-1))/100,0)</f>
@@ -5402,12 +5638,12 @@
         <v>0.02</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B19" s="2">
         <f>IFERROR(VALUE(MID(Terms!E4,FIND("%",Terms!E4)+2,FIND(",",Terms!E4)-FIND("%",Terms!E4)-2)),0)</f>
@@ -5415,7 +5651,7 @@
       </c>
       <c r="C19" s="2">
         <f>IFERROR(VALUE(MID(Terms!E5,FIND("%",Terms!E5)+2,FIND(",",Terms!E5)-FIND("%",Terms!E5)-2)),0)</f>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2">
         <f>IFERROR(VALUE(MID(Terms!E6,FIND("%",Terms!E6)+2,FIND(",",Terms!E6)-FIND("%",Terms!E6)-2)),0)</f>
@@ -5439,7 +5675,7 @@
       </c>
       <c r="I19" s="2">
         <f>IFERROR(VALUE(MID(Terms!E11,FIND("%",Terms!E11)+2,FIND(",",Terms!E11)-FIND("%",Terms!E11)-2)),0)</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J19" s="2">
         <f>IFERROR(VALUE(MID(Terms!E12,FIND("%",Terms!E12)+2,FIND(",",Terms!E12)-FIND("%",Terms!E12)-2)),0)</f>
@@ -5454,7 +5690,7 @@
         <v>20</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -5467,7 +5703,7 @@
       </c>
       <c r="C20" s="7">
         <f>IF(C19&gt;=Parameters!$B$4,ROUND(C14*C18,2),0)</f>
-        <v>990.67</v>
+        <v>0</v>
       </c>
       <c r="D20" s="7">
         <f>IF(D19&gt;=Parameters!$B$4,ROUND(D14*D18,2),0)</f>
@@ -5491,7 +5727,7 @@
       </c>
       <c r="I20" s="7">
         <f>IF(I19&gt;=Parameters!$B$4,ROUND(I14*I18,2),0)</f>
-        <v>0</v>
+        <v>989.01</v>
       </c>
       <c r="J20" s="7">
         <f>IF(J19&gt;=Parameters!$B$4,ROUND(J14*J18,2),0)</f>
@@ -5519,7 +5755,7 @@
       </c>
       <c r="C21" s="11">
         <f t="shared" si="1"/>
-        <v>100026.33</v>
+        <v>99700.2</v>
       </c>
       <c r="D21" s="11">
         <f t="shared" si="1"/>
@@ -5543,7 +5779,7 @@
       </c>
       <c r="I21" s="11">
         <f t="shared" si="1"/>
-        <v>100079</v>
+        <v>99761.99</v>
       </c>
       <c r="J21" s="11">
         <f t="shared" si="1"/>
@@ -5558,7 +5794,7 @@
         <v>103793.46</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
@@ -5571,7 +5807,7 @@
       </c>
       <c r="C22" s="7">
         <f>'Bids as Written'!F11</f>
-        <v>101317</v>
+        <v>93938</v>
       </c>
       <c r="D22" s="7">
         <f>'Bids as Written'!H11</f>
@@ -5595,7 +5831,7 @@
       </c>
       <c r="I22" s="7">
         <f>'Bids as Written'!R11</f>
-        <v>101959</v>
+        <v>102631</v>
       </c>
       <c r="J22" s="7">
         <f>'Bids as Written'!T11</f>
@@ -5667,7 +5903,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B24" s="9">
         <f>'Bid Receipt'!F4</f>
@@ -5675,7 +5911,7 @@
       </c>
       <c r="C24" s="9">
         <f>'Bid Receipt'!F5</f>
-        <v>202610060933</v>
+        <v>202610060952</v>
       </c>
       <c r="D24" s="9">
         <f>'Bid Receipt'!F6</f>
@@ -5699,7 +5935,7 @@
       </c>
       <c r="I24" s="9">
         <f>'Bid Receipt'!F11</f>
-        <v>202610051137</v>
+        <v>202610021026</v>
       </c>
       <c r="J24" s="9">
         <f>'Bid Receipt'!F12</f>
@@ -5719,7 +5955,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B25" s="2" t="str">
         <f>IF(B23="Responsive",COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&lt;"&amp;(B21-Parameters!$B$7))+COUNTIFS($B$23:$L$23,"Responsive",$B$21:$L$21,"&gt;="&amp;(B21-Parameters!$B$7),$B$21:$L$21,"&lt;="&amp;(B21+Parameters!$B$7),$B$24:$L$24,"&lt;"&amp;B24)+1,"Set aside")</f>
@@ -5766,12 +6002,12 @@
         <v>Set aside</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B27" s="7">
         <f>_xlfn.MINIFS(B21:L21,B23:L23,"Responsive")</f>
@@ -5780,7 +6016,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B28" s="2" t="str">
         <f>INDEX($B$3:$L$3,MATCH(1,$B$25:$L$25,0))</f>
@@ -5789,7 +6025,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B29" s="2" t="str">
         <f>Responsibility!B18</f>
@@ -5802,12 +6038,12 @@
       </c>
       <c r="B30" s="7">
         <f>Responsibility!B19</f>
-        <v>100079</v>
+        <v>99761.99</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B31" s="2" t="str">
         <f>INDEX($B$3:$L$3,MATCH(MIN(B22:L22),B22:L22,0))</f>
@@ -5820,12 +6056,12 @@
       </c>
       <c r="B32" s="2" t="str">
         <f>IF(B30&gt;Parameters!$B$5,"Vice president of operations","Director of supply chain")</f>
-        <v>Vice president of operations</v>
+        <v>Director of supply chain</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -5850,7 +6086,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -5861,25 +6097,25 @@
         <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -6071,11 +6307,11 @@
       </c>
       <c r="C9" s="10">
         <f>'Bids as Written'!E5</f>
-        <v>0.597</v>
+        <v>0.551</v>
       </c>
       <c r="D9" s="10">
         <f>Evaluation!C4</f>
-        <v>0.597</v>
+        <v>0.551</v>
       </c>
       <c r="E9" s="2">
         <f>Parameters!B15</f>
@@ -6083,11 +6319,11 @@
       </c>
       <c r="F9" s="7">
         <f>'Bids as Written'!F5</f>
-        <v>26865</v>
+        <v>24795</v>
       </c>
       <c r="G9" s="7">
         <f>Evaluation!C9</f>
-        <v>26865</v>
+        <v>24795</v>
       </c>
       <c r="H9" s="7">
         <f t="shared" si="0"/>
@@ -6107,11 +6343,11 @@
       </c>
       <c r="C10" s="10">
         <f>'Bids as Written'!E6</f>
-        <v>0.4</v>
+        <v>0.371</v>
       </c>
       <c r="D10" s="10">
         <f>Evaluation!C5</f>
-        <v>0.4</v>
+        <v>0.371</v>
       </c>
       <c r="E10" s="2">
         <f>Parameters!B16</f>
@@ -6119,11 +6355,11 @@
       </c>
       <c r="F10" s="7">
         <f>'Bids as Written'!F6</f>
-        <v>25900</v>
+        <v>24044</v>
       </c>
       <c r="G10" s="7">
         <f>Evaluation!C10</f>
-        <v>25600</v>
+        <v>23744</v>
       </c>
       <c r="H10" s="7">
         <f t="shared" si="0"/>
@@ -6143,11 +6379,11 @@
       </c>
       <c r="C11" s="10">
         <f>'Bids as Written'!E7</f>
-        <v>0.284</v>
+        <v>0.263</v>
       </c>
       <c r="D11" s="10">
         <f>Evaluation!C6</f>
-        <v>0.284</v>
+        <v>0.263</v>
       </c>
       <c r="E11" s="2">
         <f>Parameters!B17</f>
@@ -6155,11 +6391,11 @@
       </c>
       <c r="F11" s="7">
         <f>'Bids as Written'!F7</f>
-        <v>7668</v>
+        <v>7101</v>
       </c>
       <c r="G11" s="7">
         <f>Evaluation!C11</f>
-        <v>7668</v>
+        <v>7101</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" si="0"/>
@@ -6179,11 +6415,11 @@
       </c>
       <c r="C12" s="10">
         <f>'Bids as Written'!E8</f>
-        <v>1.702</v>
+        <v>1.576</v>
       </c>
       <c r="D12" s="10">
         <f>Evaluation!C7</f>
-        <v>1.702</v>
+        <v>1.576</v>
       </c>
       <c r="E12" s="2">
         <f>Parameters!B18</f>
@@ -6191,11 +6427,11 @@
       </c>
       <c r="F12" s="7">
         <f>'Bids as Written'!F8</f>
-        <v>15318</v>
+        <v>14184</v>
       </c>
       <c r="G12" s="7">
         <f>Evaluation!C12</f>
-        <v>15318</v>
+        <v>14184</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="0"/>
@@ -6215,11 +6451,11 @@
       </c>
       <c r="C13" s="10">
         <f>'Bids as Written'!E9</f>
-        <v>0.984</v>
+        <v>0.911</v>
       </c>
       <c r="D13" s="10">
         <f>Evaluation!C8</f>
-        <v>0.984</v>
+        <v>0.911</v>
       </c>
       <c r="E13" s="2">
         <f>Parameters!B19</f>
@@ -6227,11 +6463,11 @@
       </c>
       <c r="F13" s="7">
         <f>'Bids as Written'!F9</f>
-        <v>23616</v>
+        <v>21864</v>
       </c>
       <c r="G13" s="7">
         <f>Evaluation!C13</f>
-        <v>23616</v>
+        <v>21864</v>
       </c>
       <c r="H13" s="7">
         <f t="shared" si="0"/>
@@ -6244,7 +6480,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
@@ -6280,7 +6516,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -6316,7 +6552,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
@@ -6352,7 +6588,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -6388,7 +6624,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -6424,7 +6660,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -6460,7 +6696,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -6496,7 +6732,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" s="2">
         <v>3</v>
@@ -6532,7 +6768,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B22" s="2">
         <v>4</v>
@@ -6568,7 +6804,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B23" s="2">
         <v>5</v>
@@ -6604,7 +6840,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
@@ -6640,7 +6876,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B25" s="2">
         <v>2</v>
@@ -6676,7 +6912,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
@@ -6712,7 +6948,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B27" s="2">
         <v>4</v>
@@ -6748,7 +6984,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
@@ -6784,7 +7020,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
@@ -6820,7 +7056,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B30" s="2">
         <v>2</v>
@@ -6856,7 +7092,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B31" s="2">
         <v>3</v>
@@ -6892,7 +7128,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B32" s="2">
         <v>4</v>
@@ -6928,7 +7164,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B33" s="2">
         <v>5</v>
@@ -6964,7 +7200,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B34" s="2">
         <v>1</v>
@@ -7000,7 +7236,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B35" s="2">
         <v>2</v>
@@ -7036,7 +7272,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B36" s="2">
         <v>3</v>
@@ -7072,7 +7308,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B37" s="2">
         <v>4</v>
@@ -7108,7 +7344,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -7144,7 +7380,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
@@ -7180,7 +7416,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B40" s="2">
         <v>2</v>
@@ -7216,7 +7452,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B41" s="2">
         <v>3</v>
@@ -7252,7 +7488,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B42" s="2">
         <v>4</v>
@@ -7288,18 +7524,18 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B43" s="2">
         <v>5</v>
       </c>
       <c r="C43" s="10">
         <f>'Bids as Written'!Q9</f>
-        <v>0.957</v>
+        <v>0.985</v>
       </c>
       <c r="D43" s="10">
         <f>Evaluation!I8</f>
-        <v>0.957</v>
+        <v>0.985</v>
       </c>
       <c r="E43" s="2">
         <f>Parameters!B19</f>
@@ -7307,11 +7543,11 @@
       </c>
       <c r="F43" s="7">
         <f>'Bids as Written'!R9</f>
-        <v>22968</v>
+        <v>23640</v>
       </c>
       <c r="G43" s="7">
         <f>Evaluation!I13</f>
-        <v>22968</v>
+        <v>23640</v>
       </c>
       <c r="H43" s="7">
         <f t="shared" si="1"/>
@@ -7504,7 +7740,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B49" s="2">
         <v>1</v>
@@ -7540,7 +7776,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B50" s="2">
         <v>2</v>
@@ -7576,7 +7812,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B51" s="2">
         <v>3</v>
@@ -7612,7 +7848,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B52" s="2">
         <v>4</v>
@@ -7648,7 +7884,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B53" s="2">
         <v>5</v>
@@ -7684,7 +7920,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B54" s="2">
         <v>1</v>
@@ -7720,7 +7956,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B55" s="2">
         <v>2</v>
@@ -7756,7 +7992,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B56" s="2">
         <v>3</v>
@@ -7792,7 +8028,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B57" s="2">
         <v>4</v>
@@ -7828,7 +8064,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B58" s="2">
         <v>5</v>
@@ -7873,7 +8109,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="H60" s="2">
         <f>COUNTIF(I4:I58,"Unit price changed*")</f>
@@ -7882,7 +8118,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -7900,87 +8136,87 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="144" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="160" customHeight="1" x14ac:dyDescent="0.2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="160" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="128" customHeight="1" x14ac:dyDescent="0.2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="128" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="128" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -8308,10 +8544,10 @@
         <v>25695</v>
       </c>
       <c r="E5" s="10">
-        <v>0.597</v>
+        <v>0.551</v>
       </c>
       <c r="F5" s="7">
-        <v>26865</v>
+        <v>24795</v>
       </c>
       <c r="G5" s="10">
         <v>0.594</v>
@@ -8382,10 +8618,10 @@
         <v>25472</v>
       </c>
       <c r="E6" s="10">
-        <v>0.4</v>
+        <v>0.371</v>
       </c>
       <c r="F6" s="7">
-        <v>25900</v>
+        <v>24044</v>
       </c>
       <c r="G6" s="10">
         <v>0.404</v>
@@ -8456,10 +8692,10 @@
         <v>9936</v>
       </c>
       <c r="E7" s="10">
-        <v>0.284</v>
+        <v>0.263</v>
       </c>
       <c r="F7" s="7">
-        <v>7668</v>
+        <v>7101</v>
       </c>
       <c r="G7" s="10">
         <v>0.288</v>
@@ -8530,10 +8766,10 @@
         <v>14895</v>
       </c>
       <c r="E8" s="10">
-        <v>1.702</v>
+        <v>1.576</v>
       </c>
       <c r="F8" s="7">
-        <v>15318</v>
+        <v>14184</v>
       </c>
       <c r="G8" s="10">
         <v>1.702</v>
@@ -8604,10 +8840,10 @@
         <v>22560</v>
       </c>
       <c r="E9" s="10">
-        <v>0.984</v>
+        <v>0.911</v>
       </c>
       <c r="F9" s="7">
-        <v>23616</v>
+        <v>21864</v>
       </c>
       <c r="G9" s="10">
         <v>0.972</v>
@@ -8640,10 +8876,10 @@
         <v>23184</v>
       </c>
       <c r="Q9" s="10">
-        <v>0.957</v>
+        <v>0.985</v>
       </c>
       <c r="R9" s="7">
-        <v>22968</v>
+        <v>23640</v>
       </c>
       <c r="S9" s="10">
         <v>0.9</v>
@@ -8712,7 +8948,7 @@
       </c>
       <c r="F11" s="11">
         <f>SUM(F5:F10)</f>
-        <v>101317</v>
+        <v>93938</v>
       </c>
       <c r="H11" s="11">
         <f>SUM(H5:H10)</f>
@@ -8736,7 +8972,7 @@
       </c>
       <c r="R11" s="11">
         <f>SUM(R5:R10)</f>
-        <v>101959</v>
+        <v>102631</v>
       </c>
       <c r="T11" s="11">
         <f>SUM(T5:T10)</f>
@@ -8858,10 +9094,10 @@
         <v>133</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>127</v>
@@ -8870,30 +9106,30 @@
         <v>128</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>127</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>127</v>
@@ -8902,30 +9138,30 @@
         <v>128</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>127</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>127</v>
@@ -8934,62 +9170,62 @@
         <v>128</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>127</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>127</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>127</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>133</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>127</v>
@@ -8998,21 +9234,21 @@
         <v>128</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>127</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>133</v>
@@ -9021,7 +9257,7 @@
         <v>125</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>127</v>
@@ -9030,30 +9266,30 @@
         <v>128</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>127</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>127</v>
@@ -9062,7 +9298,7 @@
         <v>128</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>127</v>
@@ -9082,33 +9318,33 @@
         <v>168</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>127</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>127</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>133</v>
@@ -9117,7 +9353,7 @@
         <v>125</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>127</v>
@@ -9126,45 +9362,45 @@
         <v>128</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>127</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>127</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -9187,7 +9423,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -9195,19 +9431,19 @@
         <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9216,19 +9452,19 @@
         <v>Brannock Box Company</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9237,19 +9473,19 @@
         <v>Dahlgren Paper Box Co.</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9258,19 +9494,19 @@
         <v>Halvard Corrugated</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>127</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9279,13 +9515,13 @@
         <v>Kessel Container Corp.</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>200</v>
@@ -9303,16 +9539,16 @@
         <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>203</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9327,13 +9563,13 @@
         <v>205</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9354,7 +9590,7 @@
         <v>209</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9369,13 +9605,13 @@
         <v>211</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>212</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9387,16 +9623,16 @@
         <v>213</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>215</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9405,19 +9641,19 @@
         <v>Thorsgard Box &amp; Label</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>127</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9426,24 +9662,24 @@
         <v>Wenzel &amp; Krause Corrugated</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>220</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -9470,7 +9706,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -9478,51 +9714,51 @@
         <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="G4" s="9">
         <f t="shared" ref="G4:G9" si="0">VALUE(RIGHT(E4,4)&amp;LEFT(E4,2)&amp;MID(E4,4,2)&amp;LEFT(F4,2)&amp;RIGHT(F4,2))</f>
@@ -9536,27 +9772,27 @@
         <v>127</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="G5" s="9">
         <f t="shared" si="0"/>
@@ -9570,27 +9806,27 @@
         <v>127</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="0"/>
@@ -9604,7 +9840,7 @@
         <v>127</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -9612,53 +9848,53 @@
         <v>131</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="G7" s="9">
         <f t="shared" si="0"/>
-        <v>202610060938</v>
+        <v>202610060956</v>
       </c>
       <c r="H7" s="2" t="str">
         <f>IF(G7&lt;Parameters!$B$12,"Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="G8" s="9">
         <f t="shared" si="0"/>
@@ -9672,27 +9908,27 @@
         <v>127</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="G9" s="9">
         <f t="shared" si="0"/>
@@ -9706,7 +9942,7 @@
         <v>127</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -9717,24 +9953,24 @@
         <v>80</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
@@ -9765,10 +10001,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="10">
-        <v>0.597</v>
+        <v>0.551</v>
       </c>
       <c r="D14" s="10">
-        <v>0.594</v>
+        <v>0.548</v>
       </c>
       <c r="E14" s="2">
         <v>7</v>
@@ -9784,7 +10020,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B15" s="2">
         <v>1</v>
@@ -9809,7 +10045,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -9834,7 +10070,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
@@ -9859,7 +10095,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -9884,7 +10120,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -9909,7 +10145,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B21" s="2">
         <f>COUNTIF(F13:F19,"Yes")</f>
@@ -9918,7 +10154,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B22" s="2">
         <f>COUNTIF(F13:F19,"No")</f>
@@ -9927,7 +10163,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -9950,7 +10186,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -9961,19 +10197,19 @@
         <v>118</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -10013,11 +10249,11 @@
       </c>
       <c r="D5" s="7">
         <f>'Bids as Written'!F11</f>
-        <v>101317</v>
+        <v>93938</v>
       </c>
       <c r="E5" s="7">
         <f>ROUND(D5*Parameters!$B$11,2)</f>
-        <v>5065.85</v>
+        <v>4696.9</v>
       </c>
       <c r="F5" s="7">
         <f t="shared" si="0"/>
@@ -10172,11 +10408,11 @@
       </c>
       <c r="D11" s="7">
         <f>'Bids as Written'!R11</f>
-        <v>101959</v>
+        <v>102631</v>
       </c>
       <c r="E11" s="7">
         <f>ROUND(D11*Parameters!$B$11,2)</f>
-        <v>5097.95</v>
+        <v>5131.55</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" si="0"/>
@@ -10273,7 +10509,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -10297,7 +10533,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -10305,22 +10541,22 @@
         <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -10329,16 +10565,16 @@
         <v>Brannock Box Company</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="F4" s="9">
         <f t="shared" ref="F4:F14" si="0">VALUE(RIGHT(D4,4)&amp;LEFT(D4,2)&amp;MID(D4,4,2)&amp;LEFT(E4,2)&amp;RIGHT(E4,2))</f>
@@ -10351,20 +10587,23 @@
         <v>Dahlgren Paper Box Co.</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="F5" s="9">
         <f t="shared" si="0"/>
-        <v>202610060933</v>
+        <v>202610060952</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -10379,7 +10618,7 @@
         <v>286</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>287</v>
@@ -10423,7 +10662,7 @@
         <v>293</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>294</v>
@@ -10448,7 +10687,7 @@
         <v>297</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>298</v>
@@ -10470,7 +10709,7 @@
         <v>300</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>301</v>
@@ -10492,14 +10731,14 @@
         <v>303</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>233</v>
+        <v>290</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>304</v>
       </c>
       <c r="F11" s="9">
         <f t="shared" si="0"/>
-        <v>202610051137</v>
+        <v>202610021026</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>305</v>
@@ -10517,7 +10756,7 @@
         <v>307</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>308</v>
@@ -10525,9 +10764,6 @@
       <c r="F12" s="9">
         <f t="shared" si="0"/>
         <v>202610060815</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -10536,16 +10772,16 @@
         <v>Thorsgard Box &amp; Label</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="F13" s="9">
         <f t="shared" si="0"/>
@@ -10558,16 +10794,16 @@
         <v>Wenzel &amp; Krause Corrugated</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="F14" s="9">
         <f t="shared" si="0"/>
@@ -10576,7 +10812,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B16" s="2">
         <f>COUNTIF(F4:F14,"&lt;="&amp;Parameters!$B$12)</f>
@@ -10585,7 +10821,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -10612,173 +10848,173 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>320</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>112</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="I4" s="2" t="str">
         <f>IF(G4="","Open","Cleared")</f>
         <v>Cleared</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>338</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I5" s="2" t="str">
         <f>IF(G5="","Open","Cleared")</f>
         <v>Cleared</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="I6" s="2" t="str">
         <f>IF(G6="","Open","Cleared")</f>
         <v>Open</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="I7" s="2" t="str">
         <f>IF(G7="","Open","Cleared")</f>
         <v>Cleared</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
